--- a/VV-FUTURES-ALL-CLAIMS-AND-SOURCES.xlsx
+++ b/VV-FUTURES-ALL-CLAIMS-AND-SOURCES.xlsx
@@ -18027,7 +18027,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t/>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t/>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t/>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t/>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t/>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t/>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -18582,7 +18582,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t/>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -18619,7 +18619,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t/>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -18692,6 +18692,9368 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>link-bd808441fb2109553f</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Anticipated Developments in OTT Platforms Over the Next Few Years</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.14445/22312803/ijctt-v71i5p112</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, few; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The OTT platform industry is continuously evolving and advancing, and there are a number of anticipated developments expected over the next few years. The use of subscription-based models will continue to grow as it provides a reliable source of revenue for platforms and a predictable cost for consumers. Furthermore, the rise of ad-supported models is expected to gain traction as a way to increase accessibility to content and cater to those who cannot afford a subscription. The development of new technologies, such as virtual and augmented reality, will offer a new dimension to the viewing experience and may become a key differentiator for platforms. Additionally, advancements in streaming quality and device capabilities are expected to enhance the overall viewing experience and attract more consumers. This article aims to explore the anticipated advancements in OTT platforms, including the emergence of new players in the market, changes in content distribution and monetization strategies, the role of artificial intelligence and machine learning, and the impact of 5G technology. These developments will shape the future of the entertainment industry and have far-reaching implications for consumers, content creators, and distributors alike. Understanding these anticipated changes is crucial for anyone with a stake in the entertainment industry to stay ahead of the curve and remain competitive.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>link-e6c2081445d17d65b3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Circulation dampened heat extremes intensification over the Midwest USA and amplified over Western Europe</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s43247-023-01096-7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, decades, western; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Abstract Globally heat extremes have intensified in recent decades. However, while Western Europe shows a remarkably strong intensification of heat extremes, the Midwest United States experienced only weak warming of warmest nighttime and even a weak decrease in the intensity of daytime heat extremes since 1979. Here, we show that for daytime heat extremes in the Midwest United States atmospheric circulation induced ~1 °C cooling since 1979, reversing the thermodynamic warming trend. The observed circulation-induced trend is outside the multi-model range and the overall trend at the very low end of it. In Western Europe circulation greatly amplified warming by ~1 °C, accounting to one third of observed trend. The observed circulation- and thermodynamic-induced trends, as well as the total observed trends are at the high end of the model range in Western Europe. Understanding whether the strong circulation-induced trends are externally forced or unforced internal variability remains key to constrain future trends in heat extremes.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>link-5c105df83668d52d9b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Compound precipitation and wind extremes over Europe and their relationship to extratropical cyclones</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.wace.2021.100342</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, few, many, western, large, increases; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Extratropical cyclones and their associated extreme precipitation and winds can have a severe impact on society and the co-occurrence between the two extremes is important when assessing risk. In this study the extremal dependency measure, χ, is used to quantify the co-occurrence of extreme precipitation and wind gusts, and is investigated at individual grid points and spatially over Europe. Results using three observational datasets and a higher spatial and temporal resolution version of ERA5 than previously used confirm previous studies. Over Europe high co-occurrence is found over western coasts and low co-occurrence is found over eastern coasts. All datasets have qualitatively similar spatial patterns over most regions of Europe excluding some regions of high topography where ERA5 χ values are much larger. ERA5 represents the timings of daily extreme co-occurring events well, compared to observations. The differences in precipitation accumulation timescales are also accounted for by considering hourly, 6, 24 and 48 hourly co-occurrence. In a few regions co-occurrence changes with longer accumulations, indicating the different speeds and sizes of weather systems affecting these regions. χ in most regions has little increase by allowing a 24 h lag and lead between the precipitation and wind, with a few exceptions where χ is increased by up to 24%. Regions with the larger of these increases are on or around elevated topography. Using an objective feature tracking method, insight into the spatial pattern of extreme precipitation and wind within cyclones over Europe is given. As well as suggesting how many hours apart the extremes occur from one another in a particular location. Extreme co-occurring events are associated with cyclones far more of the time than non extreme events. Given an extreme co-occurring event the chance of a cyclone being within 1110 km is more than 70% for much of Europe. Regions with low co-occurrence have extremes caused by different weather systems and regions with large co-occurrence have both extremes caused by the same weather system. Cyclones linked to extreme events, particularly co-occurring and extreme wind, have larger intensity than those not and for most of Europe these cyclones also have faster mean speed.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>link-8901e41f10046a466a</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Modelling Eurasian lynx populations in Western Europe: What prospects for the next 50 years?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1101/2021.10.22.465393</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, western, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Abstract Persistence of populations may be uncertain for large carnivore species, especially for those established in human-dominated landscapes. Here, we studied the Eurasian lynx in Western Europe established in the Upper Rhine meta-population (i.e., Jura, Vosges-Palatinian and Black Forest populations) and the Alpine population. These populations are currently considered endangered or critically endangered due to high anthropogenic mortality, small population size and low genetic diversity, and isolation. We assessed lynx persistence over a 50-year time horizon by implementing a spatially-explicit individual-based model, while accounting for road mortality and habitat selection. Forecasts showed a steady growth rapidly reaching a more stable phase for the Alpine and Jura populations, and a more heterogeneous positive growth with less precision for the Vosges-Palatinian and Black Forest populations. Exchanges of individuals between populations were limited, the Jura population playing the role of a crossroad. Finally, the persistence of lynx in Western Europe seems likely on a large scale over the next 50 years. Indeed, simulations showed high female occupancy as well as average lynx density over the core areas of the four studied populations. Nevertheless, these results should be interpreted with the model limitations in mind, concerning the absence of movement barriers and inbreeding depression.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>link-a3f3e1ac175c998b33</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>An annotated checklist of bryophytes of Europe, Macaronesia and Cyprus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/03736687.2019.1694329</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, few, many; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Introduction.Following on from work on the European bryophyte Red List, the taxonomically and nomenclaturally updated spreadsheets used for that project have been expanded into a new checklist for the bryophytes of Europe.Methods.A steering group of ten European bryologists was convened, and over the course of a year, the spreadsheets were compared with previous European checklists, and all changes noted.Recent literature was searched extensively.A taxonomic system was agreed, and the advice and expertise of many European bryologists sought.Key results.A new European checklist of bryophytes, comprising hornworts, liverworts and mosses, is presented.Fifteen new combinations are proposed.Conclusions.This checklist provides a snapshot of the current European bryophyte flora in 2019.It will already be out-of-date on publication, and further research, particularly molecular work, can be expected to result in many more changes over the next few years.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>link-89558e02d2309f2b60</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Diverging hydrological drought traits over Europe with global warming</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5194/hess-24-5919-2020</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, many, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Abstract. Climate change is anticipated to alter the demand and supply of water at the earth's surface. Since many societal impacts from a lack of water happen under drought conditions, it is important to understand how droughts may develop with climate change. This study shows how hydrological droughts will change across Europe with increasing global warming levels (GWL of 1.5, 2 and 3 K above preindustrial temperature). We employ a low-flow index derived from river discharge simulations of a spatially-distributed physically-based hydrological and water use model, which was forced with a large ensemble of regional climate model projections under a high emissions (RCP8.5) and moderate mitigation (RCP4.5) pathway. Different traits of drought, including severity, duration and frequency, were investigated. The projected changes in these treats identify four main sub-regions in Europe that are characterized by somehow homogeneous and distinct behaviours with a clear southwest/northeast contrast. The Mediterranean and Boreal sub-regions of Europe show strong, but opposite, changes at all three GWLs, with the former area mostly interested by stronger droughts (with larger differences at 3 K) while the latter sees a reduction in droughts. In the Atlantic and Continental sub-regions the changes are less marked and characterized by a larger uncertainty, especially at the 1.5 and 2 K GWLs. Combining the projections in drought hazard with population and agricultural information shows that with 3 K global warming an additional 11 million people and 4.5 million ha of agricultural land will be exposed to droughts every year, on average. These are mostly located in the Mediterranean and Atlantic regions of Europe.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>link-f8a6113dacab98c94b</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Explaining carsharing supply across Western European cities</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/15568318.2018.1542756</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: many, western, countries, striking; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Carsharing can partially replace private ownership of vehicles with a service that allows the use of a car temporarily on an on-demand basis. In this study, we analyze the supply of shared cars across 177 cities in five Western European countries (Belgium, France, Germany, The Netherlands, United Kingdom), while distinguishing between the traditional business-to-consumer (B2C) business model and the more recent peer-to-peer (P2P) business model. The data on carsharing supply is individually collected of all operators in the respective cities, while data of city characteristics is drawn from international or national statistical databases. We explain carsharing supply using comparable data of 14 explanatory variables. The results indicate that carsharing is popular in cities with a high educational level or university presence and, in the B2C case, with many green party votes. Furthermore, carsharing is less popular in cities with many car commuters. Particularly striking are the differences between countries, with peer-to-peer carsharing being especially popular in French cities and business-to-consumer carsharing in Germany. We reflect on the findings in the light of (sustainable) mobility policy options.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>link-bfcd3e650b64cfd799</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Prevalence of Age-Related Macular Degeneration in Europe</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.ophtha.2017.05.035</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, decades, countries; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PURPOSE: Age-related macular degeneration (AMD) is a frequent, complex disorder in elderly of European ancestry. Risk profiles and treatment options have changed considerably over the years, which may have affected disease prevalence and outcome. We determined the prevalence of early and late AMD in Europe from 1990 to 2013 using the European Eye Epidemiology (E3) consortium, and made projections for the future. DESIGN: Meta-analysis of prevalence data. PARTICIPANTS: A total of 42 080 individuals 40 years of age and older participating in 14 population-based cohorts from 10 countries in Europe. METHODS: AMD was diagnosed based on fundus photographs using the Rotterdam Classification. Prevalence of early and late AMD was calculated using random-effects meta-analysis stratified for age, birth cohort, gender, geographic region, and time period of the study. Best-corrected visual acuity (BCVA) was compared between late AMD subtypes; geographic atrophy (GA) and choroidal neovascularization (CNV). MAIN OUTCOME MEASURES: Prevalence of early and late AMD, BCVA, and number of AMD cases. RESULTS: Prevalence of early AMD increased from 3.5% (95% confidence interval [CI] 2.1%-5.0%) in those aged 55-59 years to 17.6% (95% CI 13.6%-21.5%) in those aged ≥85 years; for late AMD these figures were 0.1% (95% CI 0.04%-0.3%) and 9.8% (95% CI 6.3%-13.3%), respectively. We observed a decreasing prevalence of late AMD after 2006, which became most prominent after age 70. Prevalences were similar for gender across all age groups except for late AMD in the oldest age category, and a trend was found showing a higher prevalence of CNV in Northern Europe. After 2006, fewer eyes and fewer ≥80-year-old subjects with CNV were visually impaired (P = 0.016). Projections of AMD showed an almost doubling of affected persons despite a decreasing prevalence. By 2040, the number of individuals in Europe with early AMD will range between 14.9 and 21.5 million, and for late AMD between 3.9 and 4.8 million. CONCLUSION: We observed a decreasing prevalence of AMD and an improvement in visual acuity in CNV occuring over the past 2 decades in Europe. Healthier lifestyles and implementation of anti-vascular endothelial growth factor treatment are the most likely explanations. Nevertheless, the numbers of affected subjects will increase considerably in the next 2 decades. AMD continues to remain a significant public health problem among Europeans.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>link-4d4d1ea570e6c93ae6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Children’s health in Europe - challenges for the next decades</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/heapro/dax023</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, decades, many; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>These reflections from a Child Public Health perspective underline the dramatic changes in children's conditions in Europe over this last century, including a considerable improvement in health. However, we still face problems, disturbing facts and alarming signs. There are important gaps in our knowledge about essential areas of children's health panorama and about particularly vulnerable sub-groups of children, which are less healthy, less well cared for and not enjoying the good conditions of life. We also see an evident lack of the child's perspective, implying acknowledgement and action on the views of the children themselves. Moreover, in spite of the generally improving standard, societal inequity in economy, education and health is increasing and the recent economic crises have struck hard on families with children. There are many good signs implying continuing progress for children and their conditions and also an improved respect for their rights. But with the increasing segregation in our societies, the risk is imminent that the health problems will increase, and that some groups get left far behind. Although actions on this field are primarily a political responsibility, people working with children can make a difference. There are also many examples of projects, particularly on local levels, where professionals act to promote children's health, prevent their ill-health and facilitate their health behaviour, rather than to repair their diseases. Children's particular needs and protection is now generally accepted, and the growing concern for their rights opens a window to the future for a more powerful child health advocacy.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>link-b116c362f8c69ca133</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Understanding the rapid summer warming and changes in temperature extremes since the mid-1990s over Western Europe</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00382-016-3158-8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, few, decades, many, western; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Analysis of observations indicates that there was a rapid increase in summer (June–August) mean surface air temperature (SAT) since the mid-1990s over Western Europe. Accompanying this rapid warming are significant increases in summer mean daily maximum temperature, daily minimum temperature, annual hottest day temperature and warmest night temperature, and an increase in frequency of summer days and tropical nights, while the change in the diurnal temperature range (DTR) is small. This study focuses on understanding causes of the rapid summer warming and associated temperature extreme changes. A set of experiments using the atmospheric component of the state-of-the-art HadGEM3 global climate model have been carried out to quantify relative roles of changes in sea surface temperature (SST)/sea ice extent (SIE), anthropogenic greenhouse gases (GHGs), and anthropogenic aerosols (AAer). Results indicate that the model forced by changes in all forcings reproduces many of the observed changes since the mid-1990s over Western Europe. Changes in SST/SIE explain 62.2 ± 13.0 % of the area averaged seasonal mean warming signal over Western Europe, with the remaining 37.8 ± 13.6 % of the warming explained by the direct impact of changes in GHGs and AAer. Results further indicate that the direct impact of the reduction of AAer precursor emissions over Europe, mainly through aerosol-radiation interaction with additional contributions from aerosol-cloud interaction and coupled atmosphere-land surface feedbacks, is a key factor for increases in annual hottest day temperature and in frequency of summer days. It explains 45.5 ± 17.6 % and 40.9 ± 18.4 % of area averaged signals for these temperature extremes. The direct impact of the reduction of AAer precursor emissions over Europe acts to increase DTR locally, but the change in DTR is countered by the direct impact of GHGs forcing. In the next few decades, greenhouse gas concentrations will continue to rise and AAer precursor emissions over Europe and North America will continue to decline. Our results suggest that the changes in summer seasonal mean SAT and temperature extremes over Western Europe since the mid-1990s are most likely to be sustained or amplified in the near term, unless other factors intervene.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>link-b5f62d9c630e5b6f04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>An overview of the progress and challenges of peatland restoration in Western Europe</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/rec.12415</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, many, western, countries; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Abstract Peatlands are the most efficient terrestrial carbon store on Earth, and deliver multiple other ecosystem services including climate regulation, water purification, preservation of ecological and archaeological records, etc. Disturbed and degraded peatlands do not provide the same ecological services and thus bear a significant cost to society. Because this cost may be alleviated by appropriate restoration measures, money is being invested in peatland restoration projects around the world. Here, we review over 25 years of restoration in Western Europe. First, we provide an overview of techniques used in different contexts and evaluate the status of the evidence base for restoration outcomes. Between 1993 and 2015, the EU‐LIFE nature programme alone invested 167.6M € in 80 projects, which aim to restore over 913 km2 of peatland habitats in Western European countries, mostly in protected sites part of the Natura 2000 EU network. This represents less than 2% of the total remaining area of peatlands in these countries, most of which have been impacted to some degree by anthropogenic disturbances. Potential for restoration should be considered in nondesignated sites. We reviewed a number of case studies covering a range of restoration approaches used in different parts of Western Europe. We found that published evidence of restoration progress was limited to specific sites/areas, and in many cases lacked baseline measurements and clear goals, that is, measurable target or contemporary reference(s). We discuss barriers and opportunities to turn the tide for peatland restoration in Western Europe and promote the establishment of robust, standardized monitoring schemes.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>link-441c793a058d365d26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pneumococcal serotype evolution in Western Europe</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s12879-015-1147-x</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: many, western, countries, introduced; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Pneumococcal diseases remain a leading cause of vaccine-preventable death worldwide in children &lt;5 years of age. The seven-valent pneumococcal conjugate vaccine (PCV7) was approved in 2001 in Europe and was introduced into the national immunization programmes of many European countries from 2006-2008. In 2009, higher-valent PCVs (PCV10 and PCV13) became available, replacing PCV7 from 2009-2011. This article describes the evolution of vaccine and non-vaccine serotypes causing invasive pneumococcal disease (IPD) following the introduction of PCVs in Western Europe, based on data from publicly-available medical publications and national surveillance systems from January 2010 to May 2015. DISCUSSION: In countries with high vaccine uptake, 5-7 years after PCV7 introduction IPD caused by vaccine serotypes has almost disappeared in children. Non-PCV7 serotypes have emerged, particularly serotypes 19A, 7 F, 3 and 1. A rapid and significant reduction of the additional serotypes included in higher-valent vaccines has been observed consistently following the introduction of these vaccines. A significant and rapid decline of serotypes 19A, 7 F, 1 and 6A in both vaccine-eligible and older age groups has been observed in countries using PCV13 while serotype 19A and 3 has increased in countries using PCV10. Serotype 3 has become one of the most prevalent serotypes in adults, with some reduction only in the UK and France. Serotype diversity increased and varied by age group, the type of vaccine in use, and the time since the introduction of higher-valent PCVs. Serotypes that are currently more frequent include 24 F, 22 F, 8 and 15A in countries that use PCV13, and serotypes 19A and 3 in countries that use PCV10. Compared with the time before the introduction of higher valent PCVs, to date, there is no single '19A-like' serotype emerging across countries and most of the newly emerging non-PCV13 vaccine types are less invasive with a low case-carrier ratio. CONCLUSIONS: It is important to closely monitor not only evolving serotypes but also the magnitude of the effect in order to evaluate the overall impact of pneumococcal vaccination programmes and to initiate the appropriate vaccination strategy. Emerging serotypes may also need to be considered for the future development of new vaccines.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>link-3a0f7611966829ab85</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Update on HIV in Western Europe</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11904-014-0198-8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: western, countries, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>HIV infection in Western Europe is mainly concentrated among men who have sex with men, heterosexuals who acquired HIV from sub-Saharan African countries, and in people who inject drugs. The rate of newly diagnosed cases of HIV has remained roughly stable since 2004 whereas the number of people living with HIV has slowly increased due to new infections and the success of antiretroviral therapy in prolonging life. An ageing population is gradually emerging that will require additional care. There are large differences across countries in HIV testing rates, proportions of people who present to care with low CD4+ cell counts, accessibility to treatment and care, and rates of retention once in care. Improved collection of HIV surveillance data will benefit countries and help to understand their epidemic better. However, social inequalities experienced by people with HIV still remain in some regions and urgently need to be addressed.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>link-518f570e539c666859</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Are European countries prepared for the next big heat-wave?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurpub/ckt121</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, countries; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Heat-waves present severe dangers to populations' health. Due to climate change, an increase in the frequency and intensity of heat-waves is to be expected. Public health measures to prevent negative health effects have been developed in several member states of the World Health Organization (WHO) European Region over the past decade. METHODS: This study presents the first comprehensive assessment of the development of heat preparedness planning in WHO European Region member states, using a unique methodology based on criteria developed and pre-tested by the WHO. This indicator-based approach is based on eight core elements that are crucial components of heat-health action plans. RESULTS: Of 53 member states of the WHO European Region, 51 countries were included in the evaluation. Results show that 18 countries have developed heat-health action plans, whereas 33 others have not. The plans developed so far vary in the degree of comprehensiveness with regard to the core elements. Gaps in terms of plan coverage have predominantly been identified in the areas of (intersectorial) long-term measures, surveillance and plan evaluation. CONCLUSIONS: For better preparedness, it can be advocated for further improving, developing and implementing heat-wave preparedness planning and response in European countries. A focus should be placed on developing all elements and strong intersectorial coordination and cooperation as well as the successful implementation of surveillance and evaluation measures.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>link-e66752b297dc0d11cd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The Marshall Plan and Western European Reconstruction</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/9789400601079.004</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, next, many, western, countries, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>When the Marshall Plan was conceived in 1947, much of Western Europe was midway through a process of economic reconstruction, though it seemed that further progress was being choked by a lack of hard currency reserves. By the time the next four years had passed, recovery had been such that output had surged past its pre-war peak and programs were in place to foster economic collaboration and interdependence. Parallels between the situation in the Soviet Union and Eastern Europe at their own critical junctures in their transitions to democratic market economies at the end of the Cold War were suggestive. Just as the Marshall Plan had facilitated the rebuilding of post-World War II Europe, so the idea was revived as the means for facilitating the transformation of post-Cold War Europe. For many policy-makers and commentators the Marshall Plan was nothing more (and nothing less) than a metaphor for a deep-rooted feeling that the West should be doing more for its ex-adversaries on the other side of the Iron Curtain. The Cold War had suddenly been won, with very little anticipation and without NATO having to fire a shot. And when the arch-enemy, the Soviet Union, then proceeded to dissolve itself and embrace Western, capitalist standards and values, it almost defied belief. With the West anticipating a large ‘peace dividend’ there were many that felt that a generous, structured commitment of assistance would not be out of place. It is one of the greatest tributes that can be paid to the Truman administration that, over forty years since its conception, the Marshall Plan should still symbolise these noble ideals and become the means for articulating them. In both Eastern Europe and Russia, there were repeated calls for a ‘Marshall Plan’ to assist these countries’ economic reconstruction and, implicitly, their political transformation. These appeals all fell on deaf ears and, to date, there has been no concerted transfer of official resources on a scale to match that of the Marshall Plan. This did not mean that there have been no official resource transfers. The main official resource has been the World Bank and the International Monetary Fund, whose assistance, however, was offered under strict, and often unacceptable conditions.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>link-f51b715b9e7bdd233e</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The Mesmerising Message: The Diffusion of Populism in Public Debates in Western European Media</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/1467-9248.12074</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, decades, western, countries; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Electorally, Western European populist political parties have been rather successful in the last two decades. But how pervasive is their actual populist message? Although some scholars have looked at the diffusion of this message, they have only focused on the arena of party politics. Research on how widespread populism is beyond the party political sphere is still in its infancy. This study looks at populism in public debates in the media. Based on a content analysis of opinion articles in newspapers in five Western European countries, I demonstrate that these debates have become more populist over the years, and that the degree of populism is strongly related to the success of populist parties. This indicates that populism is more widespread than previously assumed. I also show that letters are more populist than other opinion articles and that debates in tabloid media are not more populist than debates in elite media.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>link-7a088f7344133b41dd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Trends in Death Attributed to Heart Failure Over the Past Two Decades in Europe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurjhf/hfr182</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, decades, countries; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>AIMS: Little is known regarding temporal trends in mortality attributed to heart failure (HF) from a population perspective. The aim of this study was to assess the mortality related to HF as an underlying cause during the last 20 years in seven European countries. METHODS AND RESULTS: The number of deaths with HF as the underlying cause was collected in seven European states: Germany, Greece, England and Wales, Spain, France, Finland, and Sweden from 1987 to 2008. Disease coding for HF was based on the International Classification of Diseases (ICD 9th and 10th versions). We computed age-standardized death rates (SDRs) per 100 000 inhabitants. Mean age at death from HF was also calculated for the same period. In the seven studied countries, the HF SDR decreased continuously from 54.2 (1987) to 32.6 (2008). Despite differences in the early 1990s, SDRs related to HF seemed to converge, in these seven European countries, to ∼30 deaths per 100 000 population in the near future, for both men and women. During the study period, the mean age at death increased from 80.0 to 82.7 years. Half of the deaths from HF occurred in hospital, without change over time. CONCLUSION: There has been a 40% reduction of the SDR due to HF in seven European countries during two decades and a concomitant increase in the mean age at death from HF. We hypothesize that these results may be related to a better management of chronic and acute HF patients over the past 20 years.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>over next few Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>link-79fdcbc30a0e716074</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>claim-3d30340f6e823d1c</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Over the next few decades, many Western European countries will undergo a large demographic transformation introduced by the retirement of the “baby boomers” and the possibility of striking increases in longevity.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fortifying Citizenship: Policy Strategies for Civic Integration in Western Europe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/s0043887112000184</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: over, many, western, introduced; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Why have European states introduced mandatory integration requirements for citizenship and permanent residence? There are many studies comparing integration policy and examining the significance of what has been interpreted as a convergent and restrictive “civic turn,” a “retreat from multiculturalism,” and an “inevitable lightening of citizenship.” None of these studies, however, has puzzled over the empirical diversity of integration policy design or presented systematic, comparative explanations for policy variation. This article is the first to develop an argument for what, in fact, amounts to a wealth of variation in civic integration policy (including scope, sequencing, and difficulty). Using a historical institutionalist approach, the author argues that states use mandatory integration to address different membership problems, which are shaped by both existing citizenship policy (whether it is inclusive or exclusive) and political pressure to change it (in other words, the politics of citizenship). She illustrates this argument by focusing on three case studies, applying the argument to a case of unchallenged restrictive retrenchment and continuity (Denmark), to a case of negotiated and thus moderated restriction (Germany), and to a case that recently exhibited both liberal continuity (the United Kingdom, 2001–6) and failed attempts at new restriction (the United Kingdom, 2006–10). These cases show that although states may converge around similar mandatory integration instruments, they may apply them for distinctly different reasons. As a result, new requirements augment rather than alter the major contours of national citizenship policy and the membership association it maintains.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>over next many western Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>link-d232ef69ae660fe8a3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>The BPM Goal Hexagon: an update to the Devil’s Quadrangle</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11301-026-00586-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: current, bpm, suggest; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Abstract Business process management has traditionally focused on time, cost, quality, and flexibility as goal dimensions, known as the Devil’s Quadrangle. In light of novel emerging factors such as employee values, environmental, social, and governance requirements, as well as conscious business models, this paper investigates whether the traditional four goal dimensions of the Devil’s Quadrangle remain suitable today. Based on an extensive analysis of recent business process redesign projects published in case studies, we offer a timely assessment of the adequacy of the Devil’s Quadrangle in current times and suggest extensions to the concept, incorporating insights from a secondary study on robotic process automation. More specifically, we extend the Devil’s Quadrangle to the BPM Goal Hexagon by retaining time, quality, and flexibility, but refocusing cost to a more balanced economics dimension and adding a people dimension as well as an environment dimension. The BPM Goal Hexagon offers scholars and practitioners a timely tool to revisit the real-world relevance and sufficiency of their business process management project goals, methods, and tools.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>link-e243d8a782fc5d47b8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Benefits and Challenges in BPM Adoption in Organizations: An Analysis of Industry Professionals’ Perceptions</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5753/sbsi.2026.248288</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, conducted, information, systems; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Research Context: Business Process Management (BPM) is as a key strategic approach to enhance organizational efficiency and align operations with digital transformation. In the face of constant technological evolution and market demands, organizations are challenged to integrate BPM within increasingly dynamic environments, where people, processes, and technologies must operate in synergy. Scientific and/or Practical Problem: It is crucial to understand how BPM is currently perceived, implemented, and evaluated in organizations, considering both the consolidated theoretical foundations of recent decades and the new practices that are emerging in organizational contexts. Proposed Solution and/or Analysis: This study investigates the critical success factors, main challenges, and perceived benefits of BPM adoption, based on the perspectives of professionals from both public and private organizations. The focus is on the organizational domain and the interplay between people, processes, and technologies. Related IS Theory: The research is grounded in the Socio-technical Systems Theory, which views organizations as interdependent systems composed of social and technical subsystems. This theory supports the analysis of how BPM effectiveness depends on the balanced integration of human, technological, and organizational elements. Research Method: A survey was conducted with 62 professionals using a structured questionnaire based on existing literature and adapted from a previous study to capture updated perceptions about BPM practices. Summary of Results: Findings show that while BPM is recognized for its strategic value (especially in improving communication, standardization, and organizational alignment)it still faces obstacles such as low maturity, cultural resistance, and lack of performance indicators. Leadership support, team training, and cross-level engagement are highlighted as key enablers of BPM success. Contributions and Impact to IS area: This study contributes to Information Systems research by emphasizing BPM as a socio-technical approach and offering theoretical and practical insights into its implementation in organizational settings undergoing digital transformation.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>link-33b9aa79d298dd2091</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Farmers’ and stakeholders’ views on the adoption of agroecological practices. Results from participatory workshops in European countries</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.12688/openreseurope.20536.1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: article, conducted, countries, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Agroecological practices are prerequisites for many agri-environmental schemes in Europe and are increasingly being integrated into the EU's Common Agricultural Policy. Against the backdrop of recent protests by farmers in many European countries, with various grievances based on perceived tightening of environmental regulations and economic pressures, these protests raise questions about how farmer perceptions might hinder the adoption of agroecological practices. A series of workshops with farmers, farm advisors, and other supply chain stakeholders were organized between 2022 and 2023 in different European countries to facilitate knowledge sharing and to learn farmers' and stakeholders' views. Exercises were conducted during the workshops to explore the extent to which farmers were adopting practices that directly or indirectly promote biodiversity. The third and final phase aimed to better understand the motivations, needs, and potential trade-offs associated with implementing different agroecological practices, as well as their combination to promote functional biodiversity. The active participation of stakeholders was beneficial for collectively reflecting on relevant agroecological transition pathways, particularly farmers rational for implementation of agroecological practices for more sustainable agriculture in Europe. The results highlighted that participants had relatively good knowledge of agroecological practices and an inherent understanding of their benefits. Future new practices considered by the participants were mainly intercropping, the use of organic mulches, and direct seeding. Currently used practices, most often combined with others, include diversified crop rotations, biocontrol, and cover crops. The two main combinations were 'diversified crop rotation - cover crops', and 'biopesticide-biological control'. The main reasons for implementing different practices were that these practices are easy to implement and inexpensive, have a proven track record of success, or were subsidized. The main existing and potential future barriers to the implementation of agroecological practices were identified as lack of knowledge, appropriate financing, market opportunities, and lack of information. To overcome these obstacles, the strategies discussed in this article can facilitate or expand the implementation of agroecological practices. This work may thus be of interest to decision-makers in determining how to consider the views of farmers and technical advisors in developing policies.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>link-7f1720cecac7823d42</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Adapting BPM lifecycle to increased sustainability of processes: An approach for including sustainability in the BPM Lifecycle</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7112653822</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, information, systems; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Dissertation presented as the partial requirement for obtaining a Master's degree in Information Management, specialization in Information Systems Management</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>link-c6276d8849ea71a471</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Consensus report of the second European Consensus Workshop on Education in Periodontology</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/jcpe.13983</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, meeting, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BACKGROUND: The second European Consensus Workshop on Education in Periodontology was commissioned, as a result of the changes in the discipline and the advances in educational methods/technology, to update the 2009 Consensus report of the first European Federation of Periodontology (EFP) Workshop on the same topic that was jointly authored by the Association for Dental Education in Europe. AIM: To identify and propose changes necessary in periodontal education at three levels, namely undergraduate, specialist and continuing professional development (CPD), with respect to learning outcomes, competencies and methods of learning/training and evaluation. METHODS: Four working groups (WGs) considered education in periodontology at the undergraduate, specialist and CPD levels, and education methods. Four commissioned position papers, one per WG, summarized the relevant information. Workshop participants gathered at an in-person consensus meeting to discuss the individual reviews, and this consensus report summarizes the conclusions. RESULTS: The learning outcomes for undergraduate and specialist education in periodontology have been updated, and a proposal for learning outcomes for CPD programmes was made. Learning/teaching/training and evaluation methods were proposed for each level of education, which included face-to-face, virtual and blended learning methods. CONCLUSION: Developments in oral/dental medicine and in contemporary educational technologies have been translated into updated learning outcomes and learning/teaching/ training/evaluation methods relevant to education in periodontology.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>link-29e18c0bcefc15a634</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.M. Workshop: Community Health Practice and Research in Europe: Up front and centre!</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurpub/ckad160.674</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, researchers, countries, systems; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Abstract Community Health (CH) is one of the most undervalued and poorly funded domains of action of health systems. Although evidence is strong on its contribution to population health, well-being and equity, national and regional health systems, and to some extent public health institutions, tend to pay little attention to its contribution. Community health encompasses the application of health promotion principles and strategies at the local level to improve equity and resilience of a community. It does so through three fundamental means: cross-sectoral collaborations, community involvement/engagement, and community health workers (CHW). It engages and works with communities in a culturally appropriate manner in order to implement effective strategies. In community health, capacity building is essential. The aim of this workshop is three-fold: 1) to generate a discussion among participants on the state of practice and research, 2) to reflect on strategies to strengthen and improve community health in Europe and, 3) to enhance the visibility of this domain within the ranks of the European Public Health Association (EUPHA). The workshop will provide a space for reflections and discussions. Each of our speakers, who are researchers from 5 different countries (Belgium, Czech Republic, Germany, Spain, and UK), will have 5 minutes to provide some elements of answers to the two following questions: • What is the state of community health practice and research in your country? • What difference does it make for health systems to implement community health strategies? Eric Breton (France) will briefly introduce the workshop providing a conceptual framework for community health and an overview of the different perspectives that drive practices and policies. Manfred Cassens (Germany) and Caroline Masquillier (Belgium) will discuss how the COVID-19 pandemic has enhanced the shortfalls of health systems and lead their countries to experiment community health strategies. Camila Picchio (Spain) will demonstrate how CHWs are essential in reaching out marginalised communities as will Ekaterina Volevach (Czech Republic) drawing lessons from a programme targeting the Roma population. Both will highlight the difficulties health systems face in answering the need of vulnerable population. Catherine Jenkins (United Kingdom), will describe a city-region intervention for galvanising community-level innovation to reduce gambling-related harms. Luis Saboga-Nunes, President of the EUPHA Health Promotion Section and Goof Buijs, Manager of the UNESCO Chair Global Health &amp; Education will conclude the session. We trust that this very interactive workshop will help attendees of the EUPHA conference in Dublin working in community health to find each other and facilitate the development of partnerships. Key messages • Community Health strategies are essential in improving populations’ health and well-being. Yet, this contribution is hardly reflected in national health policies and in the resources invested locally. • The COVID-19 pandemic cast a harsh light on the limits of health systems under-investing in community engagement, community health workers and in the mobilisation of local stakeholders.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>link-2da5bbbe7fbd9068d1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Application of the BPM-Kraljic Model to Improve Supply Management in an Agroindustrial MSE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.46254/na07.20220457</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: article, bpm, information; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Studies present insufficient information on working models within the purchasing area using the BPM tool for agroindustrial companies, especially in Latin America, which aim to improve performance and optimize the processes of an organization.For this reason, the need for this research arises.This scientific article presents a model to improve supply management.The BPM methodology was proposed to standardize internal processes and the Kraljic matrix, a tool used in purchasing management to classify materials and optimize purchase planning.The level of compliance within the purchasing area did not satisfy the established policies, reaching only 55.96% and generating a gap in the savings goal of approximately S/.500,000.This causes an imbalance at the administrative and operational level due to a lack of general standardization of the processes.This triggered problems at the macro level, such as lack of communication between areas, inefficient operations, and economic losses.The proposal that was carried out covers different areas, such as a harmonization within the administrative processes to reduce time variability and logistics focused on the efficient management of purchases and classification of materials.It was possible to prove the hypothesis; it is feasible to reach 85% of the target scope by restructuring the areas and generating strategies.The simulation could prove the optimization of resources by up to 60% and reduce processing times.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>link-0d8cc5d19e14c8ad7f</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Blockchain and Business Process Management (BPM) Synergy: A Comparative Analysis of Modeling Approaches</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/info15010009</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, part, investigating; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Blockchain technology has become a powerful disruptive force that upends established ideas in several industries. A fascinating point of convergence is that of blockchain technology and Business Process Management (BPM), where the distributed and immutable characteristics of blockchain promise to completely transform the modeling, implementation, and oversight of business processes. This symbiosis offers a singular chance to develop corporate processes that are more efficient, safe, and transparent. Nevertheless, to guarantee that blockchain-specific components are accurately represented in these processes, modeling techniques need to be critically examined as part of integrating blockchain into BPM. This literature review examines blockchain-BPM integration using different modeling methodologies. Though well-established, traditional BPM approaches may need help with blockchain-specific aspects. Blockchain-oriented modeling includes smart contracts and decentralized consensus. Hybrid models with blockchain and traditional elements are popular. Adaptability, model clarity, and blockchain integration are evaluated in the analysis. This literature review aims to improve corporate processes’ efficiency, security, and transparency by investigating how to model the integration of blockchain and BPM better.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>link-ca86411b2b715f8774</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tackling the translational challenges of multi-omics research in the realm of European personalised medicine: A workshop report</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3389/fmolb.2022.974799</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: article, reflects, workshop; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Personalised medicine (PM) presents a great opportunity to improve the future of individualised healthcare. Recent advances in -omics technologies have led to unprecedented efforts characterising the biology and molecular mechanisms that underlie the development and progression of a wide array of complex human diseases, supporting further development of PM. This article reflects the outcome of the 2021 EATRIS-Plus Multi-omics Stakeholder Group workshop organised to 1) outline a global overview of common promises and challenges that key European stakeholders are facing in the field of multi-omics research, 2) assess the potential of new technologies, such as artificial intelligence (AI), and 3) establish an initial dialogue between key initiatives in this space. Our focus is on the alignment of agendas of European initiatives in multi-omics research and the centrality of patients in designing solutions that have the potential to advance PM in long-term healthcare strategies.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>link-ab88c294ddb9a6e23f</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>The influence of BPM-supportive culture and individual process orientation on process conformance</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1108/bpmj-08-2020-0363</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, conducted, contribute; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Purpose Organizations rely on their business processes to achieve their business objectives and ensure compliance with relevant laws and regulations. Hence, conformance to process specifications is essential to remain compliant. Various factors influence an organization’s ability to operate in conformance to its process specifications. This study investigates the influence of business process management (BPM)-supportive culture and individual process orientation on process conformance. Design/methodology/approach A construct was created for perceived process conformance and two constructs were selected from literature to represent BPM-supportive culture and individual process orientation. A survey was conducted with 178 employees of a global enterprise, hypotheses were formulated, and a statistical model was constructed and validated. Findings Results pinpoint the key role of the BPM-supportive culture in influencing both individual process orientation and conformance. Individual process orientation is also found to have a significant influence on process conformance. The findings provide additional evidence for the significance of human-related aspects of BPM in achieving BPM success. Originality/value The contributions of this paper help better understand how soft factors of BPM contribute to employees’ process conformance drawing on and relating concepts of BPM and organizational routines.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>link-33184cc364a56de78e</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Workshop: Developing interventions to improve migrants’ healthcare access in Europe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurpub/ckz185.089</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, countries, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Abstract The proposed workshop “Developing interventions to improve migrants’ healthcare access in Europe” will present interim results from the cross-disciplinary MyHealth project to discuss them and the early lessons with policymakers, academics, funders and practitioners in the area of migration and health. MyHealth (Models to engage migrants and refugees in their health, through community empowerment and learning alliance) is a three-year project coordinated by Fundació Hospital de la Vall d’Hebrón, Institut de Recerca (VHIR), Barcelona, Spain and implemented by a consortium of eleven partners with the CHAFEA support in the framework of the 3rd EU Health Program. The goal of the MyHealth project is to improve the healthcare access of vulnerable migrants and refugees (VMR) newly arrived to Europe, by developing and implementing models based on the knowhow of a European multidisciplinary network. This project strongly relies on a participatory approach to ensure a beneficiary-centred approach in implementing a number of interconnected objectives. To ensure a meaningful involvement of the community we applied the Metaplan technique to identify health concerns and needs perceived by vulnerable immigrants and also by professionals from diverse backgrounds working with them at the four partnering sites (Barcelona, Berlin, Brno and Athens). The Metaplan© is a qualitative technique that involves first collecting ideas or information on cards, grouping the cards according to shared characteristics, and ultimately, using a voting system to rank individual ideas or groups of ideas. The research team used this methodology to validate the health needs of immigrants identified by the MyHealth needs assessment methodology and prioritize them, and to generate, categorize and prioritize suggested solutions. These results will be analysed to identify community health strategies and to implement pilot interventions most relevant for the cultural and social reality at each of the sites. Further, the effectiveness of these interventions as a dissemination model will be evaluated. As an innovative approach, the project uses a Learning Alliance methodology to engage multiple stakeholders in the research process through a series of interconnected networks. Each of the he partners aim to document and reflect on best practices for the improvement of the migrants’ access to healthcare and thus provides an opportunity for mutual learning for the consortium members and their respective networks. The workshop will feature presentations by MyHealth partners that will be followed by the moderated Q&amp;A session with the panel of presenters. The workshop participants feedback will be additionally sought through a self-administered workshop evaluation questionnaire. The workshop will facilitate the information exchange and discussion between the MyHealth consortium partners and other ongoing initiatives to improve migrants’ healthcare in European countries. Key messages The community engagement in the development of interventions to facilitate the access to health services while ensuring quality care to migrants community is pivotal in health promotion initiatives. In spite of the notable variability across the sites, the ubiquitous barriers were associated with both host and migrant communities, for which the future interventions would need to account.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>link-36833fe4d21dee4221</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Green BPM as a Business-Oriented Discipline: A Systematic Mapping Study and Research Agenda</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su11154200</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: article, bpm, researchers; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Green Business Process Management (BPM) focuses on the ecological impact of business processes. This article provides a systematic mapping study of Green BPM literature to evaluate five attributes of the Green BPM research area: (1) scope, (2) disciplines, (3) accountability, (4) researchers and (5) quality control. The results allow developing a research agenda to enhance Green BPM as an approach for environmentally sustainable organizations. We rely on a dichotomy of knowledge production to present research directives relevant for both academics and practitioners in order to help close a rigor-relevance gap. The involvement of both communities is crucial for Green BPM to advance as an applied, business-oriented discipline.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>link-550bec7e0e1561e9f4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fourth European stroke science workshop</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/2396987318774443</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, current, researchers, countries, meeting; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Lake Eibsee, Garmisch-Partenkirchen, 16 to 18 November, 2017: The European Stroke Organisation convened &gt;120 stroke experts from 21 countries to discuss latest results and hot topics in clinical, translational and basic stroke research. Since its inception in 2011, the European Stroke Science Workshop has become a cornerstone of European Stroke Organisation's academic activities and a major highlight for researchers in the field. Participants include stroke researchers at all career stages and with different backgrounds, who convene for plenary lectures and discussions. The workshop was organised in seven scientific sessions focusing on the following topics: (1) acute stroke treatment and endovascular therapy; (2) small vessel disease; (3) opportunities for stroke research in the omics era; (4) vascular cognitive impairment; (5) intracerebral and subarachnoid haemorrhage; (6) alternative treatment concepts and (7) neural circuits, recovery and rehabilitation. All sessions started with a keynote lecture providing an overview on current developments, followed by focused talks on a timely topic with the most recent findings, including unpublished data. In the following, we summarise the key contents of the meeting. The program is provided in the online only Data Supplement. The workshop started with a key note lecture on how to improve the efficiency of clinical trial endpoints in stroke, which was delivered by Craig Anderson (Sydney, Australia) and set the scene for the following discussions.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>link-621bb4fd94fffb0251</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Getting it right! Critical Success Factors of BPM in the Public Sector: A Systematic Literature Review</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3127/ajis.v22i0.1265</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, countries, meeting; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>The continuously evolving and dynamic social, economic, political environments and public pressures demand governments to deliver effective and efficient public services. In the quest for meeting these demands, governments respond by designing extensive reforms and performance objectives to improve the efficiency and responsiveness of their agencies. Many governments have adopted Business Process Management (BPM) as a strategy to achieve these reforms. However, the successful implementation of BPM initiatives has been a challenging task for agencies responsible for these initiatives, with many projects not reaching completion or not achieving the intended outcomes. This paper reports the results of a systematic literature review on critical success factors (CSFs) related to BPM projects in the public sector. We analysed 31 papers in this review covering both the developed and developing country contexts, sourced from refereed and peer reviewed journals. A quasi-deductive approach was applied for the qualitative data analysis using NVivo 10 software. This resulted in the synthesis and identification of 14 critical success factors of BPM in the public sector, each defined and described in detail with specific attention to the sub-factors mentioned within the literature. Any differences between developed and developing country contexts were sought for, and the observations critically analysed. We propose a series of research questions, designed to support the progression of BPM in the public sector of developed as well as developing countries.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>link-b4e11c84f715505914</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.I. Workshop: Vaccinating Europe: challenges old and new</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurpub/ckx187.031</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, countries, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Chairs: Michael Edelstein, UK, Maria Ganczak, Poland Contact: michael.edelstein@doctors.org.uk Vaccines are among the most successful and effective public health interventions, saving two to three million lives each year globally. In 2017, 86% of children across the world have received their primary immunisations, the highest proportion ever achieved. Although vaccine coverage in the European region is generally high compared with other parts of the world, some new challenges have emerged. Highly mobile populations, difficulties in achieving or maintaining high vaccine coverage in routine vaccination programme, under immunised ethnic, religious or cultural minority groups, healthcare reorganisations, lack of funding and an increasingly visible and vocal anti-vaccination movement are all challenges to achieving herd immunity for vaccine-preventable diseases across Europe, resulting in outbreaks, disease and even death. This 90 minutes workshop, organised around 5 talks presenting perspectives from different parts of Europe followed by discussion, will explore some of these global, regional and local challenges, providing some insight into how they can be overcome in order to protect populations in Europe. The objectives of the workshop are to raise awareness of these emerging challenges across Europe and to provide suggestions about how to address them. The first presentation from the Vaccine confidence project (London School of Hygiene and Tropical Medicine) will set the global vaccine hesitancy landscape as the phenomenon is not limited to Europe. This will be followed by a presentation by the European Centre for Disease Prevention and Control about its role in addressing vaccine hesitancy in Europe. Then, Public Health England will present results of a longitudinal “attitudes to vaccine” survey they have been conducting for several decades, providing some very useful insights into factors associated with positive attitudes towards vaccination. The last two presentations will describe some of the consequences of the challenges described above: first in Romania where a large measles outbreak has affected thousands and killed young, previously health individuals; and second, in Denmark where a powerful anti-vaccination movement has brought the HPV vaccine programme to a virtual halt. Speakers from these respective countries will reflect on these experiences and share their approach to addressing the situation. Key messages: Achieving and maintaining high vaccine coverage in Europe is a challenge with complex, inter-related causes. Attitudes towards vaccines is a major factor. Providing tailored information to patients using the right channels and training healthcare professionals to address questions about vaccines are crucial in addressing this challenge.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>link-d8e5ca216ff2952eff</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Using a Work System Perspective to Expand BPM Research Use Cases</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2772668607</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, information, systems; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Business process management (BPM) has developed as a research field primarily situated in the computer and information systems sciences. Recently, van der Aalst (2013) analyzed the results of these research efforts and identified a set of research topics in the form of a series of BPM research use cases. Those BPM research use cases emphasize technological and computational challenges and solutions. Ideally, however, BPM research should also address managerial and organizational challenges that the existing technically oriented research use cases do not fully reflect. We propose expanding the scope and impact of BPM research by drawing on work system theory (WST) to identify new BPM research use cases and directions. After comparing a WST perspective on basic BPM topics with the technically oriented BPM perspective expressed in van der Aalst (2013), we present new research topics that extend the technically oriented BPM research use cases in van der Aalst (2013). We also present new research directions that go beyond those use cases. Taken together, the extensions of the existing research use cases and the new use cases lead to a more balanced BPM research agenda that more fully blends technical and managerial challenges.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>link-b76fb73cb5b94629f0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Using a Work System Perspective to Expand BPM Use Cases for Research</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2795946915</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, information, systems; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Business Process Management (BPM) has developed as a research field centered within the computer and information systems sciences – but also touching other fields as well. Recently, van der Aalst (2013) analyzed the results of some of these research efforts and identified a set of research topics in the form of a series of BPM use cases that primarily emphasize technological and computational challenges and solutions in BPM academia. Ideally, however, BPM should also address managerial and organizational challenges that are not fully reflected in the existing use cases identified by van der Aalst (2013). We propose drawing on work system theory (WST) to expand van der Aalst’s use cases and to identify additional BPM use cases and new research directions. After comparing a WST perspective on basic BPM topics with the BPM perspective expressed in van der Aalst (2013), we present new research topics that extend existing BPM use cases. We also present new research directions that go beyond those use cases. Taken together, the extensions of the existing use cases and the new use cases lead to a more balanced BPM research agenda that blends technical and managerial challenges more fully.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>link-e88d2967bba8303822</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>The European Network of Clinical Legal Education: The Spring Workshop 2015</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.19164/ijcle.v22i3.473</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: article, workshop, issues; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>As the clinical movement gains momentum across Europe, this article explores the issues experienced by clinicians which both promote and hinder the development of clinical programmes. The article discusses the issues raised by clinicians during the course of the Workshop, in particular, addressing the resistance clinical programmes can face from the legal profession and the academy.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>link-6afee29d46a4d279d7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>How Do We Progress? An Exploration of Alternate Explanations for BPM Capability Development</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17705/1cais.03601</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, information, systems; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Business process management (BPM) is a topic that has received immense attention in information systems research and practice. While the existing literature comprehensively covers BPM methods, techniques, and tools, the development of BPM capability in organizations remains under-researched. Existing studies mainly present maturity models with generic sequences of distinct stages that provide a rather simplistic perspective on BPM capability progress. Taking a process theory view and drawing from organizational change literature, we elaborate on alternate templates for explaining BPM capability development. By revisiting two case studies on BPM capability development, we analyze the explanatory power of four basic theories of capability development and thus advance existing approaches to explain BPM capability progress. Our analysis shows the general applicability of these theories and points to particular advantages, disadvantages, and application conditions. Using the four basic theories as alternate templates, we also offer a much more-detailed explanation of the mechanisms behind the episodes of BPM capability progress that we observed in the two case studies. In particular, the different theoretical templates allow one to better understand the influence of internal and external contexts on BPM capability progress.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>link-181b3ca5edd6a34ff5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fostering e-participation sustainability through a BPM-driven semantic model</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2253428555</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: bpm, researchers, information; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>According to a recent Eurobarometer survey (2014), 68% of Europeans tend not to trust national governments. As the increasing alienation of citizens from politics endangers democracy and welfare, governments, practitioners and researchers look for innovative means to engage citizens in policy matters. One of the measures intended to overcome the so-called democratic deficit is the promotion of civic participation. Digital media proliferation offers a set of novel characteristics related to interactivity, ubiquitous connectivity, social networking and inclusiveness that enable new forms of societal-wide collaboration with a potential impact on leveraging participative democracy. Following this trend, e-Participation is an emerging research area that consists in the use of Information and Communication Technologies to mediate and transform the relations among citizens and governments towards increasing citizens’ participation in public decision-making. However, despite the widespread efforts to implement e-Participation through research programs, new technologies and projects, exhaustive studies on the achieved outcomes reveal that it has not yet been successfully incorporated in institutional politics. Given the problems underlying e-Participation implementation, the present research suggested that, rather than project-oriented efforts, the cornerstone for successfully implementing e-Participation in public institutions as a sustainable added-value activity is a systematic organisational planning, embodying the principles of open-governance and open-engagement. It further suggested that BPM, as a management discipline, can act as a catalyst to enable the desired transformations towards value creation throughout the policy-making cycle, including political, organisational and, ultimately, citizen value. Following these findings, the primary objective of this research was to provide an instrumental model to foster e-Participation sustainability across Government and Public Administration towards a participatory, inclusive, collaborative and deliberative democracy. The developed artefact, consisting in an e-Participation Organisational Semantic Model (ePOSM) underpinned by a BPM-steered approach, introduces this vision. This approach to e-Participation was modelled through a semi-formal lightweight ontology stack structured in four sub-ontologies, namely e-Participation Strategy, Organisational Units, Functions and Roles. The ePOSM facilitates e-Participation sustainability by: (1) Promoting a common and cross-functional understanding of the concepts underlying e-Participation implementation and of their articulation that bridges the gap between technical and non-technical users; (2) Providing an organisational model which allows a centralised and consistent roll-out of strategy-driven e-Participation initiatives, supported by operational units dedicated to the execution of transformation projects and participatory processes; (3) Providing a standardised organisational structure, goals, functions and roles related to e-Participation processes that enhances process-level interoperability among government agencies; (4) Providing a representation usable in software development for business processes’ automation, which allows advanced querying using a reasoner or inference engine to retrieve concrete and specific information about the e-Participation processes in place. An evaluation of the achieved outcomes, as well a comparative analysis with existent models, suggested that this innovative approach tackling the organisational planning dimension can constitute a stepping stone to harness e-Participation value.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>article reflects issues bpm Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>link-d72b990eabb0685279</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A.5. Workshop: Facets of public health in Europe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurpub/cku164.001</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, current, researchers, countries, systems, broad; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Public health in Europe has achieved major progress in the last two centuries when it comes to reducing infectious disease. However, much remains to be done to reduce non-communicable diseases, which make up the major disease burden of the World Health Organization (WHO) European Region. In addition, the current economic crisis has undermined funding and capacities for public health in many European countries. This workshop presents findings of an ambitious new study, “Facets of public health in Europe”, undertaken by the European Observatory on Health Systems and Policies in 2009-2013 and to be published in time for the European Public Health (EPH) conference in 2014. This important new book fills a major gap in the literature. Despite the resources that are devoted to public health, there is a striking lack of knowledge on current public health practice in Europe, ultimately undermining national and European efforts to strengthen the public health function. This book takes a broad yet detailed approach to public health in Europe and offers the most comprehensive analysis of this region currently available. It considers a wide range of key topics in public health, including screening, health promotion, occupational health, environmental health, nutrition, healthcare public health, tackling the social determinants of health, intersectoral working, public health research, and knowledge brokering in public health. The book is designed to be an essential tool for anyone studying or working in the field of public health in Europe. Drawing on a series of comprehensive reviews, several ongoing or recent European research projects, and a network of leading experts from across Europe, the study explored the greatly varying structures, capacities and practices of delivering public health functions across Europe and outlines the areas in greatest need of improvement. The geographical scope of the study was, where relevant and possible, the entire WHO European Region, aiming to reflect the very different situations in different parts of the region. Furthermore, the contributions strived to achieve an appropriate balance when discussing the work of various international organizations (the European Union, WHO and others), national governments, and sub- national and civil society actors. The workshop will be of major interest to public health researchers, practitioners and policy-makers from across Europe. It aims to support WHO’s European Action Plan for Strengthening Public Health Capacities and Services and to inform current reform efforts underway in a number of European countries. The workshop will explore four key areas of public health practice in Europe: monitoring population health, strengthening public health leadership, developing the public health workforce, and conducting health impact assessments. The presentations will be informative yet sufficiently short for each to be followed by plenty of plenary participation and debate. Key messages The workshop will ask whether Europe’s public health systems are fit for purpose in the 21st century. It will challenge participants, as members of Europe’s public health community, to propose a roadmap to strengthen these.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>link-b45d269b7bc7cf9d45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>A.5. Workshop: Facets of public health in Europe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/eurpub/cku164.125</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, current, researchers, countries, systems, broad; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Public health in Europe has achieved major progress in the last two centuries when it comes to reducing infectious disease.However, much remains to be done to reduce non-communicable diseases, which make up the major disease burden of the World Health Organization (WHO) European Region.In addition, the current economic crisis has undermined funding and capacities for public health in many European countries.This workshop presents findings of an ambitious new study, ''Facets of public health in Europe'', undertaken by the European Observatory on Health Systems and Policies in 2009-2013 and to be published in time for the European Public Health (EPH) conference in 2014.This important new book fills a major gap in the literature.Despite the resources that are devoted to public health, there is a striking lack of knowledge on current public health practice in Europe, ultimately undermining national and European efforts to strengthen the public health function.This book takes a broad yet detailed approach to public health in Europe and offers the most comprehensive analysis of this region currently available.It considers a wide range of key topics in public health, including screening, health promotion, occupational health, environmental health, nutrition, healthcare public health, tackling the social determinants of health, intersectoral working, public health research, and knowledge brokering in public health.The book is designed to be an essential tool for anyone studying or working in the field of public health in Europe.Drawing on a series of comprehensive reviews, several ongoing or recent European research projects, and a network of leading experts from across Europe, the study explored the greatly varying structures, capacities and practices of delivering public health functions across Europe and outlines the areas in greatest need of improvement.The geographical scope of the study was, where relevant and possible, the entire WHO European Region, aiming to reflect the very different situations in different parts of the region.Furthermore, the contributions strived to achieve an appropriate balance when discussing the work of various international organizations (the European Union, WHO and others), national governments, and subnational and civil society actors.The workshop will be of major interest to public health researchers, practitioners and policy-makers from across Europe.It aims to support WHO's European Action Plan for Strengthening Public Health Capacities and Services and to inform current reform efforts underway in a number of European countries.The workshop will explore four key areas of public health practice in Europe: monitoring population health, strengthening public health leadership, developing the public health workforce, and conducting health impact assessments.The presentations will be informative yet sufficiently short for each to be followed by plenty of plenary participation and debate.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>link-6b098960e126f38d12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>The Workshop on Animal Botulism in Europe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1089/bsp.2012.0076</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: workshop, current, conducted, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>A workshop on animal botulism was held in Uppsala, Sweden, in June 2012. Its purpose was to explore the current status of the disease in Europe by gathering the European experts in animal botulism and to raise awareness of the disease among veterinarians and others involved in biopreparedness. Animal botulism is underreported and underdiagnosed, but an increasing number of reports, as well as the information gathered from this workshop, show that it is an emerging problem in Europe. The workshop was divided into 4 sessions: animal botulism in Europe, the bacteria behind the disease, detection and diagnostics, and European collaboration and surveillance. An electronic survey was conducted before the workshop to identify the 3 most needed discussion points, which were: prevention, preparedness and outbreak response; detection and diagnostics; and European collaboration and surveillance. The main conclusions drawn from these discussions were that there is an urgent need to replace the mouse bioassay for botulinum toxin detection with an in vitro test and that there is a need for a European network to function as a reference laboratory, which could also organize a European supply of botulinum antitoxin and vaccines. The foundation of such a network was discussed, and the proposals are presented here along with the outcome of discussions and a summary of the workshop itself.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>link-2c2894c6fa71eb39ff</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Prediction of Soil Organic Carbon at the European Scale by Visible and Near InfraRed Reflectance Spectroscopy</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0066409</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: countries, meeting, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Soil organic carbon is a key soil property related to soil fertility, aggregate stability and the exchange of CO2 with the atmosphere. Existing soil maps and inventories can rarely be used to monitor the state and evolution in soil organic carbon content due to their poor spatial resolution, lack of consistency and high updating costs. Visible and Near Infrared diffuse reflectance spectroscopy is an alternative method to provide cheap and high-density soil data. However, there are still some uncertainties on its capacity to produce reliable predictions for areas characterized by large soil diversity. Using a large-scale EU soil survey of about 20,000 samples and covering 23 countries, we assessed the performance of reflectance spectroscopy for the prediction of soil organic carbon content. The best calibrations achieved a root mean square error ranging from 4 to 15 g C kg(-1) for mineral soils and a root mean square error of 50 g C kg(-1) for organic soil materials. Model errors are shown to be related to the levels of soil organic carbon and variations in other soil properties such as sand and clay content. Although errors are ∼5 times larger than the reproducibility error of the laboratory method, reflectance spectroscopy provides unbiased predictions of the soil organic carbon content. Such estimates could be used for assessing the mean soil organic carbon content of large geographical entities or countries. This study is a first step towards providing uniform continental-scale spectroscopic estimations of soil organic carbon, meeting an increasing demand for information on the state of the soil that can be used in biogeochemical models and the monitoring of soil degradation.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>link-2e9e9d8b25e3110146</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>claim-3e149ec6a91c07b5</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>This article reflects on a workshop on current and future issues in BPM research that was conducted by seventeen IS researchers from eight European countries as part of the 2010 annual meeting of the European Research Center for Information Systems (ERCIS). The results of this workshop suggest that BPM research can meaningfully contribute to investigating a broad variety of phenomena that are of interest to IS scholars, ranging from rather technical (e.g., the implementation of software architectures) to managerial (e.g., the impact of organizational culture on process performance).</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Exposure Limits for Nanoparticles: Report of an International Workshop on Nano Reference Values</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/annhyg/mes043</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: article, reflects, workshop, issues, countries, information; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>This article summarizes the outcome of the discussions at the international workshop on nano reference values (NRVs), which was organized by the Dutch trade unions and employers' organizations and hosted by the Social Economic Council in The Hague in September 2011. It reflects the discussions of 80 international participants representing small- and medium-size enterprises (SMEs), large companies, trade unions, governmental authorities, research institutions, and non-governmental organizations (NGOs) from many European countries, USA, India, and Brazil. Issues that were discussed concerned the usefulness and acceptability of precaution-based NRVs as a substitute for health-based occupational exposure limits (OELs) and derived no-effect levels (DNELs) for manufactured nanoparticles (NPs). Topics concerned the metrics for measuring NPs, the combined exposure to manufactured nanomaterials (MNMs) and process-generated NPs, the use of the precautionary principle, the lack of information about the presence of nanomaterials, and the appropriateness of soft regulation for exposure control. The workshop concluded that the NRV, as an 8-h time-weighted average, is a comprehensible and useful instrument for risk management of professional use of MNMs with a dispersible character. The question remains whether NRVs, as advised for risk management by the Dutch employers' organization and trade unions, should be under soft regulation or that a more binding regulation is preferable.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>article reflects workshop Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>link-94e89e72345484a789</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Characteristics of special purpose acquisition companies as a new challenge in European markets</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5937/bizinfo2401089d</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, aim, managers; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Special Purpose Acquisition Company (SPAC) is a special type of public listed company available to investors in financial markets, and was formed with the aim of investing in one or more existing operating companies after raising capital. This paper provides an overview of academic and financial literature on SPACs, describes their characteristics, advantages and risks of using SPAC as a form that does not offer services and does not conduct business operations, but is formed only for the purpose of acquisition of target companies. The paper focuses on the analysis of the impact of these forms of short-term investments on private companies, SPAC managers and investors. The paper further examines whether the impact of SPACs on European financial markets can be expected to grow. Authors’ findings show that, beside limitations for growth of European SPAC number, there is evident interest among European startup companies to go public through SPACs.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>link-78a7db8bc4006dc204</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bronchiectasis in Europe: data on disease characteristics from the European Bronchiectasis registry (EMBARC)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/s2213-2600(23)00093-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: aim, describe, methods, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Bronchiectasis is a heterogeneous, neglected disease with few multicentre studies exploring the causes, severity, microbiology, and treatment of the disease across Europe. This aim of this study was to describe the clinical characteristics of bronchiectasis and compare between different European countries. METHODS: EMBARC is an international clinical research network for bronchiectasis. We report on a multicentre, prospective, observational, non-interventional, cohort study (the EMBARC registry) conducted across 27 European countries and Israel. Comprehensive clinical data were collected from adult patients (aged ≥18 years) at baseline and annual follow-up visits using electronic case report form. Data from individual countries were grouped into four regions (the UK, northern and western Europe, southern Europe, and central and eastern Europe according to modified EU EuroVoc classification). Follow-up data were used to explore differences in exacerbation frequency between regions using a negative binomial regression model. FINDINGS: Between Jan 12, 2015, and April 12, 2022, 16 963 individuals were enrolled. Median age was 67 years (IQR 57-74), 10 335 (60·9%) participants were female and 6628 (39·1%) were male. The most common cause of bronchiectasis in all 16 963 participants was post-infective disease in 3600 (21·2%); 6466 individuals (38·1%) were classified as idiopathic. Individuals with bronchiectasis experienced a median of two exacerbations (IQR 1-4) per year and 4483 (26·4%) patients had a hospitalisation for exacerbation in the previous year. When examining the percentage of all isolated bacteria, marked differences in microbiology were seen between countries, with a higher frequency of Pseudomonas aeruginosa and lower Haemophilus influenzae frequency in southern Europe, compared with higher H influenzae in the UK and northern and western Europe. Compared with other regions, patients in central and eastern Europe had more severe bronchiectasis measured by the Bronchiectasis Severity Index (51·3% vs 35·1% in the overall cohort) and more exacerbations leading to hospitalisations (57·9% vs 26·4% in the overall cohort). Overall, patients in central and eastern Europe had an increased frequency of exacerbations (adjusted rate ratio [RR] 1·12, 95% CI 1·01-1·25) and a higher frequency of exacerbations leading to hospitalisations (adjusted RR 1·71, 1·44-2·02) compared with patients in other regions. Treatment of bronchiectasis was highly heterogeneous between regions. INTERPRETATION: Bronchiectasis shows important geographical variation in causes, microbiology, severity, and outcomes across Europe. FUNDING: European Union-European Federation of Pharmaceutical Industries and Associations Innovative Medicines Initiative. TRANSLATIONS: For the Arabic, French, German, Greek, Hebrew, Irish, Russian and Spanish translations of the abstract see Supplementary Materials section.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>link-6aebd3f2bd92913b8c</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Needs of forensic psychiatric patients with schizophrenia in five European countries</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00127-022-02336-5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, five, methods, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AIMS: The purpose was to compare the frequency of needs of patients with schizophrenia in forensic services across five European countries as assessed by both the patients and their care staff. METHODS: Patients with schizophrenia and a history of significant interpersonal violence were recruited from forensic psychiatric services in Austria, Germany, Italy, Poland and England. Participants' needs were assessed using the Camberwell Assessment of Needs-Forensic Version (CANFOR). Multiple linear regression analyses were used to identify predictors of numbers of needs. RESULTS: In this sample, (n = 221) the most commonly reported need according to patients (71.0%) and staff (82.8%) was the management of psychotic symptoms. A need for information was mentioned by about 45% of staff and patients. Staff members reported a significantly higher number of total needs than patients (mean 6.9 vs. 6.2). In contrast, staff members reported a significantly lower number of unmet needs than patients (mean 2.0 vs. 2.5). Numbers of total needs and met needs differed between countries. Unmet needs as reported by patients showed positive associations with the absence of comorbid personality disorder, with higher positive symptom scores and lifetime suicide or self-harm history. Significant predictors of unmet needs according to staff were absence of comorbid personality disorder and higher positive as well as negative symptom scores according to PANSS. CONCLUSIONS: Staff rated a significantly higher number of total needs than patients, while patients rated more unmet needs. This indicates that patients' self-assessments of needs yield important information for providing sufficient help and support.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>link-6792ccc70ec13c643e</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Differences in hip fracture care in Europe: a systematic review of recent annual reports of hip fracture registries</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00068-021-01797-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, describe, process, methods; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PURPOSE: Hip fractures are of growing interest due to their increasing number, subsequent functional decline and high institutionalization rate of patients, mortality, and costs. Several process measurements are essential for hip fracture care. To compare and improve these, hip fracture registries in Europe became popular. This systematic review aims to describe the differences between hip fracture registries in Europe as well as the differences in hip fracture treatment between countries. METHODS: A systematic search using the keywords "hip fracture" AND "national" AND "database OR audit OR registry OR register" was performed in PubMed, Embase and Cochrane Library according to PRISMA guidelines till 3rd December 2020. Recent annual reports of identified hip fracture registries in Europe were additionally identified in June 2021. Comparisons of most common case-mix, process and outcome measurements were performed. RESULTS: 11 registries in Europe were identified. Differences were observed regarding inclusion criteria of the different registries. Comparison of the different registries was difficult due to differences in the way to report measurements. While mortality rates differed substantially between countries, most of the process measurements met recommendations according to recent guidelines. CONCLUSION: Hip fracture registries were a valid tool to compare hospitals within one country. However, a comparison between registries of different countries should have also been easily possible. For this, the registries need to make their data easily accessible and further unify their way of measuring and reporting.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>link-67223dedb4fa7e56a4</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>General population normative data for the EQ-5D-3L in the five largest European economies</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10198-021-01326-9</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: aim, five, methods, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AIM: The EQ-5D is a generic measure of health that is widely applied for health economic and non-economic purposes. Population norms can be used to facilitate the interpretation of EQ-5D data. The objective of this study was to develop a set of pooled normative EQ-5D-3L values for the five largest European economies (EUR5). METHODS: EQ-5D-3L index values based on the time trade-off (TTO) were available for all EUR5 countries (n = 21,425): France, Germany, Italy, Spain, and the United Kingdom (UK). Country-specific data sets were aggregated and weighted to facilitate the derivation of norms for gender and age groups. Analyses included equal weighting and weighting by population and economy size. Norms were also calculated using the European visual analog scale-based value set (European VAS), the EQ VAS and separately by dimension. RESULTS: Pooled mean (SD) population weighted TTO values for males/females were 0.967 (0.122)/0.959 (0.118) for ages 18-24; 0.965 (0.096)/0.954 (0.117) for ages 25-34; 0.943 (0.165)/0.936 (0.169) for ages 35-44; 0.934 (0.150)/0.921 (0.157) for ages 45-54; 0.896 (0.188)/0.875 (0.197) for ages 55-64; 0.900 (0.158)/0.839 (0.218) for ages 65-74; and 0.830 (0.234)/0.756 (0.291) for ages 75 and older. Mean values decreased and variance increased with age; females had slightly lower mean values than males across all age bands. The unequal weighting approaches produced similar point estimates with smaller variances. Mean values for the European VAS were slightly lower than those for the TTO-based index. DISCUSSION: Normative EQ-5D-3L values can be used to benchmark the outcomes of treated patients against the health of the general population. EUR5 norms may be useful in research applications inferring to Europe or the European Union as a whole, particularly when sample size precludes analysis at the country level.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>link-de2bb99a38114f50f2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>The Humanistic and Economic Burden of Migraine in Europe: A Cross-Sectional Survey in Five Countries</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s40120-020-00196-2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: aim, five, methods; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>INTRODUCTION: Prior studies have estimated the burden of migraine in patients suffering from ≥ 4 monthly headache days (MHDs), but the burden experienced by migraineurs suffering from one to three (1-3) MHDs is unknown. The aim of this study was to examine the incremental burden of migraine in terms of health-related quality of life (HRQoL), impairments to work and daily activities, and healthcare resource utilization (HRU) in five European countries (France, Germany, Italy, Spain, and the UK (EU5]), by comparing migraineurs with ≥ 4 MHDs and migraineurs with 1-3 MHDs. METHODS: The sample for this retrospective cross-sectional study was collected from the 2017 National Health and Wellness Survey (N = 62,000). The Short-Form 12-Item Health Survey Instrument, version-2 physical and mental component summary (PCS and MCS) scores, Short-Form 6-dimensions (SF-6D), EuroQoL 5-dimensions (EQ-5D) and EuroQoL visual analog scale (VAS) scores, impairments to work productivity and daily activities (Work Productivity and Activity Impairment [WPAI] Questionnaire) scores, and HRU were compared between migraineur groups with ≥ 4 MHDs (4-7, intermediate-frequency episodic migraine; 8-14, high-frequency episodic migraine; ≥ 15 chronic migraine) and the migraineur subgroup with 1-3 MHDs (low-frequency episodic migraine) using generalized linear modeling after adjusting for covariates. RESULTS: Data from a total of 62,000 survey respondents were examined, of whom 1323 and 1569 were considered to have 1-3 MHDs and ≥ 4 MHDs (4-7 MHDs [n = 783]; 8-14 MHDs [n = 429]; ≥ 15 MHDs [n = 357]), respectively. The adjusted HRQoL was significantly lower in the 4-7 MHDs (for MCS and SF-6D scores; p &lt; 0.0001) and 8-14 MHDs subgroups (for MCS, SF-6D, EQ-5D, and EuroQoL VAS scores, p &lt; 0.0001; for PCS scores, p = 0.0007) than in the 1-3 MHDs subgroup. Migraineurs with 4-7 and 8-14 MHDs reported higher activity impairment and more frequent visits to healthcare providers (all p &lt; 0.0001) and neurologists (p = 0.0006 and p &lt; 0.0001, respectively) compared to the 1-3 MHDs subgroup. Migraineurs with ≥ 15 MHDs had significantly lower HRQoL and increased WPAI scores and HRU than the 1-3 MHDs subgroup. CONCLUSIONS: This study provides evidence supporting the incremental burden of migraine, characterized by poorer HRQoL and increased WPAI scores and greater HRU, among migraineurs experiencing ≥ 4 MHDs compared with migraineurs experiencing 1-3 MHDs in the EU5.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>link-11f89a661f3a3918b5</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>European In-Situ Snow Measurements: Practices and Purposes</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s18072016</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: describe, methods, range; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>In-situ snow measurements conducted by European institutions for operational, research, and energy business applications were surveyed in the framework of the European Cooperation in Science and Technology (COST) Action ES1404, called "A European network for a harmonised monitoring of snow for the benefit of climate change scenarios, hydrology, and numerical weather prediction". Here we present the results of this survey, which was answered by 125 participants from 99 operational and research institutions, belonging to 38 European countries. The typologies of environments where the snow measurements are performed range from mountain to low elevated plains, including forests, bogs, tundra, urban areas, glaciers, lake ice, and sea ice. Of the respondents, 93% measure snow macrophysical parameters, such as snow presence, snow depth (HS), snow water equivalent (SWE), and snow density. These describe the bulk characteristics of the whole snowpack or of a snow layer, and they are the primary snow properties that are needed for most operational applications (such as hydrological monitoring, avalanche forecast, and weather forecast). In most cases, these measurements are done with manual methods, although for snow presence, HS, and SWE, automatized methods are also applied by some respondents. Parameters characterizing precipitating and suspended snow (such as the height of new snow, precipitation intensity, flux of drifting/blowing snow, and particle size distribution), some of which are crucial for the operational services, are measured by 74% of the respondents. Parameters characterizing the snow microstructural properties (such as the snow grain size and shape, and specific surface area), the snow electromagnetic properties (such as albedo, brightness temperature, and backscatter), and the snow composition (such as impurities and isotopes) are measured by 41%, 26%, and 13% of the respondents, respectively, mostly for research applications. The results of this survey are discussed from the perspective of the need of enhancing the efficiency and coverage of the in-situ observational network applying automatic and cheap measurement methods. Moreover, recommendations for the enhancement and harmonization of the observational network and measurement practices are provided.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>link-297d1b0a74e58b60d8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A longitudinal and comparative analysis of competitive balance in five European football leagues</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1108/tpm-09-2017-0055</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, five, design, methodology, approach; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Purpose This paper aims to provide empirical evidence on competitive balance in the “big five” European football leagues, namely, the English Premier League, French Ligue 1, German Bundesliga, Italian Serie A and Spanish La Liga. Design/methodology/approach This paper uses recognised measures of competitive balance to measure levels of concentration (within-season competitive balance) and dominance (between-season competitive balance) in the selected leagues over 22 seasons between 1995/96 and 2016/17. Findings French Ligue 1 emerged as the most balanced league in terms of both concentration and dominance measures. The analysis also points to a statistically significant decline in competitive balance in all leagues apart from Serie A (Italy). Originality/value The findings of this study are of concern for the league organisers. Competition intensity is a key component of a sport league, and a league that is dominated by one or a select few clubs is less attractive within the marketplace. This paper presents challenges at the league governance level for the five leagues examined.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>link-53d2ed67f9f5956ea9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The search for an appropriate end-of-life formula for the purpose of the European Commission Environmental Footprint initiative</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11367-016-1244-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, aim, methods, approach; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>This paper explains in details the rationale behind the choice of the end-of-life allocation approach in the European Commission Product Environmental Footprint (PEF) and Organisational Environmental Footprint (OEF) methods. The end-of-life allocation formula in the PEF/OEF methods aims at enabling the assessment of all end-of-life scenarios possible, including recycling, reuse, incineration (with heat recovery) and disposal for both open- and closed-loop systems in a consistent and reproducible way. It presents how the formula builds on existing standards and how and why it deviates from them. Various end-of-life allocation approaches and formulas, mainly taken not only from/based on existing environmental impact assessment methods and/or standards but also one original linearly degressive approach, were analysed against a predetermined set of criteria, reflecting the overall aim of the PEF/OEF methods. This set of criteria is physical realism, distribution of burdens and benefits in a product cascade system and applicability. Besides the qualitative analysis, the various formulas were implemented for several products and for different scenarios regarding recycled content and recyclability to check the robustness of the outcomes, exemplary expressed for the Global Warming Potential impact category. As reaching physical realism was impossible at both the product and overall product cascade system level by any of the end-of-life approaches analysed, one of both had to be prioritised. The paper explains in details why a product level approach was preferred in the context of the PEF/OEF methods. In consequence, allocation of the end-of-life processes which are related to more than one product in a product cascade system is needed and should be carefully considered as it has a major influence on the results and decision taking. A formula taking into account the number of recycling cycles of a material was identified as preferred to reach physical realism and to allocate burdens and benefits of repeatedly recycling of a material over the different products in a product cascade system. However, this approach was not selected for the PEF/OEF methods as data on the number of recycling cycles was insufficiently available (for the time being) for all products on the market and hence fails the criterion of “applicability”. This explains why, instead, a formula based on the 50:50 approach—allocating shared end-of-life processes equally between the previous and subsequent product—was selected for the PEF/OEF methods.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>link-d77badaef5a92e12bf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Regional differences in insulin therapy regimens in five European countries</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5414/cp202906</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, use, five, methods, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>AIMS: The purpose of this study was to investigate differences of insulin therapy regimens in five European countries. METHODS: Proportions of basal bolus therapy (intensified insulin therapy (ICT), basal insulin supported oral therapy (BOT), conventional therapy (CT), and short-acting prandial insulin (SIT) among insulin-treated diabetes patients in Germany (n = 64,055), the UK (n = 6,740), and France (n = 4,779) were estimated using representative general medicine practice databases (Disease Analyzer: 2014). Insulin regimens in Hungary (n = 40,769) and Poland (n = 68,136) were analyzed based on nationwide prescription databases (LRx: 2014). RESULTS: ICT was the most frequent insulin regimen (46 - 81%) in all countries except France (BOT &gt; ICT). SIT showed the lowest use, ranging from 2.5% in the UK to 11.2% in Germany. BOT was more frequently used than CT in Germany and Hungary, which was just the opposite in the UK and Poland. The share of insulin analogs among all prescriptions was higher in Germany, the UK, and France (short-acting insulins: 59 - 98%; basal insulins: 70 - 93%) than in Hungary and Poland (short-acting insulins: 41 - 57%; basal insulins: 23 - 46%) (all p &lt; 0.001). CONCLUSIONS: Despite national and international guidelines, insulin regimens differ substantially between European countries. Our results most likely reflect differences in regulations and reimbursement systems, national diabetes care systems as well as patient characteristics and expectations. .</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>link-685a2e4582f3e6f10c</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Forestry applications of UAVs in Europe: a review</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01431161.2016.1252477</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: aim, use, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Unmanned aerial vehicles (UAVs) or remotely piloted aircraft systems are new platforms that have been increasingly used over the last decade in Europe to collect data for forest research, thanks to the miniaturization and cost reduction of GPS receivers, inertial navigation system, computers, and, most of all, sensors for remote sensing.In this review, after describing the regulatory framework for the operation of UAVs in the European Union (EU), an overview of applications in forest research is presented, followed by a discussion of the results obtained from the analysis of different case studies.Rotary-wing and fixed-wing UAVs are equally distributed among the case studies, while ready-to-fly solutions are preferred over self-designed and developed UAVs. Most adopted technologies are visible-red, green, and blue, multispectral in visible and near-infrared, middle-infrared, thermal infrared imagery, and lidar.The majority of current UAV-based applications for forest research aim to inventory resources, map diseases, classify species, monitor fire and its effects, quantify spatial gaps, and estimate post-harvest soil displacement.Successful implementation of UAVs in forestry depends on UAV features, such as flexibility of use in flight planning, low cost, reliability and autonomy, and capability of timely provision of high-resolution data.Unfortunately, the fragmented regulations among EU countries, a result of the lack of common rules for operating UAVs in Europe, limit the chance to operate within Europe’s boundaries and prevent research mobility and exchange opportunities. Nevertheless, the applications of UAVs are expanding in different domains, and the use of UAVs in forestry will increase, possibly leading to a regular utilization for small-scale monitoring purposes in Europe when recent technologies (i.e. hyperspectral imagery and lidar) and methodological approaches will be consolidated.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>link-efe6b8a6c98afecb54</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moving beyond the “Five Freedoms” by Updating the “Five Provisions” and Introducing Aligned “Animal Welfare Aims”</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ani6100059</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: five, application, range, first; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Although the Five Freedoms paradigm has been very influential in shaping animal welfare thinking for the last two decades, it has two key disadvantages. First, the focus on "freedom" from a range of negative experiences and states has been misunderstood in a number of quarters to mean that complete freedom from these experiences and states is possible, when in fact the best that can be achieved is for them to be minimised. Second, the major focus of the Freedoms on negative experiences and states is now seen to be a disadvantage in view of current understanding that animal welfare management should also include the promotion of positive experiences and states. The challenge therefore was to formulate a paradigm that overcame these two main problems and yet was straightforward enough to be accessible to non-specialists, including members of the lay public who are interested in animal welfare. This was achieved by highlighting the Five Provisions, originally aligned with the Five Freedoms, but now updated to direct welfare management towards activities that both minimise negative experiences or states and promote positive experiences or states as specified by particular Animal Welfare Aims assigned to each Provision. Aspects of the four welfare principles from the European Welfare Quality assessment system (WQ (®) ) and elements of all domains of the Five Domains Model for animal welfare assessment have been incorporated into the new Five Provisions/Welfare Aims paradigm. Thus, the paradigm is easily understood and provides clear guidance on beneficial objectives for animal welfare management. It is anticipated that the paradigm will have application to many species found in a wide range of circumstances.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>link-1912f0da1bbb1c833e</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>The Spillover of Misery: A critical investigation into the social purpose of European integration using the case study of migration management</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17638/03002231</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, five, approach, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Irregular migrants, being defined as asylum seekers, refugees and clandestinos (people in the EU without a valid residency permit), live as a subaltern group at the fringes of European society. They are materially deprived and excluded from regular political culture. In part, this condition stems from the institutions of European integration, such as the Dublin Regulation. This dissertation attempts to understand irregular migrant subalternity by exploring its structural causes. Irregular migration and its management is used as a case study to contribute towards a deeper understanding of the social purpose of European integration. Methodologically, this thesis relies on Critical Grounded Theory. This novel approach is rooted in critical realism and thus rejects the tabula rasa-view of traditional Grounded Theory, maintaining that empirics and theory should continuously inform one another. The Gramscian concept of hegemony is employed to contextualise European integration within neofunctionalism as an ideological practice and neoliberalism as a hegemonic agenda. Vulgar neofunctionalism postulates that integration occurs as the result of spillover of one policy area into another and that European integration is pushed forward by technocratic elites. To illustrate the relationship between neofunctionalism and neoliberalism, to lay bare the consequences of neoliberal and neofunctionalist practices, and to further capture the social purpose of European integration, fieldwork was carried out in five locations (Brussels, Greece, Bulgaria, Italy and Germany) with different groups of interviewees (European Commission staff, national public officials, asylum seekers, clandestinos, fruit farm workers, asylum accommodation staff). It was found that neoliberal neofunctionalism has generated a common outlook on migratory movements which has resulted in the partial harmonisation of asylum legislation and the simultaneous fortification of the EU’s external border. This has had a significant impact on the lives of irregular migrants, who are exposed to reification, commodification, biopolitics, the state of exception, xenophobia and lacking recognition. The emergence of group consciousness is undermined, preventing them from overcoming subalternity. The social purpose of European integration is identified as the (increasingly authoritarian) neoliberal restructuration of the EU which relies on neofunctionalism as its vehicle and justification. This restructuration is self-contradictory as it aims at neoliberalism while producing nationalism, biopolitics and the EU’s deepening internal division. Within the context of the European Union’s democratic deficit and the weakness of social democracy, nationalism may represent an alternative to neoliberalism, speeding up the EU’s disintegration.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>link-5454754a26d9672808</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Epidemiology of traumatic brain injury in Europe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00701-015-2512-7</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: describe, evaluate, methodology; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Traumatic brain injury (TBI) is a critical public health and socio-economic problem throughout the world, making epidemiological monitoring of incidence, prevalence and outcome of TBI necessary. We aimed to describe the epidemiology of traumatic brain injury in Europe and to evaluate the methodology of incidence studies. METHOD: We performed a systematic review and meta-analyses of articles describing the epidemiology of TBI in European countries. A search was conducted in the PubMed electronic database using the terms: epidemiology, incidence, brain injur*, head injur* and Europe. Only articles published in English and reporting on data collected in Europe between 1990 and 2014 were included. RESULTS: In total, 28 epidemiological studies on TBI from 16 European countries were identified in the literature. A great variation was found in case definitions and case ascertainment between studies. Falls and road traffic accidents (RTA) were the two most frequent causes of TBI, with falls being reported more frequently than RTA. In most of the studies a peak TBI incidence was seen in the oldest age groups. In the meta-analysis, an overall incidence rate of 262 per 100,000 for admitted TBI was derived. CONCLUSIONS: Interpretation of published epidemiologic studies is confounded by differences in inclusion criteria and case ascertainment. Nevertheless, changes in epidemiological patterns are found: falls are now the most common cause of TBI, most notably in elderly patients. Improvement of the quality of standardised data collection for TBI is mandatory for reliable monitoring of epidemiological trends and to inform appropriate targeting of prevention campaigns.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>link-b3207048ee16d9ed37</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Development of a cross-cultural deprivation index in five European countries</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/jech-2015-205729</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: five, step, methods, used, first; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Despite a concerted policy effort in Europe, social inequalities in health are a persistent problem. Developing a standardised measure of socioeconomic level across Europe will improve the understanding of the underlying mechanisms and causes of inequalities. This will facilitate developing, implementing and assessing new and more effective policies, and will improve the comparability and reproducibility of health inequality studies among countries. This paper presents the extension of the European Deprivation Index (EDI), a standardised measure first developed in France, to four other European countries-Italy, Portugal, Spain and England, using available 2001 and 1999 national census data. METHODS AND RESULTS: The method previously tested and validated to construct the French EDI was used: first, an individual indicator for relative deprivation was constructed, defined by the minimal number of unmet fundamental needs associated with both objective (income) poverty and subjective poverty. Second, variables available at both individual (European survey) and aggregate (census) levels were identified. Third, an ecological deprivation index was constructed by selecting the set of weighted variables from the second step that best correlated with the individual deprivation indicator. CONCLUSIONS: For each country, the EDI is a weighted combination of aggregated variables from the national census that are most highly correlated with a country-specific individual deprivation indicator. This tool will improve both the historical and international comparability of studies, our understanding of the mechanisms underlying social inequalities in health and implementation of intervention to tackle social inequalities in health.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>link-b4641e4a2cf2c4f2d3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Design of a General‐Purpose European Compound Screening Library for EU‐OPENSCREEN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/cmdc.201402126</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, five, application, range, design, methodology; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>This work describes a collaborative effort to define and apply a protocol for the rational selection of a general-purpose screening library, to be used by the screening platforms affiliated with the EU-OPENSCREEN initiative. It is designed as a standard source of compounds for primary screening against novel biological targets, at the request of research partners. Given the general nature of the potential applications of this compound collection, the focus of the selection strategy lies on ensuring chemical stability, absence of reactive compounds, screening-compliant physicochemical properties, loose compliance to drug-likeness criteria (as drug design is a major, but not exclusive application), and maximal diversity/coverage of chemical space, aimed at providing hits for a wide spectrum of drugable targets. Finally, practical availability/cost issues cannot be avoided. The main goal of this publication is to inform potential future users of this library about its conception, sources, and characteristics. The outline of the selection procedure, notably of the filtering rules designed by a large committee of European medicinal chemists and chemoinformaticians, may be of general methodological interest for the screening/medicinal chemistry community. The selection task of 200K molecules out of a pre-filtered set of 1.4M candidates was shared by five independent European research groups, each picking a subset of 40K compounds according to their own in-house methodology and expertise. An in-depth analysis of chemical space coverage of the library serves not only to characterize the collection, but also to compare the various chemoinformatics-driven selection procedures of maximal diversity sets. Compound selections contributed by various participating groups were mapped onto general-purpose self-organizing maps (SOMs) built on the basis of marketed drugs and bioactive reference molecules. In this way, the occupancy of chemical space by the EU-OPENSCREEN library could be directly compared with distributions of known bioactives of various classes. This mapping highlights the relevance of the selection and shows how the consensus reached by merging the five different 40K selections contributes to achieve this relevance. The approach also allows one to readily identify subsets of target- or target-class-oriented compounds from the EU-OPENSCREEN library to suit the needs of the diverse range of potential users. The final EU-OPENSCREEN library, assembled by merging five independent selections of 40K compounds from various expert groups, represents an excellent example of a Europe-wide collaborative effort toward the common objective of building best-in-class European open screening platforms.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>link-dda7a858850ed6a414</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Healthcare databases in Europe for studying medicine use and safety during pregnancy</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/pds.3613</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, aim, describe, use, five, methods; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PURPOSE: The aim of this study was to describe a number of electronic healthcare databases in Europe in terms of the population covered, the source of the data captured and the availability of data on key variables required for evaluating medicine use and medicine safety during pregnancy. METHODS: A sample of electronic healthcare databases that captured pregnancies and prescription data was selected on the basis of contacts within the EUROCAT network. For each participating database, a database inventory was completed. RESULTS: Eight databases were included, and the total population covered was 25 million. All databases recorded live births, seven captured stillbirths and five had full data available on spontaneous pregnancy losses and induced terminations. In six databases, data were usually available to determine the date of the woman's last menstrual period, whereas in the remainder, algorithms were needed to establish a best estimate for at least some pregnancies. In seven databases, it was possible to use data recorded in the databases to identify pregnancies where the offspring had a congenital anomaly. Information on confounding variables was more commonly available in databases capturing data recorded by primary-care practitioners. All databases captured maternal co-prescribing and a measure of socioeconomic status. CONCLUSION: This study suggests that within Europe, electronic healthcare databases may be valuable sources of data for evaluating medicine use and safety during pregnancy. The suitability of a particular database, however, will depend on the research question, the type of medicine to be evaluated, the prevalence of its use and any adverse outcomes of interest. © 2014 The Authors. Pharmacoepidemiology and Drug Safety published by John Wiley &amp; Sons, Ltd.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>link-8c0d4b8f0701d051bd</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Open drug scenes: responses of five European cities</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/1471-2458-14-853</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: aim, use, five, methods, researchers, first; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Open drug scenes are gatherings of drug users who publicly consume and deal drugs. The authors conducted a study of five European cities that have met such scenes constructively. The aim was to investigate shared and non-shared interventions and strategies in order to increase the understanding of this type of problem. METHODS: First a description was made for the cities of Amsterdam, Frankfurt, Vienna, Zürich and Lisbon. These descriptions were sent to contact persons in each city prior to visit by the researchers. The methods and strategies in each city were discussed and core choices and efforts extracted. A report was sent to the contact group for corrections and clarifications. The paper analyses shared and non-shared traits and strategies. RESULTS: All of the cities had initially a period with conflict between liberal and restrictive policies. A political consensus seems to be a prerequisite for effective action. A core shared characteristic was that drug dependence was met as a health problem and drug use behaviour as a public nuisance problem. Low threshold health services including opioid maintenance treatment were combined with outreach social work and effective policing. CONCLUSION: Prevention, harm reduction and treatment should be combined with law enforcement based on cooperation between police, health care and social services. The aim should be "coexistence" between society and users of illegal substances and the strategy based on several years planning and conjoint efforts. The solutions are found in appropriate combinations of harm reduction and restrictive measures.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>link-6e88b513934bac6b7b</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>European Hernia Society classification of parastomal hernias</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10029-013-1162-z</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, aim, methods; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PURPOSE: A classification of parastomal hernias (PH) is needed to compare different populations described in various trials and cohort studies, complete the previous inguinal and ventral hernia classifications of the European Hernia Society (EHS) and will be integrated into the EuraHS database (European Registry of Abdominal Wall Hernias). METHODS: Several members of the EHS board and invited experts gathered for 2 days to discuss the development of an EHS classification of PH. The discussions were based on a literature review and critical appraisal of existing classifications. RESULTS: The classification proposal is based on the PH defect size (small is ≤5 cm) and the presence of a concomitant incisional hernia (cIH). Four types were defined: Type I, small PH without cIH; Type II, small PH with cIH; Type III, large PH without cIH; and Type IV, large PH with cIH. In addition, the classification grid includes details about whether the hernia recurs after a previous PH repair or whether it is a primary PH. Clinical validation is needed in the future to assess if the classification allows us to differentiate the treatment strategy and if the classification impacts outcome in these different subgroups. CONCLUSION: A classification of PH divided into subgroups according to size and cIH was formulated with the aim of improving the ability to compare different studies and their results.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>purpose aim describe Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>link-841969f270069fefd8</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Discounts and Rebates Granted for Medicines for Hospital Use in Five European Countries</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2174/1876824501305010001</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: use, five, methods, alternatives, used; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Objective: The study aimed to survey price reductions such as discounts and rebates granted for medicines used in hospitals.Methods: We collected official list prices and actual hospital prices of 12 medicines in 25 hospitals in European countries (Austria, the Netherlands, Norway, Portugal and Slovakia).Results: In all five countries price reductions were granted for some of the medicines surveyed.They usually had the form of discounts; additionally, ex-post rebates were reported from Austria and Portugal.For oncology, anti-inflammatory diseases, neurology-multiple sclerosis and blood no price reductions or only minor discounts/rebates on medicines prices were surveyed, whereas discounts/rebates were routinely granted for cardiovascular medicines and medicines for immunomodulation.Price reductions of 100 percent were found in Austria, Portugal and Slovakia.With the exception of Slovakia, the extent of the discounts/rebates did not differ substantially among the hospitals of a country.The highest median price reductions were identified in Norway, followed by the Netherlands.Price reductions for medicines procured by central tendering tended to be higher than those obtained in decentralized procurement. Conclusions:The study shows the existence of discounts and rebates granted for specific medicines for hospital use.The results suggest product-specific patterns.Hospitals appear to have little leeway to negotiate price reductions for medicines to which no therapeutic alternatives are available.High price reductions, including cost-free provision of medicines, tend to be granted for medicines whose treatment is likely to continue in primary care after discharge of the patient.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>link-57fccb5329fe0cde55</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>claim-665c468f893e86b0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Purpose The aim of this paper is to describe and evaluate the use of a five‐step foresight process and the application of scenario methods to grasp the range of future alternatives that might confront researchers and research managers in European metrology research institutes. Design/methodology/approach The paper illustrates how scenario methods were used to, first, serve as a basis for policy recommendations for the field of European metrology research institutes and, second, help experts and stakeholders to network and actively discuss a shared vision of the future of the field.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>The use of LibQUAL+ by European research libraries</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1108/14678041211284704</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: purpose, use, five, design, methodology, approach; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Purpose One of the aims of the LIBER strategic plan 2009‐2012 was to stimulate the use of LibQUAL+ by European research libraries. The purpose of this study is to investigate how far this initiative has been successful. Design/methodology/approach All 385 LIBER libraries were invited to complete an online survey, mounted on Survey Monkey. The questionnaire was meant for all libraries, whether or not they performed a user survey during the last five years and, if so, whether or not they used LibQUAL + as the survey instrument. Findings The study shows that the use of LibQUAL+ in Europe is widespread and that there is a great potential for further growth. LibQUAL+'s strong areas are the ease of administering and opportunities for benchmarking. A weak area is the user unfriendliness: 50 per cent of the libraries having experience with LibQUAL+ find the survey difficult to complete for the participants. Carrying out a LibQUAL+ survey has great practical implications. More than 75 per cent of the respondents took measures to improve their performance on weak areas or to promote their existing services better among the user community. About one third established new services. Practical implications The results point at the need to improve the user friendliness of LibQUAL+. Originality/value This is the first study that covers the experience of European research libraries with LibQUAL+ on a broad scale.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>purpose aim use five Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>link-cc0d4a0f5808dc2ac0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Forecast reconciliation of agricultural GHG emissions in Europe with fuzzy clustering</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10479-026-07363-y</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, compared; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Abstract We propose a novel statistical procedure which combines forecasting reconciliation techniques and unsupervised clustering algorithms to forecast annual greenhouse gases emissions at the territorial level. Specifically, we aim at predicting future emissions from the agricultural sector for Europe by aggregating bottom-level regional forecasts to the national and continental levels. Fuzzy clustering is used to define aggregations of bottom and middle-level series into clusters based on the similarity of emissions patterns; then, the fuzzy hierarchies are combined with the original administrative aggregation structure to improve the prediction accuracy of forecasting models. Empirical results show that fuzzy clustering aggregation, by leveraging uncertainty compared to crisp approaches, enhances forecast reconciliation accuracy at all levels of the hierarchy. Our approach offers a scalable solution to enhance forecast accuracy and reliability, particularly for short time series characterized by complex hierarchical structures.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>link-61c40c259231409c25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Crayfish and Climate: how invasive species amplify aquatic GHG emissions</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5194/egusphere-egu25-6790</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, decline, compared, systems; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Since their introduction to European waters in the 1970s, the invasive red swamp crayfish Procambarus clarkii has rapidly expanded due to traits such as rapid reproduction, high environmental tolerance, and opportunistic feeding. P. clarkii can significantly transform freshwater ecosystems, causing extensive reduction in plant coverage, predation on amphibians and other macroinvertebrates, and a decline in native crayfish species populations. In many systems, the expansion of P. clarkii has lead to a dramatic reduction in plant coverage at specific sites. While numerous studies have explored how climate change influences the spread of invasive species, little is known about the reverse relationship: how invasive species contribute to climate change.As a country with an extensive network of freshwater ecosystems, the Netherlands provides an excellent opportunity to study the effect of invasive species on aquatic GHG emissions. More than half of the Dutch territory has already been invaded by crayfish, with detrimental effects on submerged plants. Additionally, ditches serve as significant hotspots for GHG emissions, with estimates suggesting they are responsible for approximately 10–16% of the Dutch national annual CH4 emissions. These estimates are largely based on measurements in ditches dominated by submerged plants, which have been shown to mitigate CH₄ emissions through mechanisms such as CH4 oxidation and reduction of CH4 formationLoss of submerged plants can therefore lead to a considerable increase in CH4 emissions, further exacerbating the impact of ditches on the national GHG budget.By combining data on ditch CH4 emissions, the area invaded by P. clarkii, and results from a controlled mesocosm experiment focusing on the cascading effects of crayfish on submerged plants and GHG emissions (particularly CH4), we found that high crayfish densities (2 individuals/m2) increase CH4 emissions by 2.4 times compared to systems without crayfish. This effect seems primarily driven by plant clipping and bioturbationThese findings highlight the ecological and climatic consequences of P. clarkii invasions. By enhancing CH4 emissions, this invasive species not only disturbs local aquatic ecosystems but also contributes to global climate change. Understanding the effects of crayfish bioturbation is essential for developing targeted management strategies to mitigate their environmental impact.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>consequence ghg decline compared Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>link-a0302a5ea92787830d</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Literature review on policies to mitigate GHG emissions for cement and concrete</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.resconrec.2022.106278</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, energy; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>The production and use of cement, the binding agent in concrete, emits seven percent of global greenhouse gas emissions annually. Achieving climate change mitigation targets, such as those proposed in the Paris Agreement, requires emission reductions from this sector. The body of research on technical solutions to cement and concrete decarbonization is wide, but technical measures must be coupled with effective policy to achieve decarbonization. This study undertakes a review of previous research on cement and concrete decarbonization and analyzes the most common proposed measures along their level of action, involved stakeholders, barriers to implementation, and coordinated policy actions. The review yielded 37 studies from peer-reviewed articles and technical reports. Analysis showed consensus on the primary technical measures to decarbonize. For cement production, measures include (I) improved energy efficiency, (II) fuel switching, (III) carbon capture utilization and storage, and (IV) reduction of the clinker-to-cement ratio. For concrete production and its end-uses common proposed measures include (V) alternative binders, (VI) material and construction efficiency and (VII) CO2 uptake by concrete. While the literature shows an emerging consensus around technical solutions for decarbonization, there was less clarity about preferred policy solutions and key barriers. The reviewed studies consistently focused on technical solutions and roadmaps to achieve decarbonization, but often omitted discussion of barriers to implementation or specific policy actions to overcome them. Further research is needed to consider the feasibility and costs of implementation; identify potential points of entry for policy actions at different jurisdictional scales; and identify enforcement needs.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>link-3cda5f820c66cc4c3e</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>The GHGs Evolution of LULUCF Sector at the European Union (EU-27 + UK): Romania Case Study</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/atmos13101638</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, compared, reference, period; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Mitigating climate change is a challenge that urgently needs to be addressed, as it has an increasing impact on the planet. According to the latest reports, global CO2 emissions must be neutralized by 2050 in order to limit the rise in temperature to 1.5 °C. This work presents the evolution of Land Use, Land Use Change and Forestry (LULUCF) greenhouse gas (GHG) emissions/removals at the EU-27 + UK level for the 1990–2019 time period, as well as LULUCF emissions/removals forecasts for Romania up to 2040. The results revealed a 23% reduction in GHG emissions for the EU-27 + UK in 2019 compared to 1990. Romania’s yearly average of GHG emissions/removals was 28,000 kt CO2 eq., representing roughly 9.7% of the EU’s annual average. In terms of projections for Romania, the only scenario that will not be in the target set by the new LULUCF Regulation is WEM (Reference Scenario/With Existing Measures), in which net GHG removals will be reduced by approximately 218 kt CO2 eq., or 0.9 percent, in 2030 compared to the reference year; in 2040 compared to 1989, the trend will be accentuated both in absolute values, with a decrease of over 3000 kt CO2 eq., and in relative values of 12%.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>consequence ghg decline compared Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>link-27d87a2ab285395f4b</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>S26 An assessment of short-acting β2-agonist (SABA) use and subsequent greenhouse gas (GHG) emissions in five European countries and the consequence of their potential overuse for asthma in the UK</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/thorax-2020-btsabstracts.32</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: consequence, ghg, emissions, compared, reference, period; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Introduction The SABA Use IN Asthma (SABINA) programme associates SABA overuse (prescription of ≥3 canisters per year versus 0–2) with increased risk of exacerbations and asthma-related healthcare utilisation1; with this overuse common across Europe.2 In parallel, the environmental impact of inhaler choice receives attention but is often focussed on preventers. We analysed the volume of SABA use and its GHG emissions versus total inhaler devices and compared the U.K. with other European countries. Next, we calculated the annual volume and GHG emissions from SABA overuse in asthma in the U.K. using the SABINA U.K. study data. Methods Inhaler use was calculated using sales data obtained from life science analytics company IQVIA™ over 12 months to September 2019. Data were compared by dose, preventing confounding from device actuation count differences. SABA overuse volume in asthma i.e. sum of prescribing ≥3 prescriptions in 12 months, was extracted from Clinical Practice Research Datalink GOLD as part of SABINA U.K. (≥12 years, current asthma diagnosis, any severity, 12 month period between 2007–2019). GHG emissions of inhaler devices were estimated using published and internal AstraZeneca data on their full life cycle. Results SABA represents the majority of inhaler use and of GHG emissions in the U.K. and its neighbours (table 1). However, U.K. SABA use and GHG emissions per capita are approximately treble those of other countries. In SABINA U.K., 284,683 out of 574,913 asthma patients were potentially overusing SABA. The average for this group was 6.51 prescriptions per year. 83% of SABA prescriptions for asthma went to patients overusing SABA. For the U.K. asthma population this represents 9.24 million SABA prescriptions and 250,000 tonnes of CO2[equivalent] annually. Conclusion These data demonstrate the GHG emissions associated with high SABA use across Europe and particularly in the U.K. Implementing guidelines to drive improvements in asthma care would improve asthma control, thereby reducing reliever medication use and exacerbation frequency, benefiting patients and realising carbon savings that go beyond the reduction in SABA use alone. Reference Bloom CI, et al. Adv Ther 2020: https://doi.org/10.1007/s12325-020-01444-5 Janson C, et al. Adv Ther 2020: 37; 1124–1135</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>link-9186a5f06f42d2622f</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Perceptions of GHG emissions and renewable energy sources in Europe, Australia and the USA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11356-021-15935-7</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, energy; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>link-8a503b92ae8e6d88dc</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Assessment of the Dependence of GHG Emissions on the Support and Taxes in the EU Countries</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su13147650</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, compared, applied, energy; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>The reduction of GHG emissions is one of the priorities of the EU countries. The majority of studies show that financial support and environmental taxes are one of the most effective measures for the mitigation of the negative consequences of climate change. The EU countries employ different environmental support measures and environmental taxes to reduce GHG emissions. There is a shortage of new studies on these measures. The aim of the present study is to compare the effectiveness of the environmental support measures of the EU countries with the effectiveness of environmental taxes in relation to the reduction of GHG emissions. This study is characterized by the broad scope of its data analysis and its systematic approach to the EU’s environmental policy measures. An empirical study was performed for the EU countries with the aim of addressing this research problem and substantiating theoretical insights. A total of 27 EU member states from 2009 to 2018 were selected as research samples. The research is based on a cause-and-effect relationship, where the factors affecting environmental pollution (environmental taxes and subsidies) are the cause, and GHG emissions are the effect. Statistical research methods were used in the empirical study: descriptive statistics, the Shapiro–Wilk test, one-way analysis of variance (ANOVA), simple regression and cluster analysis. The results show that the older member countries of the EU, which had directed the financial measures of environmental policy towards a reduction in energy consumption, managed to achieve a greater reduction in GHG emissions compared to the countries which had not applied those measures. The Central and Eastern European countries are characterized by lower environmental taxes and lower expenditure allocated to environmental protection. The countries with a higher GDP per capita have greater GHG emissions that the countries with lower GDP per capita. This is associated with greater consumption, waste, and energy consumption. The study conducted gives rise to a discussion regarding data sufficiency in the assessment and forecasting of GHG emissions and their environmental consequences.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>link-c6c5d55866a5bf32ee</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Greenhouse Gas Emissions and Health in the Countries of the European Union</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3389/fpubh.2021.756652</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, compared, expected; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>In the current era of globalization, a clean environment remains a crucial factor for the health of the population. Thus, improving air quality is a major focus of environmental policies, as it affects all aspects of nature, including humans. For these reasons, it is appropriate to take into account the health risks posed by greenhouse gas (GHG) emissions released into the atmosphere. With regard to global GHG emissions, there are concerns about the loss of protection of the ozone layer and it is very likely that climate change can be expected, which multiplies the environmental threat and has potentially serious global consequences. In this regard, it is important to pay increased attention to emissions that enter the atmosphere, which include countless toxic substances. The aim of this study was to examine the associations between selected GHG emissions and the health of the European Union (EU) population represented by disability-adjusted life years (DALYs). This aim was achieved using several analytical procedures (descriptive analysis, correlation analysis, cluster analysis, and panel regression analysis), which included five environmental variables (carbon dioxide (CO2), methane (CH4) in CO2 equivalent, nitrous oxide (N2O) in CO2 equivalent, hydrofluorocarbons (HFC) in CO2 equivalent, sulfur hexafluoride (SF6) in CO2 equivalent) and one health variable (DALYs). An emphasis was placed on the use of quantitative methods. The results showed that CO2 emissions have a dominant position among selected GHG emissions. The revealed positive link between CO2 and DALYs indicated that a decrease in CO2 may be associated with a decrease in DALYs, but it is also true that this cannot be done without reducing emissions of other combustion products. In terms of CO2, the least positive scores were observed in Luxembourg and Estonia. Germany had the lowest score of DALYs, representing the most positive health outcome in the EU. In terms of total GHG emissions, Ireland and Luxembourg were considered to be less positive countries compared to the other analyzed countries. Countries should focus on reducing GHG emissions in general, but from a health point of view, reducing CO2 emissions seems to be the most beneficial.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>link-84c74bc70b2d62bea7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Economic Analysis of Measures for GHG Emission Reduction</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su13041712</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, period, expected, energy; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>The European Union, as a signatory to the Paris Agreement, has approached the action against greenhouse gas (GHG) emissions and climate change quite ambitiously, striving to achieve climate neutrality by 2050. Extension of the European Green Deal policy implementation to the Western Balkans can only increase the chances of the climate neutral agenda. Expectations from Montenegro in the coming period are transposable to other Western Balkans countries as they are urged to start implementing the Paris Agreement by establishing appropriate policies and measures. In this regard, this paper presents the analysis of the financial and economic analysis results of measures to reduce GHG emissions in Montenegro. With this respect, least cost analysis—cost effectiveness analysis and cost–benefit analysis were conducted. The analysis results indicated that due to the thermal power plant reconstruction, increased use of renewable energy sources and measures to increase energy efficiency, the largest reduction in GHG emissions in Montenegro in the next 10 years is expected in the energy sector.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>link-62982c74d2ed4dcdb8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>The influence of ore grade decline on energy consumption and GhG emissions: The case of gold</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.envdev.2021.100683</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, decline, energy; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>consequence ghg decline compared Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>link-4f4dd4235d13fede5e</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GHG Emissions Performance: Alternative Accounting Approaches for the European Union</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.18267/j.pep.761</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, period; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>This study provides evidence on the probability of adopting an accounting approach for emission allowances and greenhouse gas emissions as a function of each company's GHG emissions performance. The different accounting treatments adopted by national standard-setters and the lack of specific guidance from the International Accounting Standard Board (IASB) allow identification of the use of multiple accounting approaches. Based on a sample of 85 companies registered with the Portuguese, Spanish, and French National Plans of Allocation, data collected from the annual reports were analysed for the period 2008-2014. The results suggest that the probability of adopting omission strategies is positively associated with better GHG emissions performances. It addresses the importance of introducing the transactions of the European Union Emissions Trading Scheme (EU ETS) in financial reporting as the visibility of the costs of polluting is one of the purposes of the market mechanism.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>link-e19a41805ae8687a6e</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>How photovoltaics can contribute to GHG emission reductions of 55% in the EU by 2030</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.rser.2020.109836</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, long-term, energy; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>The new European Commission plans to raise the greenhouse gas (GHG) emissions reduction target from 40% towards 55% by 2030 and make Europe the first climate-neutral continent by 2050. Achieving this will require accelerated energy efficiency measures, deeper electrification of sectors currently consuming conventional fuels and the deployment of more renewables, faster. This opinion article looks specifically at the role of photovoltaics (PV), based on scenarios from the Commission's 2018 long-term strategy (LTS) for energy and climate. To reach a 55% GHG emissions reduction, the cumulative PV capacity in the EU and the UK would need to surge to 455–605 GW, depending on the strategic policy scenario. This implies a compound annual growth rate between 12 and 15% in the timeframe 2020–203 to increase the annual PV market from approximately 16.5 GW in 2019 to 50–80 GW by 2030. Such a volume can provide the basis for reviving the European solar manufacturing industry as well as creating more than 100 000 jobs along the value chain.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>link-ab909c8af86328ecda</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>The role of woody biomass for reduction of fossil GHG emissions in the future North European energy sector</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.apenergy.2020.115360</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, transport, compared, same, applied; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>In this study, we analyse the use of woody biomass in the heat and power sector in Northern Europe towards 2040 and quantify the fossil GHG-emission reductions from biomass use at different carbon price levels. The applied partial equilibrium energy system model has endogenous capacity investments in relevant heat and power technologies. The results show that use of woody biomass can reduce the direct emissions from the Northern European power and heat sector by 4–27% for carbon prices in the range of 5–103 €/tonne CO2eq in 2030 compared to a scenario where woody biomass is not available for power and heat generation. The cost of delivering heat and electricity increases with 0.2–0.7% when wood chips are excluded, depending on the carbon price. At a low carbon price, the use of natural gas, wind, and coal power generation increases when biomass is not available for power and heat generation. At higher carbon prices, solar power, wind power, power-to-heat, and natural gas become increasingly competitive, and therefore the use of biomass has a lower impact on emission reductions. Using the same biomass volumes for liquid transport fuel, we find a higher impact on fossil carbon emission reductions but substantially higher costs. The main conclusion from this study is that woody biomass contribution to lowering the fossil emission from heat and power generation in the Northern Europe, and the transition to low carbon energy system will likely be more costly if biomass is excluded from heat and power generation.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>link-8166614cfa32b9f7a6</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Spatial Planning Policy for Sustainability: Analysis Connecting Land Use and GHG Emission in Rural Areas</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su12030947</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, systems; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Anthropogenic greenhouse gas (GHG) emissions are the highest they have ever been and the climate change they have triggered is having consequences on both human and natural systems. The aim of the paper is to demonstrate that an integrated reading of urban and rural land uses in relation to GHG emissions is feasible and useful at the regional level in order to reach emissions reduction. The Po Valley in Italy is an emblematic case study because its features are unique in Europe for high population density, urban sprawl, intensive agriculture, livestock management and consequently high emission levels. The methodology examines the total GHG emissions in relation to urban and rural areas. Between 2000 and 2010, the trend of CO2-equivalent emissions for the macro-regions of Italy shows a national decrease in contrast to the area of our case study which has seen a steady increase and growth trend over time. The paper analyzes some possible reasons linked to this anomaly, and it presents an estimation of the CO2-equivalent emissions related to the use of agricultural land. The main output of the paper is a new overview for research that aims to propose integrated solutions and policies at the local level with a wider vision focused on GHG emission knowledge, supported by Strategic Environmental Assessment.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>link-e32d2869e733947c2b</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GHG emissions and fossil energy use as consequences of efforts of improving human well-being in Africa</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jenvman.2020.111136</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, energy; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>link-76346b229b4b09c7f4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Embodied GHG emissions of buildings – The hidden challenge for effective climate change mitigation</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.apenergy.2019.114107</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, energy; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Buildings are major sources of greenhouse gas (GHG) emissions and contributors to the climate crisis. To meet climate-change mitigation needs, one must go beyond operational energy consumption and related GHG emissions of buildings and address their full life cycle. This study investigates the global trends of GHG emissions arising across the life cycle of buildings by systematically compiling and analysing more than 650 life cycle assessment (LCA) case studies. The results, presented for different energy performance classes based on a final sample of 238 cases, show a clear reduction trend in life cycle GHG emissions due to improved operational energy performance. However, the analysis reveals an increase in relative and absolute contributions of so‐called ‘embodied’ GHG emissions, i.e., emissions arising from manufacturing and processing of building materials. While the average share of embodied GHG emissions from buildings following current energy performance regulations is approximately 20–25% of life cycle GHG emissions, this figure escalates to 45–50% for highly energy-efficient buildings and surpasses 90% in extreme cases. Furthermore, this study analyses GHG emissions at time of occurrence, highlighting the ‘carbon spike’ from building production. Relating the results to existing benchmarks for buildings’ GHG emissions in the Swiss SIA energy efficiency path shows that most cases exceed the target of 11.0 kgCO2eq/m2a. Considering global GHG reduction targets, these results emphasize the urgent need to reduce GHG emissions of buildings by optimizing both operational and embodied impacts. The analysis further confirmed a need for improving transparency and comparability of LCA studies.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>link-931d100a71d2e54cd3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Driving factors of GHG emissions in the EU transport activity</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.tranpol.2017.10.008</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, transport; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>link-e4d65ee6bdcd495530</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Comparing Madrid and Salvador GHG emission inventories: Implications for future researches</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.12660/joscmv10n1p17-32</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, energy; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>This paper compares the Greenhouse Gas (GHG) emission inventories of Madrid and Salvador and discusses some implications for future researches, focusing on city-level carbon accounting (CLCA) of emissions from urban supply chains (USC) and final consumers. To carry out this study, secondary data were collected from official documents of municipal governments of these two cities. According to the results, there are differences in stationary energy GHG emissions due to the big distinction concerning electricity emission factors used by each city. Air transportation GHG emissions are also very different. These two cities share some common figures regarding road transportation and per capita waste sector GHG emissions. In the conclusion section, we discuss opportunities for improvement of the cities’ GHG emission inventories as well as some implications for policy-making and future researches on carbon accounting, with focus on an integrated production-consumption system.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>consequence ghg decline compared Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>link-ce4f03e5a15e397e02</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EU Reference Scenario 2016 - Energy, transport and GHG emissions Trends to 2050.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2521262923</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, transport, reference, energy; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>link-84e44693433174b395</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>The Best (and Worst) of GHG Emission Trading Systems: Comparing the EU ETS with Its Followers</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3389/fenrg.2016.00027</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, systems; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>The European Emission Trading System (EU ETS) is generally considered as the prototype system for the other Emission Trading Systems (ETSs) for the reduction of Greenhouse Gases (GHG) that are rapidly spreading around the world. To get a deeper understanding on the actual capacity of the EU ETS to stand as a model for the other ETSs, the present paper discusses the differences and similarities of the EU ETS with respect to the other main ETSs and the emerging trends that these systems seem to share, comparing the different cap and trade regimes in order to identify the best practices and the desirable features that future ETSs should have. As emerges from the comparative analysis performed in this article, although the followers share some common flaws with the EU ETS, they have also shown the capacity to innovate and possibly devise alternative ways to manage their own ETS regimes, which may in the long term jeopardise the EU leadership in the ETSs context.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>consequence ghg decline compared Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>link-92753a5655cdf60863</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Does stakeholder pressure influence corporate GHG emissions reporting? Empirical evidence from Europe</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1108/aaaj-12-2013-1547</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, grow, applied; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Purpose – The purpose of this paper is to seek to shed light on the practice of incomplete corporate disclosure of quantitative Greenhouse gas (GHG) emissions and investigates whether external stakeholder pressure influences the existence, and separately, the completeness of voluntary GHG emissions disclosures by 431 European companies. Design/methodology/approach – A classification of reporting completeness is developed with respect to the scope, type and reporting boundary of GHG emissions based on the guidelines of the GHG Protocol, Global Reporting Initiative and the Carbon Disclosure Project. Logistic regression analysis is applied to examine whether proxies for exposure to climate change concerns from different stakeholder groups influence the existence and/or completeness of quantitative GHG emissions disclosure. Findings – From 2005 to 2009, on average only 15 percent of companies that disclose GHG emissions report them in a manner that the authors consider complete. Results of regression analyses suggest that external stakeholder pressure is a determinant of the existence but not the completeness of emissions disclosure. Findings are consistent with stakeholder theory arguments that companies respond to external stakeholder pressure to report GHG emissions, but also with legitimacy theory claims that firms can use carbon disclosure, in this case the incomplete reporting of emissions, as a symbolic act to address legitimacy exposures. Practical implications – Bringing corporate GHG emissions disclosure in line with recommended guidelines will require either more direct stakeholder pressure or, perhaps, a mandated disclosure regime. In the meantime, users of the data will need to carefully consider the relevance of the reported data and develop the necessary competencies to detect and control for its incompleteness. A more troubling concern is that stakeholders may instead grow to accept less than complete disclosure. Originality/value – The paper represents the first large-scale empirical study into the completeness of companies’ disclosure of quantitative GHG emissions and is the first to analyze these disclosures in the context of stakeholder pressure and its relation to legitimation.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>link-2f25ad1f7da4276334</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Reducing GHG emissions from ships in port areas</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.rtbm.2015.10.008</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Climate change has recently received more attention in the shipping sector. This is mainly due to a growing demand for reduced global emissions and the fact that shipping is one of the fastest growing sectors in terms of greenhouse gas (GHG) emissions. In parallel, ports have started to introduce programmes and policies to address these emissions. This study aims at quantifying potential reductions of ships' emissions of GHG from efforts implemented by ports. Building on a model that calculates GHG emissions from ships in various scenarios for individual ports, different kinds of measures for emission reductions are investigated for diverse types of vessels and parts of the port area. A case study of the ship traffic to the Port of Gothenburg is performed. Projections of ship emissions in the port area for 2030 are made, and three scenarios, ‘1. Alternative fuel’, ‘2. Ship design’ and ‘3. Operation’, are analysed. These scenarios are related to a business as usual development. GHG emissions from ships in the port are projected to increase by 40% to 2030 in a business as usual (BAU) scenario. The highest reductions were seen in the ‘Operation’ scenario where GHG emissions were 10% lower than the BAU level.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>consequence ghg emissions Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>link-c8cf4332ab2be8b5a4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>claim-70046b6e95c1592f</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>As a consequence, GHG emissions by transport will decline 12% by 2030 compared with 2005; in the reference scenario in the same period, emissions are expected to grow 17%. The model suite applied in iTREN-2030 comprises POLES (prospective outlook on long-term energy systems), a simulation model for development of long-term (2050) energy supply-and-demand scenarios; TREMOVE; ASTRA (assesment of transport strategies); and TRANS-TOOLS.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>The Impact of Agro-Economic Factors on GHG Emissions: Evidence from European Developing and Advanced Economies</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/su71215815</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: ghg, emissions, compared; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Environmental degradation by greenhouse gas (GHG) emissions has been an important challenge of sustainable economic development and climate changes control. Industry is the major source of CO2 emissions, whereas 84% of global anthropogenic methane and nitrous-oxide emissions emerge from agriculture. The impact of agro-economic factors on GHG emissions in European developing economies (Southeastern Europe in focus) as compared with European advanced economies has been examined in this paper. The results have confirmed the existence of significant differences in impact of these factors depending on the level of economic development. For both groups of economies, we have confirmed the Environmental Kuznets Curve (EKC) hypothesis (inverted U-shaped relationship between GDP per capita and carbon dioxide emissions), but different sectoral outputs, too. We have also established different impacts of agro emission sources. In developing economies, we have recognized livestock breeding as a predominant factor and recommended measures for reducing the emissions in this sector, following developed economies. The findings may be useful to European developing economies as a support to implementation of binding commitments emerging from the UN Framework Convention on Climate Change (UNFCCC). In the panel analysis, we have taken into consideration the non-stationarity of the series, heterogeneity of the sample, and also examined a dynamic specification.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>consequence ghg decline compared Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>link-ef9ae261b1d077ba30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Benchmark Beating with the Increasing Convex Order</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.48550/arxiv.2311.01692</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, benchmark, order; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>In this paper we model benchmark beating with the increasing convex order (ICX order). The mean constraint in the mean-variance theory of portfolio selection can be regarded as beating a constant. We then investigate the problem of minimizing the variance of a portfolio with ICX order constraints, based on which we also study the problem of beating-performance-variance efficient portfolios. The optimal and efficient portfolios are all worked out in closed form for complete markets.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>all since benchmark order Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>link-0066ee1b25934ca567</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>European anthropogenic AFOLU greenhouse gas emissions: a review and benchmark data</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5194/essd-12-961-2020</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: benchmark, order, national, credible; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Abstract. Emission of greenhouse gases (GHG) and removals from land, including both anthropogenic and natural fluxes, require reliable quantification, along with estimates of their inherent uncertainties, in order to support credible mitigation action under the Paris Agreement. This study provides a state-of-the-art scientific overview of bottom-up anthropogenic emissions data from agriculture, forestry and other land use (AFOLU) in Europe. The data integrates recent AFOLU emission inventories with ecosystem data and land carbon models, covering the European Union (EU28) and summarizes GHG emissions and removals over the period 1990–2016, of relevance for UNFCCC. This compilation of bottom-up estimates of the AFOLU GHG emissions of European national greenhouse gas inventories (NGHGI) with those of land carbon models and observation-based estimates of large-scale GHG fluxes, aims at improving the overall estimates of the GHG balance in Europe with respect to land GHG emissions and removals. Particular effort is devoted to the estimation of uncertainty, its propagation and role in the comparison of different estimates. While NGHGI data for EU28 provides consistent quantification of uncertainty following the established IPCC guidelines, uncertainty in the estimates produced with other methods will need to account for both within model uncertainty and the spread from different model results. At EU28 level, the largest inconsistencies between estimates are mainly due to different sources of data related to human activity which result in emissions or removals taking place during a given period of time (IPCC 2006) referred here as activity data (AD) and methodologies (Tiers) used for calculating emissions/removals from AFOLU sectors. The referenced datasets related to figures are visualised at https://doi.org/10.5281/zenodo.3460311, Petrescu et al., 2019.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>all since benchmark order Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>link-bdae73e1f2df930355</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Europe since 1970</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5040/9781474207775.0093</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, since, national; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>There are forty-six countries in Europe, sharing myriad influences and overlaps. The Second World War only ended in 1945, followed by the Cold War. On one side stood Capitalist Western Europe, protected by America: on the other were Eastern European Warsaw Pact countries under Soviet Communism (plus non-aligned Yugoslavia and Albania). The USA and USSR pursued a deadly nuclear race, as well as proxy conflicts around the globe. Repressed panic and paranoia lasted in Europe until the Berlin Wall ‘fell’ in 1989. In this period, while war in Europe was no longer between nations, internal violence within some countries was rife. The continent also appeared to still be divided between Western Europe and Eastern Europe. However, the European Economic Community (later European Union) gradually incorporated more countries. Following the Communist collapse, Eastern Europe nations joined the EU fold, today containing twenty-eight member countries (although Britain has voted to leave). Europe is the world’s second-largest economic unit after America, containing four of the world’s eight richest nations. There persist, however, considerable discrepancies in wealth, also reflected in relative political strength (e.g. Germany) and weakness (e.g. Greece). Culturally and socially, the decisive change in Europe since 1970 was from post-war state-regulated ‘command economies’ – Social Democracy in Western Europe, Communism in Eastern Europe – to US-style Neoliberal Capitalism, the latter arguing for minimal state intervention and a ‘free market’, and prioritizing financial services and the consumption of goods and services rather than industrial production, which now generally happens in Asia or elsewhere. Today, due to the inroads of Neoliberal policies, architects in all European countries bid competitively for work. Nation-states are correspondingly weaker, whereas global corporations, mostly American, operate beyond national politics and economic systems. Globalization, however, must be seen as a deeper process offering real opportunities for European architects. American cultural influences have been especially strong in Europe since 1970. Car ownership soared, with cities dominated by the combustion engine. France was the country that most resented American influences, and indeed Europe still retains its own cultures and idiosyncratic ways. The major sociocultural change stems from the collapse of former European empires, with millions of people from ex-colonies migrating to the ‘home country’. What is Europe’s role within this post-imperial, globalized world? Europe’s relatively wealth, deep architectural traditions, and elite knowledge-based creative services means it can plausibly claim to be the world’s architectural epicentre (e.g. 600,000 architects, around 1 architect per 1,000 people, 360 architectural schools, etc.). Numerous ‘starchitects’ are European, proportionately higher than for the USA or Asia. Yet there is no distinctive ‘European’ architecture: its design diversity has become marketable. With the 1970s/80s ending of Communism and Welfare States, state-funded schemes evaporated. Deaths of first-generation and second-generation Modernists happened when European Modernism was condemned as unpopular and alienating. Post-Modernism was one reaction, strongest in Italy and Austria; another was Critical Theory, from French Post-Structuralism, as incubated by Manfredo Tafuri and furthered by Rem Koolhaas, Bernard Tschumi, Zaha Hadid, and so on. The 1973–74 ‘Oil Crises’ intensified criticisms of high-consumption Capitalism, leading to sustainable architecture. Yet profit accumulation and technological innovation continued, epitomized by digitalization from the USA. What emerged from the 1970s was ‘Hyper Modernism’, continuing earlier Modernist themes/forms, but incorporating new issues like digitalization. Three responses emerged – British High Tech, Dutch genericism, and Swiss renunciation – while others preferred to reaffirm civic traditions, notably Aldo Rossi, Hans Hollein, James Stirling, Rafael Moneo, Álvaro Siza Vieira, or West Berlin’s IBA programme. In future, Hyper Modernism, spurred by design research, can focus on social participation or urban historic regeneration such as Herzog and de Meuron’s Elbe Philharmonic.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>all since appears Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>link-cd025356f67cfa717b</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>The European Union and Democratization in Central and Southeastern Europe since 1989</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/9781108752466.021</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: since, governments, credible; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>A central tool of the European Union (EU) to promote the democratization of post-communist Europe is its accession conditionality: the conditions it attaches to the offer of membership. Yet the EU’s influence on democratization varies across countries, and over time between the periods before and after accession. A key factor limiting the EU’s impact are the domestic costs of complying with the EU’s conditionality: the more governments rely on illiberal and undemocratic means to maintain power, the less influence the EU has. Moreover, even if the domestic adjustment costs are not prohibitively high, for EU conditionality to bring about, or lock in democratic change, the positive and negative incentives relating to the benefits of EU membership have to be credible. The limited credibility of the EU’s incentives, both of the sanctions against backsliding in new members and of the reward of accession for current candidate countries in Southeastern Europe, is a key explanation for the setback in the EU’s democratizing role during this decade.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>all since appears Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>link-7ac05a043fdf561fc8</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Europe since 1970</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5040/9781474207775.093</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, since, national; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>There are forty-six countries in Europe, sharing myriad influences and overlaps. The Second World War only ended in 1945, followed by the Cold War. On one side stood Capitalist Western Europe, protected by America: on the other were Eastern European Warsaw Pact countries under Soviet Communism (plus non-aligned Yugoslavia and Albania). The USA and USSR pursued a deadly nuclear race, as well as proxy conflicts around the globe. Repressed panic and paranoia lasted in Europe until the Berlin Wall ‘fell’ in 1989. In this period, while war in Europe was no longer between nations, internal violence within some countries was rife. The continent also appeared to still be divided between Western Europe and Eastern Europe. However, the European Economic Community (later European Union) gradually incorporated more countries. Following the Communist collapse, Eastern Europe nations joined the EU fold, today containing twenty-eight member countries (although Britain has voted to leave). Europe is the world’s second-largest economic unit after America, containing four of the world’s eight richest nations. There persist, however, considerable discrepancies in wealth, also reflected in relative political strength (e.g. Germany) and weakness (e.g. Greece). Culturally and socially, the decisive change in Europe since 1970 was from post-war state-regulated ‘command economies’ – Social Democracy in Western Europe, Communism in Eastern Europe – to US-style Neoliberal Capitalism, the latter arguing for minimal state intervention and a ‘free market’, and prioritizing financial services and the consumption of goods and services rather than industrial production, which now generally happens in Asia or elsewhere. Today, due to the inroads of Neoliberal policies, architects in all European countries bid competitively for work. Nation-states are correspondingly weaker, whereas global corporations, mostly American, operate beyond national politics and economic systems. Globalization, however, must be seen as a deeper process offering real opportunities for European architects. American cultural influences have been especially strong in Europe since 1970. Car ownership soared, with cities dominated by the combustion engine. France was the country that most resented American influences, and indeed Europe still retains its own cultures and idiosyncratic ways. The major sociocultural change stems from the collapse of former European empires, with millions of people from ex-colonies migrating to the ‘home country’. What is Europe’s role within this post-imperial, globalized world? Europe’s relatively wealth, deep architectural traditions, and elite knowledge-based creative services means it can plausibly claim to be the world’s architectural epicentre (e.g. 600,000 architects, around 1 architect per 1,000 people, 360 architectural schools, etc.). Numerous ‘starchitects’ are European, proportionately higher than for the USA or Asia. Yet there is no distinctive ‘European’ architecture: its design diversity has become marketable. With the 1970s/80s ending of Communism and Welfare States, state-funded schemes evaporated. Deaths of first-generation and second-generation Modernists happened when European Modernism was condemned as unpopular and alienating. Post-Modernism was one reaction, strongest in Italy and Austria; another was Critical Theory, from French Post-Structuralism, as incubated by Manfredo Tafuri and furthered by Rem Koolhaas, Bernard Tschumi, Zaha Hadid, and so on. The 1973–74 ‘Oil Crises’ intensified criticisms of high-consumption Capitalism, leading to sustainable architecture. Yet profit accumulation and technological innovation continued, epitomized by digitalization from the USA. What emerged from the 1970s was ‘Hyper Modernism’, continuing earlier Modernist themes/forms, but incorporating new issues like digitalization. Three responses emerged – British High Tech, Dutch genericism, and Swiss renunciation – while others preferred to reaffirm civic traditions, notably Aldo Rossi, Hans Hollein, James Stirling, Rafael Moneo, Álvaro Siza Vieira, or West Berlin’s IBA programme. In future, Hyper Modernism, spurred by design research, can focus on social participation or urban historic regeneration such as Herzog and de Meuron’s Elbe Philharmonic.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>all since appears Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>link-65fc64b9ec89502b32</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Benchmarking Framework to Encourage Energy Efficiency Investments in South Europe. The Trust EPC South Approach</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.proenv.2017.03.125</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, since, order, national, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>The Energy Performance Contracting (EPC) market is still embryonic in South Europe since there are still many barriers: difficult access to financing, limited investors’ confidence in EPC models, scarcity of flagship projects, lack of certification schemes and financing mechanisms, especially for the tertiary sector (hospitality, tourism, healthcare), which presents a huge potential for Energy Efficiency (EE). The Trust EPC South project, funded by Horizon 2020 Research and Innovation Programme, aims to scale up investments in EE solutions in the private tertiary sector in South Europe, by delivering a robust investment standardization and benchmarking framework and a pipeline of bankable EPC projects in 6 countries (Portugal, Spain, France, Italy, Croatia and Greece); its results will eventually be extended to the Balkan. Tailored capacity building activities will allow an easier access to third-party financing, thus unlocking the large tertiary sector EE and Renewable Energy market potential. Initially, national market analyses took place (EPC providers, beneficiaries-clients, and financial institutions) to identify the market potential. National Discussion Platforms were set up to develop the national roadmaps addressing mechanisms for mitigation of policy, legal, and especially financial barriers. An investment standardization and benchmarking framework, built upon an established real estate assessment tool (Green Rating™), is actually setting up in order to build trust amongst all parts of the EPC value chain. The methodology will be upgraded including a financial assessment model.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>all since benchmark order Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>link-8ee0d9d569b990581f</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Modelling recent and future climatic suitability for fasciolosis in Europe</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4081/gh.2015.352</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, since, appears, order, programmes; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Fasciola hepatica is a parasitic worm responsible for fasciolosis in grazed ruminants in Europe. The free-living stages of this parasite are sensitive to temperature and soil moisture, as are the intermediate snail hosts the parasite depends on for its life-cycle. We used a climate-driven disease model in order to assess the impact of recent and potential future climate changes on the incidence of fasciolosis and to estimate the related uncertainties at the scale of the European landmass. The current climate appears to be highly suitable for fasciolosis throughout the European Union with the exception of some parts of the Mediterranean region. Simulated climatic suitability for fasciolosis significantly increased during the 2000s in central and northwestern Europe, which is consistent with an observed increased in ruminant infections. The simulation showed that recent trends are likely to continue in the future with the estimated pattern of climate change for northern Europe, possibly extending the season suitable for development of the parasite in the environment by up to four months. For southern Europe, the simulated burden of disease may be lower, but the projected climate change will increase the risk during the winter months, since the simulated changes in temperature and moisture support the development of the free-living and intra-molluscan stages between November and March. In the event of predicted climate change, F. hepatica will present a serious risk to the health, welfare and productivity of all ruminant livestock. Improved, bespoke control programmes, both at farm and region levels, will then become imperative if problems, such as resistance of the parasite associated with increased drug use, are to be mitigated.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>all since appears Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>link-f81a837a860f194076</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fauna Europaea – all European animal species on the web</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3897/bdj.2.e4034</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, governments, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Fauna Europaea is Europe's main zoological taxonomic index, making the scientific names and distributions of all living, currently known, multicellular, European land and freshwater animals species integrally available in one authoritative database. Fauna Europaea covers about 260,000 taxon names, including 145,000 accepted (sub)species, assembled by a large network of (&gt;400) leading specialists, using advanced electronic tools for data collations with data quality assured through sophisticated validation routines. Fauna Europaea started in 2000 as an EC funded FP5 project and provides a unique taxonomic reference for many user-groups such as scientists, governments, industries, nature conservation communities and educational programs. Fauna Europaea was formally accepted as an INSPIRE standard for Europe, as part of the European Taxonomic Backbone established in PESI. Fauna Europaea provides a public web portal at faunaeur.org with links to other key biodiversity services, is installed as a taxonomic backbone in wide range of biodiversity services and actively contributes to biodiversity informatics innovations in various initiatives and EC programs.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>all since appears Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>link-3791d1041108b9979d</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Benchmarking Beam Envelope Models for the European Spallation Source</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.18429/jacow-ipac2014-tupro061</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, since, benchmark, order; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>TraceWin is used at the European Spallation Source (ESS) as the design tool, while fast and accurate on-line models will be needed during the operations. Three models are compared: the ESS Linac Simulator (ELS), TraceWin and the OpenXAL. In all of the benchmarked models, dynamics of each beam-line element is, to the first order, represented by a transfer matrix. Differences in the matrices occur, since different reference frames are used and as well different assumptions about the energy of the particles are made. General transformations of the reference frames will be presented. Using those, the comparison of transfer maps among TraceWin and OpenXAL are given. When the differences between TraceWin and OpenXAL were unclear, the benchmark versus other code, like MAD-X and Dynac was done. The best implementations were combined into a new on-line model implementation Java ELS (or JELS) and at last the comparison of the latter with TraceWin is given.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>all since benchmark order Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>link-11c2f7d451f79141db</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>The Multimodal Brain Tumor Image Segmentation Benchmark (BRATS)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/tmi.2014.2377694</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, good, benchmark; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>In this paper we report the set-up and results of the Multimodal Brain Tumor Image Segmentation Benchmark (BRATS) organized in conjunction with the MICCAI 2012 and 2013 conferences. Twenty state-of-the-art tumor segmentation algorithms were applied to a set of 65 multi-contrast MR scans of low- and high-grade glioma patients-manually annotated by up to four raters-and to 65 comparable scans generated using tumor image simulation software. Quantitative evaluations revealed considerable disagreement between the human raters in segmenting various tumor sub-regions (Dice scores in the range 74%-85%), illustrating the difficulty of this task. We found that different algorithms worked best for different sub-regions (reaching performance comparable to human inter-rater variability), but that no single algorithm ranked in the top for all sub-regions simultaneously. Fusing several good algorithms using a hierarchical majority vote yielded segmentations that consistently ranked above all individual algorithms, indicating remaining opportunities for further methodological improvements. The BRATS image data and manual annotations continue to be publicly available through an online evaluation system as an ongoing benchmarking resource.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>all since benchmark order Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>link-456fc9824c61e88e6a</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Income Inequality in the European Union</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1787/5k9bdt47q5zt-en</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: all, since, appears, reduce, national, large; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Poor growth performance over the past decades in Europe has increased concerns for rising income dispersion and social exclusion. European authorities have recently launched the Europe 2020 strategy which aims to improve social inclusion in Europe on top of already existing European regional policies aiming to reduce regional disparities through stimulating growth in areas where incomes are relatively low. While it is most common to confine measures of inequality to national borders, the existence of such union-wide objectives and policies motivates measuring income dispersion among all Europeans in this paper. Towards the end of the 2000s the income distribution in Europe was more unequal than in the average OECD country, albeit notably less so than in the United States. It is the within-country, not the between-country dimension, which appears to be most important. Inequality in Europe has risen quite substantially since the mid 1980s. While the EU enlargement process has contributed to this, it is not the only explanation since inequality has also increased within a “core” of 8 European countries. Large income gains among the 10% top earners appear to be a main driver behind this evolution.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>all since appears Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>link-091ff26cb050d79a4f</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>claim-828f32d0bc636845</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>All in all, since the EC forecast appears to be a good benchmark, in order to reduce the (optimistic) forecast bias, national governments could be forced to justify any large (optimistic) deviation from this benchmark when presenting their respective national Stability and Growth Programmes. Credible fiscal plans that aim at restoring fiscal sustainability will be essential to counter the present increase in debt levels all across Europe.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Management, regulation and environmental impacts of nitrogen fertilization in northwestern Europe under the Nitrates Directive; a benchmark study</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5194/bg-9-5143-2012</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: since, benchmark, national; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Abstract. Implementation of the Nitrates Directive (NiD) and its environmental impacts were compared for member states in the Northwest of the European Union (Ireland, UK, Denmark, The Netherlands, Belgium, Northern France and Germany). The main sources of data were national reports for the third reporting period for the NiD (2004–2007) and results of the MITERRA-EUROPE model. Implementation of the NiD in the considered member states is fairly comparable regarding restrictions for where and when to apply fertilizer and manure, but very different regarding application limits for N fertilization. Issues of concern and improvement of the implementation of the NiD are accounting for the fertilizer value of nitrogen in manure, and relating application limits for total nitrogen (N) to potential crop yield and N removal. The most significant environmental effect of the implementation of the NiD since 1995 is a major contribution to the decrease of the soil N balance (N surplus), particularly in Belgium, Denmark, Ireland, The Netherlands and the UK. This decrease is accompanied by a modest decrease of nitrate concentrations since 2000 in fresh surface waters in most countries. This decrease is less prominent for groundwater in view of delayed response of nitrate in deep aquifers. In spite of improved fertilization practices, the southeast of The Netherlands, the Flemish Region and Brittany remain to be regions of major concern in view of a combination of a high nitrogen surplus, high leaching fractions to groundwater and tenacious exceedance of the water quality standards. On average the gross N balance in 2008 for the seven member states in EUROSTAT and in national reports was about 20 kg N ha−1 lower than by MITERRA. The major cause is higher estimates of N removal in national reports which can amount to more than 50kg N ha−1. Differences between procedures in member states to assess nitrogen balances and water quality and a lack of cross boundary policy evaluations are handicaps when benchmarking the effectiveness of the NiD. This provides a challenge for the European Commission and its member states as the NiD remains an important piece of legislation for protecting drinking water quality in regions with many private or small public production facilities and controlling aquatic eutrophication from agricultural sources.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>all since benchmark order Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>link-769053cdc3e4d7fc42</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Editorial: Critical perspectives in times of uncertainty</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1108/dpm-08-2025-435</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, environment, climate; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>This special issue centers diverse voices of scholars, practitioners and community leaders and highlights different methods of communicating these critical approaches within the field of disasters, hazards and risks. Many scholars have reminded us that “critical” scholarship and approaches are not necessarily new. This special issue serves as a testament to scholars, activists and practitioners who have sought to employ critical approaches to their work and its continuous development. Just in the past couple of years, the global community has witnessed and experienced the dire effects of climate change, the COVID-19 pandemic, the development of the Ukraine–Russia war, the genocide in Gaza and, most recently, the involvement of the United States in the developing conflict between Iran and Israel. These shifting realities, each with endless and complex possibilities, compel people to respond. Whether these events are labeled a crisis, an emergency, a disaster or a catastrophe, when humanity is threatened, when the constitution of acceptable risk reaches its threshold, people are called to respond. This special issue is dedicated to the recognition that critical perspectives evolve in times of uncertainty.In the face of uncertainty, vulnerable spaces become sites of contestation as people resist and adapt to satisfy their needs in a changing environment. Yet, change itself does not always or necessarily yield to transformation. Critical perspectives and approaches offer the potential to reveal the unnatural systemic forces that dictate people's choices. Structural violence, embedded within and perpetuated by social institutions, shapes the constitution and outcomes of disasters. Critical theories uncover root causes, not solely the symptoms. That is to say, as Jacobs (2019) has argued, we must start with the isms – racism, sexism, classism and beyond – instead of the social categories formed as byproducts. “Othered knowledge,” community-originated, -driven and -centered approaches and participatory, creative and reflexive research methodologies allow us to do so. When Anderson and Dynes wrote of the May Movement in Curacao in Los Angeles (1975), instead of asking, “Why do people riot?” they asked, “How do people respond to injustice when constrained daily by institutions embedded with oppression?” They made clear that the riots existed within a social context and could only be interpreted as such. Following in those footsteps, that is the path forward: research that brings to the center those on the fringes of society and honors that they, too, have stories to tell. The significance of these approaches pushes the epistemology of disasters forward as we envision what emancipation and justice look like for marginalized and underserved communities.The multiplicity of voices amplified in this special issue – by way of the guest editors, authors and the studied communities impacted by the shifting climates – teaches us that the development of critical approaches bridges us across geographic and disciplinary lines. The threads of inquiry must be global in nature, borne in groups of scholars, advocates, artists, makers, community members, practitioners, professionals and beyond. We must expand our circles to include holders of knowledge along a spectrum of socio-political positionalities and thereby pave the way for ingenuity and innovation in how we understand, question and respond in times of uncertainty.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>link-69cefa5e3fff0ef0a6</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>A Critical Review of the 2025 RSHE Guidance and Alternative Approach Framed in Safe Uncertainty</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/chso.70004</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, concern; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>ABSTRACT This policy review critically examines the English government's 2025 statutory guidance on Relationships Education, Relationship and Sex Education and Health Education (RSHE), analysing its educational assumptions, strengths and limitations through the lens of safe uncertainty. While the updated guidance somewhat reinstates key inclusive elements and promotes social and emotional literacy, it continues to position RSHE as a risk domain requiring tight control and cautious delivery. This review highlights areas of concern including contradictions in the guidance's treatment of digital image sharing, the approach to gender and the conditional framing of children's rights and participation. Drawing on the concept of safe uncertainty, we advocate a more coherent rights‐based framework, clearer policy direction and sustained investment in teacher support and infrastructure. We call for RSHE policy and practice to move beyond compliance and certainty, and instead build relational, reflective and dialogic spaces where students can engage meaningfully with the ethical and social dimensions of their lives. In doing so, RSHE can fulfil its broader educational promise in preventing harm and supporting the flourishing of students as relational and sexual citizens.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>link-ca09699634c3a41af5</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>A Critical Review of the 2025 RSHE Guidance and Alternative Approach Framed in Safe Uncertainty</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/chso.13012</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, concern; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>ABSTRACT This policy review critically examines the English government's 2025 statutory guidance on Relationships Education, Relationship and Sex Education and Health Education (RSHE), analysing its educational assumptions, strengths and limitations through the lens of safe uncertainty. While the updated guidance somewhat reinstates key inclusive elements and promotes social and emotional literacy, it continues to position RSHE as a risk domain requiring tight control and cautious delivery. This review highlights areas of concern including contradictions in the guidance's treatment of digital image sharing, the approach to gender and the conditional framing of children's rights and participation. Drawing on the concept of safe uncertainty, we advocate a more coherent rights‐based framework, clearer policy direction and sustained investment in teacher support and infrastructure. We call for RSHE policy and practice to move beyond compliance and certainty, and instead build relational, reflective and dialogic spaces where students can engage meaningfully with the ethical and social dimensions of their lives. In doing so, RSHE can fulfil its broader educational promise in preventing harm and supporting the flourishing of students as relational and sexual citizens.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>link-0f631e227503570ad6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lithium: critical, or not so critical?</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1144/geoenergy2023-045</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, current, overall; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Some metals necessary to deliver renewable energy are considered critical. Metal criticality is a major factor in achieving energy decarbonization, leading to efforts to make metals uncritical . Among the most critical is lithium which, like many critical metals, represents a small-scale market experiencing significant demand increase causing price and supply volatility, thereby hindering necessary transformative investment. Global lithium demand is soaring, with current supply now dominated by pegmatite-sourced lithium hydroxide. Clay extraction has yet to be industrially proven, thus there remains uncertainty from where and in what quantity future lithium supply will come, and whether lithium remains critical, however geoscience research is best focused on pegmatite and clay-sourced lithium to improve discovery and extraction. Of five lithium criticality scenarios (business as usual; clays onstream; everything plus recycling; shift away from lithium; black swan event), only two project a longer-term criticality reduction. However, few metals will be critical over the very long term as techno-economic and environmental, social, and governance challenges can be overcome and/or metal demand will be structurally adjusted by substitution. Although criticality may be a short to medium term barrier to the energy transition, effective research and overall market forces will reduce the majority of mineral criticality over the longer term. Thematic collection: This article is part of The energy-critical metals for a low carbon transition collection available at: https://www.lyellcollection.org/topic/collections/critical-metals</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>link-aa63ed1f61411769a3</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Critical Disposition Towards the Uncertainty of Events – Aspirations, Endeavour and Plans of Future Teachers</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17951/j.2023.36.4.19-35</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, critical; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Functioning in a situation of change and uncertainty has become an important determinant of contemporary teachers’ condition. The article assumes the essential role of critical dispositions (especially the so-called critical orientation): courage, reflectiveness, rationality, reality, scepticism, progressive engagement, intellectual submissiveness, principle, independence, flexibility and tolerance for ambiguity, mindfulness and openness, and curiosity as mediators in the purchase of critical rationality, as well as in coping with non-obviousness of events. The qualitative analysis of essays’ content for 66 future teachers of preschool and early school education was concentrated on decoding their aspirations and plans within the process of creating the status change and on revealing by narrators their critical dispositions. Adopting a qualitative text analysis strategy allowed for capturing an in-depth, contextual view of the examined problem. Analysis of the content and form of written statements indicate significant negligence of this development area for students, which may be a derivative of macro-social, educational and personal barriers. Within the light of elaborated research material, it seems to be a matter of great importance to promote the value of critical dispositions as well as to create and apply programmes developing them during the process of preparing future teachers for their professional careers in the situation of cultural and technological changes.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>link-2ad87fc993f65687e2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>The So-Called Creative PhD</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.31182/cubic.2024.7.75</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, concern, particularly; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>This paper constitutes a short reflection on architectural research and knowledge production in the tertiary education sector, with particular reference to the establishment of a ‘creative’ PhD degree in South Africa. It arises from the growing interest in and pressure for the establishment of a practice-led (architecture) PhD. This interest has emerged predominantly from within performance-based disciplines whose application takes the form of practice-based and professionally produced work. In reflecting on the nature of PhDs and on various ‘alternative’ approaches, I conclude that the conventional PhD implicitly infers creativity and is entirely capable of sponsoring any performance-based PhD enquiry – particularly within practice-based disciplines in which theory and method have been critically identified to support appropriate investigations. Concern is therefore raised regarding the emerging predominance of an author’s self-evaluation of their own ‘creative’ production at the level of a PhD enquiry. On the one hand, knowledge remains largely embedded within the performance/production, and on the other hand, the subjectivity intrinsic to autoethnographic studies is noted for its privileging of the self over the other, and its method often follows what may be termed a self-fulfilling prophesy.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>link-357bf104c803f2641f</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>A Critical Comment on T.S. Kuhn’s Views about the So-called Copernican Revolution and Several Current Prejudices – Barriers in Scientific Communities</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4467/2543702xshs.23.004.17695</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, critical, current, about; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>The article is a case study on the views of the famous T.S. Kuhn about the so-called Copernican revolution. Generally, Kuhn is presented as a very successful historian and philosopher of science: an author of world bestsellers. The division among his supporters, i.e. about so-called left-wing and right-wing Kuhnians, is recalled, and the fact that Kuhn himself vehemently dissociated from a large proportion of his adherents. It is also noted here, that in the last 30 years, in addition to abundant hagiographic literature on T. S. Kuhn, there have also been a few critical studies of Kuhn’s achievements. The rest of the article presents the author’s critical analysis of Kuhn’s views on the so-called Copernican Revolution, which formed the basis of Kuhn’s scheme of scientific development presented in The Structure of Scientific Revolutions (1962); i.e. the world’s most famous monograph in social sciences and humanities so far. The criticism encompasses a genesis, content and reception of Kuhn’s views and the development of his interpretations. The analysis is carried out by the means of methodology of historical sciences and a scientific method, which the author describes as the hypothetico-deductive method of correspondence thinking. The criticism is based on the author’s current publications (developed here further on), which were sadly unnoticed by the researchers, although presented in the world center for the Copernican research, and are available on the Internet freely. This fact leads the author to the assumption that international Kuhnian research is underdeveloped seriously and that strong prejudices – barriers may exist in scientific circles, such as, e.g., primacy of number of citations (and other bibliometric indicators) over content analysis, the Matthew effect, the effect of alleged and actual scientific centers and peripheries, some mental remnants of the Cold War, as well as underdevelopment of scientific communication.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>link-f8fbf725b23a959fc7</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Knowledge, Integration and Scope of Deepfakes in Arts Education: The Development of Critical Thinking in Postgraduate Students in Primary Education and Master’s Degree in Secondary Education</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/educsci13111073</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, critical, current; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>If the appearance of digital images does not coincide with what they look like when they are presented as authentic photos or videos, we must reflect on concepts such as mimesis, truth, Artificial Intelligence and impersonation, something that is currently gaining prominence in the education of teachers and university professors. The current study presents the results of a research focused on the scope and knowledge of the so-called ‘deepfake images’ by the university student body of the Visual and Plastic Education subject, in the Graduate Certificate in Primary Education, and the student body of the Activity Design subject, in the master’s degree in Secondary Education—Specialty in Drawing, in the subject of Activity Design, University of Zaragoza. To do so, a quasi-experimental design with qualitative methodology was used, in which of 100 students participated. As a data collection strategy, reports were used, based on semi-structured questions, for the analysis of the development of critical thinking. The achieved results allow us to verify that deepfakes put forward an innovation in the study by university classrooms. The use of these deepfake representations is a novel issue that generates some moral and ethical controversy due to the different uses it can have, where the age of the interpreter is a differentiating factor for the knowledge and the possibilities that these imaginaries present. Therefore, it is a work area belonging to the field of artistic education on which little exploration and research has been conducted. Based on the obtained results, we conclude that there is currently a better awareness on the part of artistic education, and of education itself, in general terms, regarding the knowledge by the students, the relevance of its use, and the possibilities of these technological tools, both in their creative aspect and their misinformative ones.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>link-91fcccbebaa3479522</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Supplying Critical Materials in a Time of Uncertainty</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.31410/limen.2022.315</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, critical, climate; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>The high demand for energy, food, and raw materials is putting an enormous strain on ecosystems around the planet. Therefore, the indus­trial strategies of many countries rely on the so-called green plan and tran­sition toward climate neutrality. In this sense, the need for new materials greatly exceeds the existing possibilities and capacities. Critical materials are raw materials that have great economic importance and for which there is a probability of shortage. Since the world is facing more and more serious problems, whether it is an economic crisis, a pandemic, or war conflicts, the general character of the present and, one would say, future time, is uncer­tain. Prediction of uncertainty is a task that decision-makers must keep in mind when deciding on the present and the future, not only of economies but of entire ecosystems and populations as a whole. The paper shows how critical materials affect development and growth, and the fulfillment of en­vironmental requirements, using examples from various industries.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>link-a681d4beb9de069497</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Truth and uncertainty. A critical discussion of the error concept versus the uncertainty concept</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5194/amt-15-1145-2022</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, uncertainties, found; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Abstract. Contrary to the claims put forward in “Evaluation of measurement data – Guide to the expression of uncertainty in measurement”, issued by the Joint Committee for Guides in Metrology, the error concept and the uncertainty concept are the same. Arguments in favour of the contrary have been analyzed and were found not compelling. Neither was any evidence presented in this document that “errors” and “uncertainties” define a different relation between the measured and the true value of the variable of interest, nor does this document refer to a Bayesian account of uncertainty beyond the mere endorsement of a degree-of-belief-type conception of probability.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>link-8533073f0f18308a8c</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Last Call for 1.5 Degrees:</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.21552/cclr/2022/4/4</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: degrees, climate; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>The twenty-seventh Conference of the Parties (COP27) to the United Nations Framework Convention on Climate Change (UNFCCC) in Sharm el-Sheikh made history by for the first time ever discussing and ultimately even agreeing to establish a fund to address loss and damage caused by climate change. However, the conference did little to limit the occurrence of loss and damage in the first place by containing the extent of climate change. This article discusses the conference's outcomes in the areas of mitigation and adaptation, loss and damage, the Global Stocktake, cooperation under Article 6 of the Paris Agreement, climate finance, and gender-responsiveness. While modest progress can be observed, it is too slow to actually achieve the objectives of the Paris Agreement. This pace is leading many, not least the most vulnerable countries, to search for parallel arenas of cooperation.</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>link-258f5827158ed3d7fb</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Responsible prediction under critical uncertainty: an epistemic analysis of neuroprognostic innovation practices after cardiac arrest</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3990/1.9789036552349</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, uncertainties, preferences; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Preferences for prognostication of coma after cardiac arrest: the Dutch societal perspective on physiological and normative futility "Deciding whether and when to use a new tool can be one of the most difficult challenges in clinical practice."Kenneth W. Goodman -Ethics, Medicine, and Information Technology "The only certainty, whether spoken or not, is that the doctors, nurses, and technicians are fighting not only death, but their own uncertainties as well.In most resuscitations, those uncertainties can be narrowed down to two main questions: Are we doing the right things?and, Should we be doing anything at all?" Sherwin B. Nuland -How We Die … to my mother and the one we lost Unfortunately, a degree of uncertainty always remains in prognosis (Smith et al. 2013) and neuroprognostication after cardiac arrest is especially precarious.Predicting how much damage the brain suffered is very difficult and the implications for the patient' s mental and physical recovery are only really apparent after the patient regains consciousness-if they regain consciousness at all.Better prognostic tools are needed but each tool has its own epistemological and ethical shortcomings.With this research, I sought to identify and analyze these shortcomings so that they can adequately be addressed.This would help ensure responsible innovation of the neuroprognostic practice for patients in coma after cardiac arrest. 1 Brainstem reflexes can be tested through either clinical examination of pupillary and corneal reflexes or through a somatosensory evoked potentials test (SSEP-test) checking cortical responses.2 Prognostic tools such as electroencephalography (EEG); serum biomarkers like Neuron Specific Enolase (NSE); and neuroimaging such as Computerized Tomography (CT) and Magnetic Resonance Imaging (MRI) including novel sequences such as Diffusion Tensor Imaging (DTI).3 Meaning that corneal and pupillary reflexes or cortical responses are still present. Science and Technology Studies &amp; Philosophy of TechnologyMy focus on technology development in practices quickly resulted in a fascination for social constructivism and what different approaches actually do.Similarly, as put forward in science and technology studies (STS) (Latour 1996, Felt et al. 2016) and philosophy of technology (Verbeek 2005(Verbeek , 2006)), technology is not an independent, neutral device that only performs the activity it was designed to perform.Instead, Conceptual AnalysisIn the theoretical approach section above, I emphasized the value of combining empirical work with more theory-oriented, analytic philosophy.The empirical data collected shows immense complexity and appropriately responding to the concerns raised requires, in the first place, a better understanding of them.The Chapter 1Liminal innovation practices: questioning three common assumptions in responsible innovation</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>link-bd49971b7863541e1a</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Uncertainty and the politics of transformation</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4324/9781003023845-1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, uncertainties, about, climate; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>This introductory chapter asks why the idea of uncertainty is so important to politics today. To explore this, the chapter reviews the diverse contributions to the book on themes ranging from finance and banking to insurance to technology regulation, to critical infrastructures, infectious disease responses, climate change, natural disasters, migration, crime and security and spirituality and religion. Across this wide field, the chapter argues that uncertainties are constructions of knowledge, materiality, experience, embodiment and practice; and acknowledging this means challenging singular notions of modernity and progress. Given these multiple dimensions of uncertainty, there can be no singular assumptions about ‘the future’. Instead, the directions taken in pursuit of sustainability and development depend on social, and deeply political, choices. Discussing challenges to singular versions of ‘modernity’ through embracing uncertainty and ignorance and respecting difference, the chapter explores necessary shifts from ‘calculative control’ towards ‘creative care’. Examining how uncertainties are experienced and futures constructed in contexts of marginalisation and precarity, the chapter calls for a new collective, convivial politics of responsibility. The chapter concludes by showing how, in a time of crisis for democratic struggle, embracing uncertainty and challenging control raise hopes of much-needed progressive transformation.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>link-a075d1b1f6b5613e39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Dealing with Uncertainty in pWCET Estimations</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3396234</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, uncertainties, environment; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>The problem of estimating a tight and safe Worst-Case Execution Time (WCET), needed for certification in safety-critical environment, is a challenging problem for modern embedded systems. A possible solution proposed in past years is to exploit statistical tools to obtain a probability distribution of the WCET. These probabilistic real-time analyses for WCET are, however, subject to errors, even when all the applicability hypotheses are satisfied and verified. This is caused by the uncertainties of the probabilistic-WCET distribution estimator. This article aims at improving the measurement-based probabilistic timing analysis approach providing some techniques to analyze and deal with such uncertainties. The so-called region of acceptance model based on state-of-the-art statistical test procedures is defined over the distribution space parameters. From this model, a set of strategies is derived and discussed to provide the methodology to deal with the trade-off safety/tightness of the WCET estimation. These techniques are then tested over real datasets, including industrial safety-critical applications, to show the increased value of using the proposed approach in probabilistic WCET analyses.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>link-a089e07690b319f5c0</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>The Call for Critical Multiculturalism</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.32396/usurj.v6i3.469</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, current; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>This review looks at the current literature within Indigenous and newcomer relationships under the contemporary Canadian multicultural framework. The ever-increasing prevalence of Indigenous social movements and instances of cross-continental migration position the topic at the forefront of social policy since the inception of multiculturalism as a governmental policy in the 1970s. Traditional multiculturalism positions newcomer populations in support of the ongoing formation of the Canadian settler state due to factors of misinformation and hierarchized measures of a newcomer group’s ability to successfully integrate. Considerable efforts are required to diminish the discursive gap between the historically oppressed social groups. The literature posits structural change within the theory of critical multiculturalism to support nuanced binationalism and increased instances of social interaction. These efforts are required to facilitate a potentially transformative relationship between each group in relation to the greater multicultural project.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>link-74a62326b39a895032</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Analyzing the Degree of Consensus in Current Academic Literature on Critical Pedagogy</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.33178/scenario.13.2.6</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, current, related; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Critical Pedagogy is a philosophy and approach to education which has influenced theory and practice for almost 50 years, most recently in the fields of Applied Drama and performative pedagogy.However, what exactly is understood by Critical Pedagogy in the 21 st century is unclear, and whether its roots still align with the ideas and practices of its progenitor Paulo Freire is uncertain.Therefore, this systematic review of literature aims to explore the interpretations of Critical Pedagogy presented in 100 peer-reviewed papers published in recent times.After identifying frequently emergent themes in the selected literature, which are associated with the work of Freire, this paper examines the degree of consensus around Critical Pedagogy's transformative aim, its associated democratic classroom approaches, and the concepts of conscientization and praxis.Through this analysis, the review distinguishes a number of peripheral discussions that are related to a modern/postmodern debate within the literature.This paper concludes by asserting that there are more points of convergence than of divergence in the various interpretations of Critical Pedagogy available in the articles surveyed.We suggest that the current branching out of Critical Pedagogy has not been rendered devoid of core meanings as an educational tradition, one which holds considerable potential for the field of Applied Drama, and for other forms of performative education.</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>link-782fdcbba3e4ae163b</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>What Is so Positive about Positive Animal Welfare?—A Critical Review of the Literature</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ani9100783</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, current, about; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>It is claimed that positive animal welfare (PAW) developed over the last decade in reaction to animal welfare focusing too much on avoiding negatives. However, it remains unclear what PAW adds to the animal welfare literature and to what extent its ideas are new. Through a critical review of the PAW literature, we aim to separate different aspects of PAW and situate it in relation to the traditional animal welfare literature. We find that the core PAW literature is small (n = 10 papers) but links to wider areas of current research interest. The PAW literature is defined by four features: (1) positive emotions which is arguably the most widely acknowledged; (2) positive affective engagement which serves to functionally link positive emotions to goal-directed behavior; (3) quality of life which serves to situate PAW within the context of finding the right balance of positives over negatives; (4) happiness which brings a full life perspective to PAW. While the two first points are already part of welfare research going back decades, the two latter points could be linked to more recent research agendas concerning aggregation and how specific events may affect the ability of animals to make the best of their lives.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>link-788b94bf20c451855f</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Degree studies in Information and Documentation in Spain. From their antecedents to the current situation: A critical view</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.6084/m9.figshare.7367444</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, critical, current; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Abstract University studies in Documentation Sciences in Spain go back to the 1980s with the implementation of the University degree in Librarianship and Documentation. This was followed later by the Licentiate degree (roughly equivalent to the M.A. degree) and Doctorate courses in Documentation. The process of adapting Spain’s university system to the European Space for Higher Education resulted in the appearance of Bachelors’ degree courses in Information and Documentation. This study presents the origin of these degree courses, their development and current situation, and their antecedents, without which, would be impossible to understand the current reality. The so-called “crisis of Documentation studies in Spain” is analyzed, together with the need to rethink the country’s university studies.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>link-5ddbdb9bc4233a901d</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Education in Times of Uncertainty. Uncertainty in Education. A Critical Approach</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2756167973</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, about, environment; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>The essential aspects of today’s reality are determined by the dominant variant of socioeconomic system, which is built around the concept of development (whether in terms of narrower – growth). The result of the dominance of neo-liberal vision of the economy become socio-economic inequalities, precarious conditions of employment, encompassing the uncertainty of human existence, as well as the real limitations of civil rights of particular social categories (denizens) and the devastation of the environment. In the face of these phenomena it seems reasonable to pose questions about the limits of the concept of economic development from the perspective of the social consequences, or more broadly – about the direction we are heading, or in other words – “progress” of civilization. These issues will be analyzed in the context of education, ie. at every level of the education process. Particular attention will be placed on changes in education since the late 80s of the last century.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>link-0d3c2dae5c42963825</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>The call of the not-so-mild</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1242/jeb.147173</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: found, current, about; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Flies and many other insects show an inordinate fondness for feces. They oviposit there and occasionally visit animal excrement to dine. But it turns out that not all poop is created equal, and flies are rather discerning in their choice of fecal targets. While some piles of feces are highly attractive, the fragrant bouquet of displeasing targets is met with extreme prejudice. Now, in a recent paper in Current Biology, Suzan Mansourian and her collaborators from the University of Lund in Sweden show why.Large mammals can be partitioned in many different ways, and one of the larger divisions concerns diet and the traits that go with it. Beyond the obvious differences between carnivores and herbivores (teeth, claws, etc.), these animals also differ in the length and structure of their guts. Deeper still, they maintain dramatically different microbiomes to aid in digestion. And it is this latter difference, according to Mansourian and colleagues, that matters most to flies.When the research team offered flies a choice between carnivore and herbivore feces for oviposition, they found marked differences. While flies were attracted or indifferent to herbivore feces, they were positively repulsed by carnivore waste. Moreover, their aversion disappeared when the assays were repeated with flies lacking a specific type of olfactory neuron, making it clear that their choice was caused by an odor preference.To determine why one animal's waste smelled better than the other, the team subjected the fecal samples to detailed chemical analysis. It was little surprise that the feces contained a complex brew of smells. However, while many chemicals distinguished feces in general from, say, a bottle of lager or a ripe banana, only very few were directly tied to the animal's diet. Phenol, in particular, was abundant in carnivore feces but entirely absent from the excrement of herbivores. More important, the team determined that this chemical alone was sufficient to drive fly behaviors. When normally acceptable giraffe feces was spiked with phenol, the flies turned up their noses and oviposited elsewhere. And when flies were forced to oviposit on phenol-laced food, they layed nearly five times fewer eggs.But why should flies avoid phenol? To determine this, the team analyzed the bacteria found in herbivore and carnivore guts. The most interesting differences, it turned out, were for bacterial species that are pathogenic for insects. And these bacterial species, not coincidentally, make phenol. But don't trust just flies. When the team offered dung beetles, bonafide poo experts, a choice between herbivore and carnivore feces, these too chose the former. Thus, aversion to phenol cues appears to be widespread.The neatest aspects of these results are the diverse links between chemical ecology, neurobiology and animal behavior. But these same aspects also highlight the loose threads that offer some promising avenues for future research. Among these, why are frugivorous fruit flies so discriminating about feces? How reliable a cue is phenol for the risk of fly disease? Does phenol concentration scale with the true risk to flies? Are the phenol producers really pathogenic? I hope the authors can address at least some of these intriguing questions in the future.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>link-eb5a48fc5eb2f38656</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Current debates in urban theory: A critical assessment</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/0042098016634002</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, current, about; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Urban studies today is marked by many active debates. In an earlier paper, we addressed some of these debates by proposing a foundational concept of urbanisation and urban form as a way of identifying a common language for urban research. In the present paper we provide a brief recapitulation of that framework. We then use this preliminary material as background to a critique of three currently influential versions of urban analysis, namely, postcolonial urban theory, assemblage theoretic approaches and planetary urbanism. We evaluate each of these versions in turn and find them seriously wanting as statements about urban realities. We criticise (a) postcolonial urban theory for its particularism and its insistence on the provincialisation of knowledge, (b) assemblage theoretic approaches for their indeterminacy and eclecticism and (c) planetary urbanism for its radical devaluation of the forces of agglomeration and nodality in urban-economic geography.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>link-6587d3794b17718545</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Critical Zone Research and Observatories: Current Status and Future Perspectives</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2136/vzj2016.06.0050</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, current, environment; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Core Ideas Major findings in CZ science have been achieved in the past several years, especially from CZOs. “Deep” science—deep time, deep depth, and deep coupling—is used to synthesize recent CZ studies. Major opportunities include developing a global CZO network and a library of CZ models and databases. The Critical Zone (CZ) is the thin layer of the Earth's terrestrial surface and near‐surface environment that ranges from the top of the vegetation canopy to the bottom of the weathering zone and plays fundamental roles in sustaining life and humanity. The past few years have seen a number of Critical Zone Observatories (CZOs) being developed following the first CZOs established in the United States in 2007. This update summarizes major research findings in CZ science achieved in the past 5 yr or so (2011–2016), especially those obtained from recognized CZOs. A conceptual framework of “deep” science—deep time, deep depth, and deep coupling—is used to synthesize recent CZ studies across a broad range of spatial and temporal scales. This “deep” science concept emphasizes the integration of Earth surface processes that underlies the contributions of CZ science to terrestrial environmental research. We identify some main knowledge gaps and major opportunities to advance the frontiers of CZ science. We advocate that the CZ scientific community work toward a global network of CZOs to link sites, people, ideas, data, models, and tools. We hope that this update can stimulate continuous scientific advancement and practical applications of CZ science worldwide.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>so-called critical degrees current</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>link-a445008664fd467ae6</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Management strategies in hospitals: scenario planning</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3205/iprs000065</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: so-called, critical, uncertainties, environment; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Instead of waiting for challenges to confront hospital management, doctors and managers should act in advance to optimize and sustain value-based health. This work highlights the importance of scenario planning in hospitals, proposes an elaborated definition of the stakeholders of a hospital and defines the influence factors to which hospitals are exposed to. METHODOLOGY: Based on literature analysis as well as on personal interviews with stakeholders we propose an elaborated definition of stakeholders and designed a questionnaire that integrated the following influence factors, which have relevant impact on hospital management: political/legal, economic, social, technological and environmental forces. These influence factors are examined to develop the so-called critical uncertainties. Thorough identification of uncertainties was based on a "Stakeholder Feedback". RESULTS: Two key uncertainties were identified and considered in this study: the development of workload for the medical staff the profit oriented performance of the medical staff. According to the developed scenarios, complementary education of the medical staff as well as of non-medical top executives and managers of hospitals was the recommended core strategy. Complementary scenario-specific strategic options should be considered whenever needed to optimize dealing with a specific future development of the health care environment. CONCLUSION: Strategic planning in hospitals is essential to ensure sustainable success. It considers multiple situations and integrates internal and external insights and perspectives in addition to identifying weak signals and "blind spots". This flows into a sound planning for multiple strategic options. It is a state of the art tool that allows dealing with the increasing challenges facing hospital management.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>link-c9ceee1ba8b64b9083</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>claim-867e108783aed073</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>These so-called critical uncertainties were found to be degrees to which: (i) current patterns of globalization will continue, or be replaced by regionalism, and (ii) concern about the environment, particularly climate change, related policy initiatives and customer preferences, will materialize. The overall future of the Swedish solid wood-product industry looks bright, irrespective of which of the four possible futures occurs, provided it accommodates the expected growth in demand for factory-made, energy-efficient construction components.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Uncertainty in the availability of natural resources: Fossil fuels, critical metals and biomass</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.enpol.2015.02.031</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: critical, uncertainties; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Energy policies are strongly influenced by resource availability and recoverability estimates. Yet these estimates are often highly uncertain, frequently incommensurable, and regularly contested. This paper explores how the uncertainties surrounding estimates of the availability of fossil fuels, biomass and critical metals are conceptualised and communicated. The contention is that a better understanding of the uncertainties surrounding resource estimates for both conventional and renewable energy resources can contribute to more effective policy decision making in the long term. Two complementary approaches for framing uncertainty are considered in detail: a descriptive typology of uncertainties and a framework that conceptualises uncertainty as alternative states of incomplete knowledge. Both have the potential to be useful analytical and communication tools. For the three resource types considered here we find that data limitations, inconsistent definitions and the use of incommensurable methodologies present a pervasive problem that impedes comparison. Many aspects of resource uncertainty are also not commonly captured in the conventional resource classification schemes. This highlights the need for considerable care when developing and comparing aggregate resource estimates and when using these to inform strategic energy policy decisions.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>so-called critical uncertainties</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>link-26862e2c1c531dda06</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>European strategic antinomy</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.polgeo.2026.103616</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: strategic, key, uncertainties; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Over the last decade, “strategic autonomy” has emerged as a key geonarrative in debates on EUrope's relation to the world. Initially focused more narrowly on matters of security and defence, it is now being applied to a much wider set of issues. Confronted with the rise of non-Western powers, uncertainties about the future of transatlantic relations, and a wide-spread sense that one-sided dependencies must be reduced, the concept of strategic autonomy is the lens through which EUrope tries to address a broad array of geopolitical and geoeconomic challenges. Yet, Europe struggles to come to terms with the “geo” in geopolitics and geoeconomic. The article advances the argument that these difficulties are an effect of EUrope's self-description and self-observation in universal terms: Obviously, EUrope recognizes the presence of other players on the international scene. But to the extent that European modernity is seen as universal rather than merely European the organization of political space in terms of difference (e.g. geopolitical or geoeconomic competition) runs into contradictions. EUrope envisions itself both as a province among provinces (competing with China and increasingly also the US) and it retains the ambition to singularly represent the world. In a nutshell, casting itself in universal terms, EUrope struggles to process and acknowledge difference, and faced with difference tends to talk to itself about itself. The article demonstrates that this is not due to a lack of strategic resolve but rather the effect of antinomies at the core of EUropean geonarrative production.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>link-6af62d7d0c17066466</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>De-Europeanization or Strategic Recalibration? Irish Neutrality, NATO Partnership, and Contested Security Identity in a Geopolitical Europe</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.18186394</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: argues, insights, strategic, culture; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Abstract This paper examines the theoretical dimensions of Irish neutrality within the context of deepening European security integration and expanding NATO partnership arrangements. Drawing upon Europeanization theory and constructivist approaches to security identity formation, the analysis interrogates whether Ireland's evolving security posture represents a fundamental de-Europeanization of its foreign policy orientation or constitutes a strategic recalibration reflecting adaptive responses to geopolitical transformation. The study extends theoretical frameworks concerning small state behavior, normative contestation, and identity politics within security governance structures. By synthesizing insights from Europeanization scholarship, socialization theory, and critical security studies, the paper develops a conceptual framework for understanding how Ireland navigates the tension between historical neutrality commitments and contemporary security interdependence (Tonra, 2007). The analysis demonstrates that Irish security identity remains fundamentally contested, marked by competing narratives of exceptionalism, pragmatic Atlanticism, and selective multilateralism. Rather than representing linear progression toward either full European defense integration or isolation, Irish policy exhibits characteristics of what may be termed "strategic ambiguity"—a deliberate maintenance of flexibility that simultaneously preserves symbolic neutrality while deepening operational military cooperation through NATO's Partnership for Peace and EU Common Security and Defence Policy frameworks. The paper contributes to theoretical debates concerning the limits of Europeanization in high politics domains, the resilience of national security cultures, and the conditions under which small states maintain distinctive foreign policy identities within constraining institutional environments. Ultimately, the study argues that Ireland's security trajectory reflects neither wholesale de-Europeanization nor complete integration, but rather represents an emergent hybrid model wherein traditional neutrality undergoes continuous renegotiation without resolution (Tonra, 2001, 2006). Keywords: Irish neutrality, Europeanization, NATO Partnership for Peace, security identity, CSDP, small states, strategic culture</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>link-ad1cc14c65bf105d1f</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>European manual on strategic culture</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7163482322</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: strategic, culture, particularly; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Welcome to the manual of strategic culture! We are pleased that you took the time to familiarize yourself with its contents and hope that you’ll see the benefits of this in your daily work. As the authors, we firmly believe that the capacity to identify and assess the characteristics and potential implications of strategic culture on national security behavior constitutes a core professional qualification of contemporary military officers, defense policy experts and decision-makers. Beyond mere awareness of the cultural dimensions of security, the ability to operate effectively within a strategic cultural environment is rapidly becoming an essential component of professional expertise in the field of security and defense policy. Strategic culture is fundamentally something that needs to be experienced, either through engagement in the field, reflection or rigorous analysis. An interest and curiosity toward how strategic views may differ is a good starting point. Conversely, the realization that we tend to think we are special in this regard may guide us out of our strategic cultural “blind spots” and biases. This concise manual is intended to help readers understand and navigate the complex socio-political environment shaped by strategic culture, particularly within European security and defense. It aims to illustrate how strategic culture can affect the ways in which professionals working in the field of strategy –such as within the EU’s Common Security and Defense Policy – identify shared perspectives and differences, address challenges arising from diverse strategic cultures, and foster common ground across varying issues.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>link-355469ea325c73818c</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>European Strategic Culture at a Crossroads</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4324/9781032636566</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: strategic, culture, key; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>This book examines European strategic culture at both national and supranational levels. Focusing on elite perceptions extracted from official discourses, this book empirically analyses how the European Union and its member states perceive the important dimensions and their perceptual changes in the foreign security and defence realm and explores their convergence/divergence. It also discusses the prospects for the emergence of a European strategic culture in the context of the Russia–Ukraine war, concluding that, whilst the war has given a boost to Europe’s thinking and approach with respect to security and defence, which may lead to further integration, there had already been convergence in strategic culture between the member states and between them and the EU, even before the war. This book will be of key interest to scholars and students of European foreign, security, and defence policy, and more broadly, to those of European studies, international relations, security studies, and foreign policy.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>link-bef5d1ae79009b45e8</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Mapping the European Negotiation Landscape: Insights from the 2025 European Negotiation Conference</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.70714/x3jghe28</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, strategic, internal; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>This paper examines how geopolitical disruption is reshaping the European negotiation landscape. Against the backdrop of Russia’s invasion of Ukraine, pressure on the rules-based international order, and growing political polarisation, it explores how practitioners perceive current changes in Europe and the European Union. The study draws on 19 semi-structured expert interviews conducted at the 2025 European Negotiation Conference with practitioners, researchers, and educators. Using abductive qualitative content analysis, it focuses on two interconnected levels: macro-level geopolitical and normative shifts, and meso-level institutional and organisational dynamics. The findings indicate that the EU’s normative and value-based framework remains a strategic asset in an increasingly transactional and authoritarian environment, supporting its position as a credible long-term partner. Yet this advantage depends on internal consistency: gaps between proclaimed norms and operational outcomes weaken credibility, trust, and bargaining power. The analysis also shows that the EU’s consensus-oriented, multi-level governance architecture generates legitimacy but, under crisis-driven time pressure, often produces delay and incrementalism.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>argues insights particularly suited Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>link-6ea8d18d1efaecf30b</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DECONSTRUCTING SDG PERFORMANCE FOR STRATEGIC INSIGHT: QUANTITATIVE INSIGHTS FROM TÜRKİYE AND EUROPEAN COUNTRIES</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.15544/mts.2025.29</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, strategic, particularly; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Significant disparities remain in the achievement of Sustainable Development Goals (SDGs) among European Union (EU) member and candidate countries, despite their common commitments. This article aims to address this issue by examining Türkiye's SDG performance through an in-depth, indicator-based comparative analysis with other EU and non-EU European countries. The methods include standardized scoring of indicators on a 1–10 Likert scale, regression analyses, and comparative visualization techniques. The data comprises quantitative SDG indicators from the EUROSTAT database, gathered from April to August 2024, encompassing 79 indicators related to 16 SDGs. Findings reveal that while Türkiye holds the lowest overall rank, it exhibits notably high performance in specific indicators significantly surpassing the European average in certain areas. These strengths highlight substantial potential areas where Türkiye can leverage existing successes to enhance its overall sustainability performance. However, Türkiye also demonstrates critical weaknesses, with the lowest scores in 32 out of 79 indicators, particularly in SDGs such as gender equality, affordable and clean energy, decent work and economic growth, and no poverty. The study’s results provide policymakers with detailed insights into Türkiye's SDG-related strengths and weaknesses, guiding targeted interventions to reinforce and expand upon these areas. This focused analytical approach offers practical guidance for future strategic planning and emphasizes the value of nuanced, indicator-based evaluations in sustainability assessments.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>link-e98cbb09167ab6f1d2</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Korea in Strategic Competition: A European Perspective</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7119569940</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, strategic, key; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>CSDS In-Depth Paper, No. 20 1 CSDS In-Depth Papers provide critical reflections on issues that affect European security and Europe's partners.The Papers are dedicated to providing analytical insights on specific diplomatic, strategic and security challenges.The Centre for Security, Diplomacy and Strategy (CSDS) seeks to contribute to a better understanding of the key contemporary security and diplomatic challenges of the 21st century -and their impact on Europewhile reaching out to the policy community that will ultimately need to handle such challenges.Our expertise in security studies will seek to establish comprehensive theoretical and policy coverage of strategic competition and its impact on Europe, whilst paying particular attention to the Transatlantic relationship and the wider Indo-Pacific region.Diplomacy as a field of study will be treated broadly and comparatively to encompass traditional statecraft and foreign policy analysis, as well as public, economic and cultural diplomacy.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>link-230c3198e9e7aa8fc6</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Scaling Decision‐Support Tools to Promote Soil Health: Insights From Stakeholders in Europe and Turkey</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/ejss.70113</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, drivers; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>ABSTRACT Soil health and climate change are increasingly impacting agriculture across Europe. Decision support tools (DSTs) have emerged as essential tools to help make accurate, evidence‐based agricultural decisions aimed at enhancing productivity, profitability, and effective soil health management. Nevertheless, the adoption of these tools remains limited among farmers and varies across different regions. The aim of this study was to investigate, through a participatory approach, the challenges and drivers influencing the uptake and adoption of DSTs for sustainable soil management in Europe and Turkey. Our goal was to engage various stakeholders to identify the challenges and drivers associated with this process and collaboratively develop actionable recommendations to expand the application of DSTs. Multi‐stakeholder workshops were conducted in Italy, Latvia, Sweden and Turkey, bringing together end‐users, farmers, advisors, tool developers, researchers and policymakers from diverse agricultural contexts. The discussions during these workshops addressed the current use of DSTs, barriers to adoption, and potential solutions for scaling their use. The findings revealed that the primary barriers to adoption and scaling included costs, tool viability, data complexity, limited access to technical support, compatibility issues and insufficient marketing. To overcome these barriers and enhance the appeal of DSTs to users, stakeholders highlighted the necessity for user‐friendly, affordable tools that offer enhanced transparency, real‐time information, and adaptability to local farming conditions. Furthermore, stakeholders emphasised the importance of user‐driven designs that could stimulate the innovation process and consider the interactions between human and technology. This study emphasises the complexity of adopting and scaling DSTs and the need for considering the local agricultural context. Stakeholder insights were categorised into a set of recommendations such as defining the scope of DSTs application, enhancing capacity building, creating a road map for stakeholders, and considering regional disparities in the participatory implementation process. A systematic, participatory approach is essential for addressing the different dimensions of the DST adoption and scaling process while taking into account regional differences in conditions and user needs.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>argues insights particularly suited Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>link-7b7daccc1ee7d3fc37</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Arguing</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/oso/9780198866053.003.0008</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, particularly, suited; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Abstract This chapter discusses three genres concerned with argumentative advocacy of or against certain positions. The dialogue, a genre with deep ancient roots, was by its very nature suitable for the discussion of controversial subjects. The dissertation, an extremely prolific genre in Central and Northern Europe, was originally the basis of a disputatio, an academic exercise in scholarly argumentation; from the eighteenth century, it began to evolve into the proof of a candidate’s scientific capacity which it is today. Dissertations were avidly collected by some because of the novelty of their contents. Innovativeness was also a hallmark of the monograph, the focused treatment of a single, coherent topic, which rose to new prominence in early modern times. Medium-sized, neatly structured, and thoroughly argued, this type of book was particularly well suited to the presentation of new insights and theories.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>argues insights particularly suited Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>link-f56f35dd24470ffa9a</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Strategic partnerships and China’s diplomacy in Europe: Insights from Italy</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/13691481221127571</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, strategic, ideational; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>As discussions of a ‘new cold war’ between China and the West intensify, it has never been more important to understand how China engages internationally. Crucially, as of 2022, China has established 110 ‘strategic partnerships’, without stipulating any formal treaty of alliance, but we know little about strategic partnerships and how China uses them, despite their centrality as a foreign policy tool. Departing from the assumption of the state as a unitary and monolithic actor in international affairs, this article proposes a new framework of strategic partnerships which incorporates sub-state entities as well as an ideational component, highlighting the image-building purpose that these partnerships serve. Empirically, the analysis focuses on the evolution of the Sino-Italian strategic partnership, drawing on a critical discourse analysis of 1294 news articles published as part of the agreement between the Chinese and Italian news agencies Xinhua and ANSA.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>link-9c1cf8d1fd652c476c</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Strategic European counterterrorism? An empirical analysis</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/09662839.2022.2029847</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, strategic, assessment; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>This paper investigates the extent to which the European Union is strategically engaging against terrorism. It builds on traditional scholarship on strategic thinking and elaborates an analytical framework to empirically assess strategic policy formulation at the supranational level in the case of terrorism. The framework revolves around three analytical categories: i) threat assessment; ii) objectives setting; and iii) policy measures. Through qualitative content analysis of text data, we show that, while objectives are clearly presented in the documents, the threat that the strategy is supposed to counter is unspecified. In addition to that, the formulation of concrete policy measures remains largely vague. Overall, the article adds to the growing academic debate on EU security governance and offers fresh empirical insights on strategic thinking in counterterrorism policy.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>argues insights strategic Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>link-51f41f2ea8a30dfd76</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>claim-c3b72e57c2fbf098</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>It argues that insights from strategic culture research are particularly suited to outline trajectories of the likely when combined with the assessment of internal and external drivers of ideational and material change, the examination of discontinuities, and key uncertainties.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Demystifying the modernized European data protection regime: Cross‐disciplinary insights from legal and regulatory governance scholarship</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/rego.12401</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: insights, key, uncertainties; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Abstract This article critically examines fundamental aspects of the recently reformed European regime for protection of personal data, focusing on the General Data Protection Regulation (GDPR) adopted by the European Union (EU) in 2016. Although the GDPR is now a central concern for many organizations across multiple sectors, many complain that it is arcane, confusing, and complex. By combining knowledge from two disciplinary perspectives – from regulatory governance scholarship, on the one hand, with legal scholarship from the fields of data protection law, constitutional law, and fundamental rights, on the other hand – this article seeks to “demystify” the key elements of the regime's architecture and approach in light of the significant uncertainties concerning the nature of its requirements. In particular, this article examines the tension between the regime's pronounced “risk‐based” approach to compliance and its basic objective of safeguarding fundamental rights, and the challenges facing data protection authorities in providing timely clarifications of the regime's norms. We argue that, despite its complex and arcane character and continuing uncertainty about the precise scope of its requirements, the regime is an innovative hybrid with a significant degree of in‐built “future‐proofing” that should help render it more resistant to being rapidly overtaken or outpaced by organizational–technological developments. The secondary aim of this article is to demonstrate how academic insights from two distinct but related disciplinary perspectives – legal scholarship and regulatory governance studies – offer a potentially fruitful approach to enrich understandings of the European data protection regime in particular, and of the mechanics, efficacy, and legitimacy of regulatory governance regimes more generally.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>argues insights particularly suited Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>link-e32b3a70b6e46a139b</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Application of DPSIR model to ascertain driving forces and their impacts on the Volta basin</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.heliyon.2024.e38734</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, ascertain; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Managing trans-boundary water and its watershed areas is a challenging task. The riparian countries sharing the boundary may have different economic and national goals that can dictate the pressures exerted on water bodies and their catchments areas. The pressure will have dire consequences on the environment, the climate and the sustainability of the Volta River. This paper seeks to apply the Driving Forces-Pressure-State-Impact-Response (DPSIR) framework as a model to ascertain the driving forces and their impacts on the Black and the White sub-basins of the Volta River. The research was carried out through desk study of literature, reports and policies on the Volta basin as well as information from international bodies such as World Bank, United Nations, and European Union among others. The DPSIR framework thus established the state of the ecosystem, pressure exerted, impact and the responses to provide scientific basis for decision-making and address the impacts on the Volta River. The DPSIR framework was focused on Ghana and Burkina Faso due to their large share of the basin. Burkina Faso's share of the Volta basin area is 43 %, whereas, that of Ghana is 41.6 %. The use of DPSIR model will help stakeholders and policy makers in proper decision making. It was therefore recommended that there should be policy regulations to reduce the impact on the environment.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>link-d34f2d827c9097d632</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Evolution and Impact of Hepatitis A Epidemiology in Europe—Systematic Literature Review of the Last 20 Years</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/jvh.14030</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, population; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>While globally hepatitis A (hepA) infections occur in 150 million people annually, European high-income countries now have a low endemicity. However, this results in a more susceptible adult population which is prone to severe illness. To determine current epidemiological characteristics, we performed a systematic literature review to assess the severity of hepA disease in the past two decades in 11 European countries (i.e., Denmark, France, Germany, Greece, Hungary, Italy, the Netherlands, Spain, Sweden, Switzerland and the United Kingdom). Literature search was performed using PubMed and Embase between 1 January 2001 and 14 April 2021. Search terms included the disease (hepA), the 11 selected countries, the term 'outbreaks' and its synonyms, outcomes and terms for hepA virus circulation. In total, 43 records reported data on hepA disease outcomes. Hospitalisation rates varied between the countries, with annual rates exceeding 50% at least once in seven countries. The lowest hospitalisation rates were reported for the Netherlands (≤ 32%) and the highest for Greece (≥ 81%). Liver failure, haemorrhagic and other complications were rarely reported, and case fatality rates were low (0.03%-0.26%). Our findings are consistent with the trends observed globally. This systematic literature review highlights the need to increase awareness of hepA risks and to strengthen prevention strategies. Continuous monitoring of epidemiological data is crucial to assess which populations would most benefit from prevention, mainly with respect to future vaccination recommendations.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>link-6fb48c5ed9b33f2b43</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Education and Fertility: A Review of Recent Research in Europe</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.12765/cpos-2023-21</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>This paper reviews research on education and childbearing in Europe over the last decade. Early demographic research attributed declining fertility in advanced economies in the second half of the twentieth century to increasing female educational levels. The twenty-first century has witnessed further increases in educational attainment coupled with trend reversals in fertility. The relationship between education and fertility has become more complex, sparking renewed interest in the interplay between the two life domains. We examine how educational enrolment and attainment influence individuals’ fertility behaviour – both fertility timing and level – and how the relationship between education and fertility is shaped by contextual factors such as family policies, macroeconomic shocks, and normative changes in gender attitudes. We also summarise the recent literature on educational gradients in male fertility and review methodological developments to address issues of self-selection and unmeasured heterogeneity in the study of education and fertility. Finally, this paper identifies and discusses challenges and important areas for future research.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>link-ff1024aef77e763b4e</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Human and environmental impacts of nanoparticles: a scoping review of the current literature</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s12889-023-15958-4</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, majority; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Use of nanoparticles have established benefits in a wide range of applications, however, the effects of exposure to nanoparticles on health and the environmental risks associated with the production and use of nanoparticles are less well-established. The present study addresses this gap in knowledge by examining, through a scoping review of the current literature, the effects of nanoparticles on human health and the environment. We searched relevant databases including Medline, Web of Science, ScienceDirect, Scopus, CINAHL, Embase, and SAGE journals, as well as Google, Google Scholar, and grey literature from June 2021 to July 2021. After removing duplicate articles, the title and abstracts of 1495 articles were first screened followed by the full-texts of 249 studies, and this resulted in the inclusion of 117 studies in the presented review.In this contribution we conclude that while nanoparticles offer distinct benefits in a range of applications, they pose significant threats to humans and the environment. Using several biological models and biomarkers, the included studies revealed the toxic effects of nanoparticles (mainly zinc oxide, silicon dioxide, titanium dioxide, silver, and carbon nanotubes) to include cell death, production of oxidative stress, DNA damage, apoptosis, and induction of inflammatory responses. Most of the included studies (65.81%) investigated inorganic-based nanoparticles. In terms of biomarkers, most studies (76.9%) used immortalised cell lines, whiles 18.8% used primary cells as the biomarker for assessing human health effect of nanoparticles. Biomarkers that were used for assessing environmental impact of nanoparticles included soil samples and soybean seeds, zebrafish larvae, fish, and Daphnia magna neonates.From the studies included in this work the United States recorded the highest number of publications (n = 30, 25.64%), followed by China, India, and Saudi Arabia recording the same number of publications (n = 8 each), with 95.75% of the studies published from the year 2009. The majority of the included studies (93.16%) assessed impact of nanoparticles on human health, and 95.7% used experimental study design. This shows a clear gap exists in examining the impact of nanoparticles on the environment.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>link-f172e8a7d399dbf1ee</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>The Impact of Patient Support Programs in Europe: A Systematic Literature Review</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s40271-022-00582-y</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>BACKGROUND AND OBJECTIVE: Patient support programs aim to provide solutions beyond the medication itself, by enhancing treatment adherence, improving clinical outcomes, elevating patient experience, and/or increasing quality of life. As patient support programs increasingly play an important role in assisting patients, numerous observational studies and pragmatic trials designed to evaluate their impact on healthcare have been conducted in recent years. This review aims to characterize these studies. METHODS: A systematic literature review, supplemented by a broad search of gray literature, was conducted following PRISMA (Preferred Reporting Items for Systematic Reviews and Meta-Analyses) and Cochrane recommendations. Observational studies and pragmatic trials conducted in Europe to evaluate the impact of patient support programs, published in English or Spanish between 17/03/2010 and 17/03/2020, were reviewed. Two patient support program definitions were applied starting with Ganguli et al.'s broad approach, followed by the European Medicines Agency definition, narrowed to Marketing Authorization Holders organized systems and their medicines. The quality of publications was assessed using the STROBE (Strengthening the Reporting of Observational Studies in Epidemiology) statement 22-item checklist. RESULTS: Of the 49 identified studies following the Ganguli et al. definition, 20 studies met the European Medicines Agency definition and were reviewed. Patient support program impact was evaluated based on a wide range of methodologies: 70% assessed patient support program-related patient-reported outcomes, 55% reported clinical outcomes, and 25% reported economic impacts on health resources. Only 45% conducted a comparative analysis. Overall, 75% of the studies achieved their proposed objectives. CONCLUSIONS: The heterogeneity of the observational studies reviewed reflects the complexity of patient support programs that are built ad hoc for specific diseases, treatments, and patients. Results suggest that patient support programs play a key role in promoting treatment effectiveness, clinical outcomes, and satisfaction. However, there is a need for standardizing the definition of patient support programs and the methods to evaluate their impact.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>link-377760015c98b783b3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>The Evolutionarily Mismatched Impact of Urbanization on Insomnia Symptoms: a Short Review of the Recent Literature</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11920-021-01239-7</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature, majority; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PURPOSE OF REVIEW: For the most part of human existence, individuals have been living a rural lifestyle in a rural setting. However, such sleep-conducive conditions have largely been transformed dramatically by urbanization within a relatively short span of time in recent history, and the resulting evolved mechanisms-environment mismatch is theorized to bring about an increased risk for insomnia symptoms. This brief review of the recent literature is designed to evaluate the veracity of this proposition. RECENT FINDINGS: The majority of recent findings have suggested that most proposed evolutionarily mismatched urban factors are indeed related to the presence of insomnia symptoms. However, there is a general paucity of longitudinal evidence (and for some other factors, a lack of enough evidence of any kind). Although there is a preponderance of recent findings indicating a link between evolutionarily mismatched urban phenomena and insomnia symptoms, more longitudinal data are needed before any causative conclusion can be drawn.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>link-99f16be34bdaf74cc3</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Migrants’ and refugees’ health status and healthcare in Europe: a scoping literature review</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s12889-020-08749-8</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, difficult, population; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>BACKGROUND: There is increasing attention paid to the arrival of migrants from outwith the EU region to the European countries. Healthcare that is universally and equably accessible needs to be provided for these migrants throughout the range of national contexts and in response to complex and evolving individual needs. It is important to look at the evidence available on provision and access to healthcare for migrants to identify barriers to accessing healthcare and better plan necessary changes. METHODS: This review scoped 77 papers from nine European countries (Austria, Cyprus, France, Germany, Greece, Italy, Malta, Spain, and Sweden) in English and in country-specific languages in order to provide an overview of migrants' access to healthcare. The review aims at identifying what is known about access to healthcare as well as healthcare use of migrants and refugees in the EU member states. The evidence included documents from 2011 onwards. RESULTS: The literature reviewed confirms that despite the aspiration to ensure equality of access to healthcare, there is evidence of persistent inequalities between migrants and non-migrants in access to healthcare services. The evidence shows unmet healthcare needs, especially when it comes to mental and dental health as well as the existence of legal barriers in accessing healthcare. Language and communication barriers, overuse of emergency services and underuse of primary healthcare services as well as discrimination are described. CONCLUSIONS: The European situation concerning migrants' and refugees' health status and access to healthcare is heterogeneous and it is difficult to compare and draw any firm conclusions due to the scant evidence. Different diseases are prioritised by different countries, although these priorities do not always correspond to the expressed needs or priorities of the migrants. Mental healthcare, preventive care (immunization) and long-term care in the presence of a growing migrant older population are identified as priorities that deserve greater attention. There is a need to improve the existing data on migrants' health status, needs and access to healthcare to be able to tailor care to the needs of migrants. To conduct research that highlights migrants' own views on their health and barriers to access to healthcare is key.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>link-f59cc7bf5b579fcffe</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>The European media discourse on immigration and its effects: a literature review</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/23808985.2018.1497452</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, shown, leads, negative; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>To understand public opinion about immigration in Europe, one has to understand the media’s role in it. We present a literature review on research on media discourse on immigration and their effects. Despite differences in the way immigration and migrant groups are represented in European media, we can observe common patterns. Migrants are generally under-represented and shown as delinquents or criminals. Although, media framing differs based on specific migrant groups the discourse is focusing on, immigration coverage is often negative and conflict-centred. Frequent exposure to such media messages leads to negative attitudes towards migration, may activate stereotypical cognitions of migrant groups, and even influence vote choice. In addition to discussing these issues in depth, the present review also focuses on comparative findings.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>link-91ab50bd11d3bbe271</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Oral Health Impact Profile in Celiac Patients: Analysis of Recent Findings in a Literature Review</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1155/2018/7848735</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature, according; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>The increment of recording atypical oral manifestation in young patients often related to systematic disease is today a challenge for the therapists. Sometime, the presence of tooth enamel lesions correlated with soft tissue lesions is just a symptom or a trigger sign for a deeper and undetermined disease. Recently, high impact has been developed toward the influence of the diet as a controlled and modifiable factor in patients affected by celiac pathologies. The celiac disease (CD) is a chronic immune-mediated disorder triggered by the ingestion of gluten that appears in genetically predisposed patients. Gluten is a proline-rich and glutamine-rich protein present in wheat (gliadin), barley (hordein), and rye (secalin). The gluten-free diet (GFD) seems to better influence the oral health status of the CD patients. For this reason, the main objective of this revision was to analyze the international data highlighting the relationship between celiac patients and the oral health impact profile. A comprehensive review of the current literature was conducted according to the PRISMA guidelines by accessing the NCBI PubMed database. Authors conducted the search of articles in the English language published from 2008 to 2018. The first analysis with filters recorded 67 manuscripts accordingly with the selected keywords. Finally, a number of 16 appropriate published papers were comprehended in the review. The studies were different in terms of the structure, findings, outcomes, and diet quality evaluation, and for this reason, it was not possible to accomplish a meta-analysis of the recorded data. This manuscript offers some observational evidence to justify the advantages of gluten-free diets related to a better oral health status in the patients involved.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>link-b894727371c0fa3756</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Hyperemesis Gravidarum: A Review of Recent Literature</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1159/000477853</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature, difficult; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>BACKGROUND: In the United States, hyperemesis gravidarum is the most common cause of hospitalization during the first half of pregnancy and is second only to preterm labor for hospitalizations in pregnancy overall. In approximately 0.3-3% of pregnancies, hyperemesis gravidarum is prevalent and this percentage varies on account of different diagnostic criteria and ethnic variation in study populations. Despite extensive research in this field, the mechanism of the disease is largely unknown. Although cases of mortality are rare, hyperemesis gravidarum has been associated with both maternal and fetal morbidity. The current mainstay of treatment relies heavily on supportive measures until improvement of symptoms as part of the natural course of hyperemesis gravidarum, which occurs with progression of gestational age. However, studies have reported that severe, refractory disease manifestations have led to serious adverse outcomes and to termination of pregnancies. SUMMARY: Despite extensive research in the field, the pathogenesis of hyperemesis gravidarum remains unknown. Recent literature points to a genetic predisposition in addition to previously studied factors such as infectious, psychiatric, and hormonal contributions. Maternal morbidity is common and includes psychological effects, financial burden, clinical complications from nutritional deficiencies, gastrointestinal trauma, and in rare cases, neurological damage. The effect of hyperemesis gravidarum on neonatal health is still debated in literature with conflicting results regarding outcomes of birth weight and prematurity. Available therapy options remain largely unchanged in the past several decades and focus on parenteral antiemetic medications, electrolyte repletion, and nutritional support. Most studies of therapeutic options do not consist of randomized control studies and cross-study analysis is difficult due to considerable variation of diagnostic criteria. Key Messages: Hyperemesis gravidarum carries a significant burden on maternal health and US health care. Most published research on pathogenesis is observational and suggests multifactorial associations with hyperemesis gravidarum. Precise, strictly defined criteria for clinical diagnosis are likely to benefit meta-analyses of further research studies regarding pathogenesis as well as therapeutic options.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>link-ef87eef7563465b5d5</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Personality Traits of Entrepreneurs: A Review of Recent Literature</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3386/w24097</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature, population; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>We review the extensive literature since 2000 on the personality traits of entrepreneurs.We first consider baseline personality traits like the Big-5 model, self-efficacy and innovativeness, locus of control, and the need for achievement.We then consider risk attitudes and goals and aspirations of entrepreneurs.Within each area, we separate studies by the type of entrepreneurial behavior considered: entry into entrepreneurship, performance outcomes, and exit from entrepreneurship.This literature shows common results and many points of disagreement, reflective of the heterogeneous nature of entrepreneurship.We label studies by the type of entrepreneurial population studied (e.g., Main Street vs. those backed by venture capital) to identify interesting and irreducible parts of this heterogeneity, while also identifying places where we anticipate future large-scale research and the growing depth of the field are likely to clarify matters.There are many areas, like how firm performance connects to entrepreneurial personality, that are woefully understudied and ripe for major advances if the appropriate crossdisciplinary ingredients are assembled.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>link-010dba079973e735fa</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Hazardous waste and health impact: a systematic review of the scientific literature</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s12940-017-0311-8</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, population; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Waste is part of the agenda of the European Environment and Health Process and included among the topics of the Sixth Ministerial Conference on Environment and Health. Disposal and management of hazardous waste are worldwide challenges. We performed a systematic review to evaluate the evidence of the health impact of hazardous waste exposure, applying transparent and a priori defined methods. The following five steps, based on pre-defined systematic criteria, were applied. 1. Specify the research question, in terms of "Population-Exposure-Comparators-Outcomes" (PECO). POPULATION: people living near hazardous waste sites; Exposure: exposure to hazardous waste; Comparators: all comparators; Outcomes: all diseases/health disorders. 2. Carry out the literature search, in Medline and EMBASE. 3. Select studies for inclusion: original epidemiological studies, published between 1999 and 2015, on populations residentially exposed to hazardous waste. 4. Assess the quality of selected studies, taking into account study design, exposure and outcome assessment, confounding control. 5. Rate the confidence in the body of evidence for each outcome taking into account the reliability of each study, the strength of the association and concordance of results.Fifty-seven papers of epidemiological investigations on the health status of populations living near hazardous waste sites were selected for the evidence evaluation. The association between 95 health outcomes (diseases and disorders) and residential exposure to hazardous waste sites was evaluated. Health effects of residential hazardous waste exposure, previously partially unrecognized, were highlighted. Sufficient evidence was found of association between exposure to oil industry waste that releases high concentrations of hydrogen sulphide and acute symptoms. The evidence of causal relationship with hazardous waste was defined as limited for: liver, bladder, breast and testis cancers, non-Hodgkin lymphoma, asthma, congenital anomalies overall and anomalies of the neural tube, urogenital, connective and musculoskeletal systems, low birth weight and pre-term birth; evidence was defined as inadequate for the other health outcomes. The results, although not conclusive, provide indications that more effective public health policies on hazardous waste management are urgently needed. International, national and local authorities should oppose and eliminate poor, outdated and illegal practices of waste disposal, including illegal transboundary trade, and increase support regulation and its enforcement.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>recent literature ascertain impact Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>link-b2ce4dd765913f9dec</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Pan-European seasonal trends and recent changes of drought frequency and severity</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.gloplacha.2016.11.013</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, according; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>In the last decades drought has become one of the natural disasters with most relevant impacts in Europe and this not only in water scarce areas such as the Mediterranean that are inclined to such events. As a complex natural phenomenon, drought is characterized by many hydro-meteorological aspects, a large variety of possible impacts and definitions. This study focuses on meteorological drought, investigated by using indicators that include precipitation and potential evapotranspiration (PET), i.e. the Standardized Precipitation Index (SPI) and the Standardized Precipitation-Evapotranspiration Index (SPEI). These indicators account for the lack of precipitation and the drying effects of hot temperatures and in this study have been computed for short-accumulation periods (3-month) to capture the seasonality of droughts. The input variables, monthly precipitation and temperature for 1950–2015, stem from daily gridded E-OBS data and indicators were computed on regular grids spanning over the whole of Europe. PET was calculated from minimum and maximum temperatures using the Hargreaves-Samani formulation. Monthly precipitation and PET have then been used to compute the SPI-3 and the SPEI-3 time series. From these series drought events were defined at seasonal scale and trends of frequency and severity of droughts and extreme droughts were analyzed for the periods 1950–2015 and 1981–2015. According to the SPI (driven by precipitation), results show a statistically significant tendency towards less frequent and severe drought events over North-Eastern Europe, especially in winter and spring, and a moderate opposite tendency over Southern Europe, especially in spring and summer. According to the SPEI (driven by precipitation and temperature), Northern Europe shows similar wetting patterns, while Southern and Eastern Europe show a more remarkable drying tendency, especially in summer and autumn. Both for frequency and severity, the evolution towards drier conditions is more relevant in the last three decades over Central Europe in spring, the Mediterranean area in summer, and Eastern Europe in autumn.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>link-4a2b8042237fc1ddff</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Alien species and public health impacts in Europe: a literature review</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3897/neobiota.27.5007</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: literature, article; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Impacts of alien species on human health have recently become a major issue in medical research and invasion ecology, but comprehensive assessments of this subject are largely lacking. Here, we provide a literature review of alien species with public health impacts in Europe based on a systematic search in the Thomson Reuters Web of Science. We detected 77 relevant articles, of which 21 were reviews and 56 were original research articles. The taxonomic focus was on vascular plants (n=31 articles) and dipterans (n=25 articles). The original research articles mainly covered the spread of the study species, while early invasion stages (introduction, establishment) as well as impact and management were less investigated. Alien species of health concern in Europe are mostly introduced as contaminants, and mostly originate from climatically similar regions of the Northern Hemisphere. In those cases (36% of all articles) when information on the trend in range and abundance was provided, this trend was mostly increasing. We detected little information on the severity of the impacts (two articles) and the interaction with climate change (three articles). In 15 original articles (28%) specific management measures were suggested, in only one article the socioeconomic costs were assessed. We conclude that European research on human health impacts of alien species is biased towards few species, and that several important aspects such as early invasion stages, severity of impact and its temporal trends, and the scale of the socioeconomic costs caused are poorly understood. Interdisciplinary projects bridging gaps between ecologists medical researchers, socioeconomists and public health authorities are required to link alien species to severity and trends of impacts, which is a crucial requisite for risk assessment and decision making.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>link-f96d39f1ff3da77aa4</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Brothers and Sisters in Medieval European Literature</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1515/9781782045113</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>strong_candidate</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>eu_in_later_text</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature, shown; EU scope visible. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>A wideranging and groundbreaking investigation of the sibling relationship as shown in European literature, from 500 to 1500. The literature of the European Middle Ages attends closely to the relationship of brother and sister, laying bare sibling behaviours in their most dramatic forms as models to emulate, to marvel at or to avoid. The literary treatment of siblings opens up multiple perspectives on brothers' and sisters' emotions: love, hate, rivalry, desire, nurturing and ambivalence underlie sibling stories. These narratives are in turn inflected by rank, social context andmost crucially, gender. This book examines these sibling relationships, focusing on the important vernacular literatures of Iceland, France, England and Germany, and building on recent research on siblings in psychology, history and social science. Multiple and subtle patterns in sibling interaction are teased out, such as the essential sibling task of "borderwork" (the establishment of individuality despite genetic resemblance), and the tensions caused by the easy substitutability of one sibling for another in certain social situations. When the sibling bond is extended to the in-law relation, complex emotional, strategic and political forces and powerful ambivalences nuancethe relationship still further. Quasi-siblings: foster- or sworn-brothers complete the sibling picture in ways which reflect and contrast with the sibling blood-tie. Carolyne Larrington is a Fellow and Tutor in medieval English literature at St John's College, University of Oxford.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>link-ea21fb630894615312</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>claim-e335375482d9217e</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Recent literature has shown that it is difficult to ascertain the impact of an ageing population on labour productivity.According to the majority of studies, workforce ageing leads to lower employment and a decline in the professional skills of the employed, so we should expect that it has a negative impact on technological changes and productivity.In this article, we present a review of studies on this issue.After that, an empirical study for Bulgaria is provided using sensitivity tests of long-term projections of labour productivity (to 2050), based on population number and age distribution.A model of the International Labour Organisation (ILO) is applied which allows us to calculate three variants of changing age, number and structure of population, assuming three different rates of improvement in life expectancy -fast, medium and slow.The study confirms that an ageing population has a negative effect on labour productivity.The timeframe is long but, with that limitation in mind, the overall direction of the trend is clear.The article concludes with some policy considerations to help ameliorate the effects of Bulgaria's demographic challenge.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Microorganisms with Claimed Probiotic Properties: An Overview of Recent Literature</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ijerph110504745</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>possible_candidate</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>eu_not_established</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Shared claim-specific concepts: recent, literature, shown, majority; EU scope not established. This is a provisional connection, not an outcome finding.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Probiotics are defined as live microorganisms, which when administered in adequate amounts, confer a health benefit on the host. Health benefits have mainly been demonstrated for specific probiotic strains of the following genera: Lactobacillus, Bifidobacterium, Saccharomyces, Enterococcus, Streptococcus, Pediococcus, Leuconostoc, Bacillus, Escherichia coli. The human microbiota is getting a lot of attention today and research has already demonstrated that alteration of this microbiota may have far-reaching consequences. One of the possible routes for correcting dysbiosis is by consuming probiotics. The credibility of specific health claims of probiotics and their safety must be established through science-based clinical studies. This overview summarizes the most commonly used probiotic microorganisms and their demonstrated health claims. As probiotic properties have been shown to be strain specific, accurate identification of particular strains is also very important. On the other hand, it is also demonstrated that the use of various probiotics for immunocompromised patients or patients with a leaky gut has also yielded infections, sepsis, fungemia, bacteraemia. Although the vast majority of probiotics that are used today are generally regarded as safe and beneficial for healthy individuals, caution in selecting and monitoring of probiotics for patients is needed and complete consideration of risk-benefit ratio before prescribing is recommended.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>unchecked</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>recent literature shown Europe</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>